--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/12/2026 7:57:00 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/12/2026 7:17:53 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/12/2016 to 9/12/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/13/2016 to 9/13/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/12/2026 7:17:53 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/13/2026 8:39:34 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/13/2026 8:39:34 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/13/2026 7:33:58 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/13/2016 to 9/13/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/14/2016 to 9/14/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/13/2026 7:33:58 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/14/2026 10:34:19 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/14/2026 10:34:19 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/14/2026 7:39:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/14/2016 to 9/14/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/15/2016 to 9/15/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/14/2026 7:39:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/15/2026 9:15:48 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/15/2026 9:15:48 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/15/2026 7:34:55 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/15/2016 to 9/15/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/16/2016 to 9/16/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/15/2026 7:34:55 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/16/2026 9:15:04 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/16/2026 9:15:04 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/16/2026 7:38:34 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/16/2016 to 9/16/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/17/2016 to 9/17/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/16/2026 7:38:34 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/17/2026 9:15:02 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/17/2026 9:15:02 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/17/2026 7:24:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/17/2016 to 9/17/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/18/2016 to 9/18/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/17/2026 7:24:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/18/2026 7:27:35 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/18/2016 to 9/18/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/19/2016 to 9/19/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/18/2026 7:27:35 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/19/2026 8:22:44 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/19/2026 8:22:44 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/19/2026 8:01:04 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/19/2016 to 9/19/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/20/2016 to 9/20/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/19/2026 8:01:04 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/20/2026 8:24:59 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/20/2026 8:24:59 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/20/2026 7:33:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/20/2016 to 9/20/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/21/2016 to 9/21/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/20/2026 7:33:16 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/21/2026 10:43:14 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/21/2026 10:43:14 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/21/2026 7:38:33 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/21/2016 to 9/21/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/22/2016 to 9/22/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/21/2026 7:38:33 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/22/2026 9:18:42 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/22/2026 9:18:42 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/22/2026 7:40:19 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/22/2016 to 9/22/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/23/2016 to 9/23/2026</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/22/2026 7:40:19 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/23/2026 9:08:03 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,32 +385,32 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9591</t>
+          <t xml:space="preserve">9612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Tualatin Oregon Facility</t>
+          <t xml:space="preserve">Lombard Street Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D4">
-        <v>46477</v>
+        <v>46349</v>
       </c>
       <c s="11" r="E4">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G4">
-        <v>46266</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="0">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c s="10" r="D5">
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c s="11" r="E5">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
@@ -461,10 +461,10 @@
         </is>
       </c>
       <c s="10" r="D6">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E6">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c s="10" r="D7">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E7">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c s="10" r="D8">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -540,24 +540,24 @@
     <row r="9" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">9590</t>
+          <t xml:space="preserve">9591</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">J.R. Johnson, LLC</t>
+          <t xml:space="preserve">Tualatin Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D9">
         <v>46326</v>
       </c>
       <c s="11" r="E9">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
@@ -565,69 +565,69 @@
         </is>
       </c>
       <c s="12" r="G9">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">9588</t>
+          <t xml:space="preserve">9590</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
+          <t xml:space="preserve">J.R. Johnson, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D10">
-        <v>46314</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E10">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G10">
-        <v>46254</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">9556</t>
+          <t xml:space="preserve">9588</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">JeniusBank</t>
+          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D11">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c s="11" r="E11">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G11">
-        <v>46244</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="0">
@@ -638,19 +638,19 @@
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">JeniusBank</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c s="10" r="D12">
         <v>46304</v>
       </c>
       <c s="11" r="E12">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
@@ -664,21 +664,21 @@
     <row r="13" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">9555</t>
+          <t xml:space="preserve">9556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">Bowtech, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D13">
-        <v>46446</v>
+        <v>46304</v>
       </c>
       <c s="11" r="E13">
         <v>1</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c s="12" r="G13">
-        <v>46230</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="0">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c s="10" r="D16">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c s="10" r="D17">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E17">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -819,24 +819,24 @@
     <row r="18" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">9553</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D18">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E18">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -844,34 +844,34 @@
         </is>
       </c>
       <c s="12" r="G18">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D19">
-        <v>46266</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E19">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G19">
@@ -881,94 +881,94 @@
     <row r="20" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D20">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E20">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G20">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D21">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E21">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G21">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E22">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G22">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="0">
@@ -979,19 +979,19 @@
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D23">
         <v>46206</v>
       </c>
       <c s="11" r="E23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
@@ -1010,19 +1010,19 @@
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D24">
         <v>46206</v>
       </c>
       <c s="11" r="E24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
@@ -1036,32 +1036,32 @@
     <row r="25" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D25">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E25">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G25">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="0">
@@ -1072,23 +1072,23 @@
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D26">
         <v>46234</v>
       </c>
       <c s="11" r="E26">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G26">
@@ -1103,19 +1103,19 @@
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D27">
         <v>46234</v>
       </c>
       <c s="11" r="E27">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
@@ -1134,12 +1134,12 @@
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D28">
@@ -1165,19 +1165,19 @@
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D29">
         <v>46234</v>
       </c>
       <c s="11" r="E29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
@@ -1191,55 +1191,55 @@
     <row r="30" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D30">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E30">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G30">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D31">
-        <v>46333</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E31">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c s="12" r="G31">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="0">
@@ -1258,23 +1258,23 @@
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D32">
-        <v>46234</v>
+        <v>46333</v>
       </c>
       <c s="11" r="E32">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G32">
@@ -1289,19 +1289,19 @@
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D33">
         <v>46234</v>
       </c>
       <c s="11" r="E33">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F33">
         <is>
@@ -1320,19 +1320,19 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D34">
         <v>46234</v>
       </c>
       <c s="11" r="E34">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F34">
         <is>
@@ -1351,19 +1351,19 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D35">
         <v>46234</v>
       </c>
       <c s="11" r="E35">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F35">
         <is>
@@ -1382,19 +1382,19 @@
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D36">
         <v>46234</v>
       </c>
       <c s="11" r="E36">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
@@ -1408,86 +1408,86 @@
     <row r="37" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A37">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D37">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E37">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G37">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D38">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E38">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G38">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D39">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E39">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F39">
         <is>
@@ -1495,49 +1495,49 @@
         </is>
       </c>
       <c s="12" r="G39">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D40">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E40">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G40">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
@@ -1546,18 +1546,18 @@
         </is>
       </c>
       <c s="10" r="D41">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E41">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F41">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G41">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="0">
@@ -1568,7 +1568,7 @@
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
@@ -1594,24 +1594,24 @@
     <row r="43" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D43">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E43">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F43">
         <is>
@@ -1619,38 +1619,38 @@
         </is>
       </c>
       <c s="12" r="G43">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D44">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E44">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G44">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="0">
@@ -1661,19 +1661,19 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D45">
         <v>46131</v>
       </c>
       <c s="11" r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
@@ -1687,63 +1687,63 @@
     <row r="46" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D46">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E46">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G46">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D47">
         <v>46117</v>
       </c>
       <c s="11" r="E47">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G47">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="0">
@@ -1754,19 +1754,19 @@
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D48">
         <v>46117</v>
       </c>
       <c s="11" r="E48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F48">
         <is>
@@ -1785,12 +1785,12 @@
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D49">
@@ -1816,12 +1816,12 @@
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D50">
@@ -1847,12 +1847,12 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D51">
@@ -1878,12 +1878,12 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D52">
@@ -1909,12 +1909,12 @@
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D53">
@@ -1940,12 +1940,12 @@
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D54">
@@ -1971,7 +1971,7 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
@@ -2002,7 +2002,7 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
@@ -2033,12 +2033,12 @@
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D57">
@@ -2064,12 +2064,12 @@
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D58">
@@ -2095,12 +2095,12 @@
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D59">
@@ -2126,7 +2126,7 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
@@ -2157,19 +2157,19 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D61">
         <v>46117</v>
       </c>
       <c s="11" r="E61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F61">
         <is>
@@ -2188,19 +2188,19 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D62">
         <v>46117</v>
       </c>
       <c s="11" r="E62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
@@ -2219,19 +2219,19 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D63">
         <v>46117</v>
       </c>
       <c s="11" r="E63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2250,12 +2250,12 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D64">
@@ -2281,12 +2281,12 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D65">
@@ -2307,24 +2307,24 @@
     <row r="66" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A66">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D66">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E66">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
@@ -2343,19 +2343,19 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D67">
         <v>46112</v>
       </c>
       <c s="11" r="E67">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
@@ -2374,19 +2374,19 @@
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D68">
         <v>46112</v>
       </c>
       <c s="11" r="E68">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2400,24 +2400,24 @@
     <row r="69" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D69">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E69">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
@@ -2425,30 +2425,30 @@
         </is>
       </c>
       <c s="12" r="G69">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D70">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E70">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
@@ -2456,30 +2456,30 @@
         </is>
       </c>
       <c s="12" r="G70">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D71">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E71">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c s="12" r="G71">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="0">
@@ -2498,7 +2498,7 @@
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
@@ -2510,7 +2510,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E72">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2529,19 +2529,19 @@
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D73">
         <v>46014</v>
       </c>
       <c s="11" r="E73">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
@@ -2555,43 +2555,43 @@
     <row r="74" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D74">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E74">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G74">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
@@ -2600,29 +2600,29 @@
         </is>
       </c>
       <c s="10" r="D75">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E75">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G75">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c s="10" r="D76">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E76">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
@@ -2648,63 +2648,63 @@
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D77">
         <v>46054</v>
       </c>
       <c s="11" r="E77">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G77">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D78">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E78">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G78">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="0">
@@ -2715,19 +2715,19 @@
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D79">
         <v>45916</v>
       </c>
       <c s="11" r="E79">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
@@ -2746,7 +2746,7 @@
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
@@ -2758,7 +2758,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E80">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
@@ -2777,7 +2777,7 @@
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
@@ -2789,7 +2789,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E81">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
@@ -2803,24 +2803,24 @@
     <row r="82" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D82">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E82">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c s="12" r="G82">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="0">
@@ -2839,23 +2839,23 @@
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D83">
         <v>46022</v>
       </c>
       <c s="11" r="E83">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G83">
@@ -2870,19 +2870,19 @@
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D84">
         <v>46022</v>
       </c>
       <c s="11" r="E84">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
@@ -2901,19 +2901,19 @@
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D85">
         <v>46022</v>
       </c>
       <c s="11" r="E85">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
@@ -2932,19 +2932,19 @@
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D86">
         <v>46022</v>
       </c>
       <c s="11" r="E86">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
@@ -2958,55 +2958,55 @@
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D87">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E87">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G87">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D88">
         <v>46017</v>
       </c>
       <c s="11" r="E88">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
@@ -3020,28 +3020,28 @@
     <row r="89" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D89">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E89">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G89">
@@ -3065,14 +3065,14 @@
         </is>
       </c>
       <c s="10" r="D90">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E90">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G90">
@@ -3082,86 +3082,86 @@
     <row r="91" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D91">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E91">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G91">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D92">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E92">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G92">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D93">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E93">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
@@ -3169,18 +3169,18 @@
         </is>
       </c>
       <c s="12" r="G93">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c s="10" r="D94">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E94">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
@@ -3200,38 +3200,38 @@
         </is>
       </c>
       <c s="12" r="G94">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E95">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G95">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="0">
@@ -3251,14 +3251,14 @@
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E96">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G96">
@@ -3268,24 +3268,24 @@
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E97">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
@@ -3293,34 +3293,34 @@
         </is>
       </c>
       <c s="12" r="G97">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D98">
         <v>45976</v>
       </c>
       <c s="11" r="E98">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G98">
@@ -3330,63 +3330,63 @@
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D99">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E99">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G99">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D100">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E100">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G100">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="0">
@@ -3397,7 +3397,7 @@
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
@@ -3409,7 +3409,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E101">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
@@ -3423,12 +3423,12 @@
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
@@ -3437,41 +3437,41 @@
         </is>
       </c>
       <c s="10" r="D102">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E102">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G102">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E103">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
@@ -3479,18 +3479,18 @@
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
@@ -3499,49 +3499,49 @@
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E104">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E105">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
@@ -3552,19 +3552,19 @@
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D106">
         <v>45912</v>
       </c>
       <c s="11" r="E106">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
@@ -3578,63 +3578,63 @@
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D107">
         <v>45912</v>
       </c>
       <c s="11" r="E107">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E108">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G108">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="0">
@@ -3645,19 +3645,19 @@
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D109">
         <v>45853</v>
       </c>
       <c s="11" r="E109">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
@@ -3676,7 +3676,7 @@
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
@@ -3688,7 +3688,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E110">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
@@ -3719,7 +3719,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E111">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
@@ -3733,86 +3733,86 @@
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E112">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G112">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E113">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E114">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E115">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E116">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
@@ -3888,24 +3888,24 @@
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E117">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
@@ -3913,30 +3913,30 @@
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D118">
         <v>45838</v>
       </c>
       <c s="11" r="E118">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
@@ -3950,94 +3950,94 @@
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D119">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E119">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D120">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E120">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D121">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E121">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G121">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="0">
@@ -4048,19 +4048,19 @@
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D122">
         <v>45866</v>
       </c>
       <c s="11" r="E122">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
@@ -4074,55 +4074,55 @@
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E123">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E124">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
@@ -4130,85 +4130,85 @@
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E125">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E126">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D127">
@@ -4219,69 +4219,69 @@
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D128">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E128">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G128">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D129">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E129">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G129">
@@ -4291,43 +4291,43 @@
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E130">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G130">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
@@ -4336,103 +4336,103 @@
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E131">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G131">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D132">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E132">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G132">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E133">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G133">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E134">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
@@ -4440,38 +4440,38 @@
         </is>
       </c>
       <c s="12" r="G134">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E135">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G135">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="0">
@@ -4482,19 +4482,19 @@
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D136">
         <v>45707</v>
       </c>
       <c s="11" r="E136">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
@@ -4508,63 +4508,63 @@
     <row r="137" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E137">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G137">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E138">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G138">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="0">
@@ -4575,19 +4575,19 @@
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D139">
         <v>45696</v>
       </c>
       <c s="11" r="E139">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
@@ -4601,86 +4601,86 @@
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E140">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G140">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E141">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D142">
         <v>45931</v>
       </c>
       <c s="11" r="E142">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
@@ -4694,43 +4694,43 @@
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E143">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G143">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
@@ -4739,18 +4739,18 @@
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E144">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G144">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="0">
@@ -4761,19 +4761,19 @@
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D145">
         <v>45726</v>
       </c>
       <c s="11" r="E145">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4792,19 +4792,19 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D146">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E146">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4823,19 +4823,19 @@
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D147">
         <v>45725</v>
       </c>
       <c s="11" r="E147">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
@@ -4854,19 +4854,19 @@
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E148">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
@@ -4885,12 +4885,12 @@
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D149">
@@ -4916,12 +4916,12 @@
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D150">
@@ -4947,19 +4947,19 @@
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E151">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
@@ -4978,19 +4978,19 @@
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E152">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
@@ -5009,7 +5009,7 @@
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E153">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5040,19 +5040,19 @@
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E154">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
@@ -5066,12 +5066,12 @@
     <row r="155" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
@@ -5080,72 +5080,72 @@
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E155">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G155">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E156">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G156">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E157">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
@@ -5153,100 +5153,100 @@
         </is>
       </c>
       <c s="12" r="G157">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E158">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E159">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G159">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D160">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E160">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G160">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="0">
@@ -5257,19 +5257,19 @@
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D161">
         <v>45611</v>
       </c>
       <c s="11" r="E161">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
@@ -5300,7 +5300,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E162">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c s="9" t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C163">
@@ -5331,7 +5331,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E163">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5345,28 +5345,28 @@
     <row r="164" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A164">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C164">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E164">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G164">
@@ -5376,24 +5376,24 @@
     <row r="165" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C165">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E165">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
@@ -5401,38 +5401,38 @@
         </is>
       </c>
       <c s="12" r="G165">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E166">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G166">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="0">
@@ -5443,23 +5443,23 @@
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D167">
         <v>45544</v>
       </c>
       <c s="11" r="E167">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G167">
@@ -5469,55 +5469,55 @@
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E168">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E169">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E170">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
@@ -5576,14 +5576,14 @@
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E171">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G171">
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
@@ -5638,14 +5638,14 @@
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E173">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G173">
@@ -5655,24 +5655,24 @@
     <row r="174" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C174">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E174">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c s="12" r="G174">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="175" ht="18" customHeight="0">
@@ -5700,14 +5700,14 @@
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E175">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G175">
@@ -5717,24 +5717,24 @@
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C176">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E176">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
@@ -5742,13 +5742,13 @@
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E177">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
@@ -5773,18 +5773,18 @@
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E178">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
@@ -5804,30 +5804,30 @@
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D179">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E179">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E180">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E181">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
@@ -5903,32 +5903,32 @@
     <row r="182" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C182">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E182">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G182">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="0">
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E183">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
@@ -5996,43 +5996,43 @@
     <row r="185" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E185">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G185">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E186">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
@@ -6052,111 +6052,111 @@
         </is>
       </c>
       <c s="12" r="G186">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D187">
         <v>45471</v>
       </c>
       <c s="11" r="E187">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E188">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E189">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
@@ -6165,134 +6165,134 @@
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E190">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E191">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G191">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D192">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E192">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G192">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D193">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E193">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G193">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E194">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6300,18 +6300,18 @@
         </is>
       </c>
       <c s="12" r="G194">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
@@ -6320,41 +6320,41 @@
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E195">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E196">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
@@ -6373,7 +6373,7 @@
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
@@ -6385,7 +6385,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E197">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
@@ -6399,24 +6399,24 @@
     <row r="198" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E198">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
@@ -6424,34 +6424,34 @@
         </is>
       </c>
       <c s="12" r="G198">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E199">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G199">
@@ -6466,19 +6466,19 @@
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D200">
         <v>45382</v>
       </c>
       <c s="11" r="E200">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6497,19 +6497,19 @@
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D201">
         <v>45382</v>
       </c>
       <c s="11" r="E201">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6528,7 +6528,7 @@
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
@@ -6540,7 +6540,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E202">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
@@ -6559,12 +6559,12 @@
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D203">
@@ -6585,32 +6585,32 @@
     <row r="204" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E204">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G204">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="0">
@@ -6621,23 +6621,23 @@
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D205">
         <v>45366</v>
       </c>
       <c s="11" r="E205">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G205">
@@ -6647,55 +6647,55 @@
     <row r="206" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E206">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G206">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E207">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c s="12" r="G207">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="0">
@@ -6714,19 +6714,19 @@
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D208">
         <v>45275</v>
       </c>
       <c s="11" r="E208">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6745,19 +6745,19 @@
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D209">
         <v>45275</v>
       </c>
       <c s="11" r="E209">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6776,19 +6776,19 @@
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D210">
         <v>45275</v>
       </c>
       <c s="11" r="E210">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6802,24 +6802,24 @@
     <row r="211" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A211">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D211">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E211">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6827,30 +6827,30 @@
         </is>
       </c>
       <c s="12" r="G211">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="212" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D212">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E212">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6858,30 +6858,30 @@
         </is>
       </c>
       <c s="12" r="G212">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E213">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c s="12" r="G213">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="0">
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E214">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E215">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
@@ -6957,24 +6957,24 @@
     <row r="216" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E216">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
@@ -6982,18 +6982,18 @@
         </is>
       </c>
       <c s="12" r="G216">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
@@ -7005,7 +7005,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E217">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7019,12 +7019,12 @@
     <row r="218" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
@@ -7036,7 +7036,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E218">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7050,24 +7050,24 @@
     <row r="219" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D219">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E219">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7075,61 +7075,61 @@
         </is>
       </c>
       <c s="12" r="G219">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E220">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G220">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E221">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c s="12" r="G221">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="0">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E222">
         <v>2</v>
@@ -7188,14 +7188,14 @@
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E223">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G223">
@@ -7210,7 +7210,7 @@
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
@@ -7222,11 +7222,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E224">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G224">
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
@@ -7272,7 +7272,7 @@
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
@@ -7284,7 +7284,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E227">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E228">
         <v>1</v>
@@ -7374,14 +7374,14 @@
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E229">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G229">
@@ -7396,7 +7396,7 @@
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
@@ -7408,7 +7408,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E230">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
@@ -7422,86 +7422,86 @@
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E231">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E232">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G232">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E233">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
@@ -7515,24 +7515,24 @@
     <row r="234" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D234">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E234">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c s="12" r="G234">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="0">
@@ -7560,10 +7560,10 @@
         </is>
       </c>
       <c s="10" r="D235">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E235">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F235">
         <is>
@@ -7577,24 +7577,24 @@
     <row r="236" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E236">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c s="12" r="G236">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="0">
@@ -7613,19 +7613,19 @@
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E237">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
@@ -7639,32 +7639,32 @@
     <row r="238" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E238">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G238">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="0">
@@ -7684,10 +7684,10 @@
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E239">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
@@ -7701,24 +7701,24 @@
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E240">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7726,30 +7726,30 @@
         </is>
       </c>
       <c s="12" r="G240">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E241">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
@@ -7757,123 +7757,123 @@
         </is>
       </c>
       <c s="12" r="G241">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E242">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G242">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E243">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G243">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E244">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G244">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E245">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
@@ -7881,30 +7881,30 @@
         </is>
       </c>
       <c s="12" r="G245">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E246">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
@@ -7912,61 +7912,61 @@
         </is>
       </c>
       <c s="12" r="G246">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E247">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G247">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E248">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
@@ -7974,30 +7974,30 @@
         </is>
       </c>
       <c s="12" r="G248">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E249">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c s="12" r="G249">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
@@ -8016,12 +8016,12 @@
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D250">
@@ -8047,12 +8047,12 @@
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D251">
@@ -8078,12 +8078,12 @@
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D252">
@@ -8109,12 +8109,12 @@
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D253">
@@ -8135,86 +8135,86 @@
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E254">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G254">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E255">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G255">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E256">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
@@ -8228,24 +8228,24 @@
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E257">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8253,30 +8253,30 @@
         </is>
       </c>
       <c s="12" r="G257">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D258">
         <v>45079</v>
       </c>
       <c s="11" r="E258">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
@@ -8290,12 +8290,12 @@
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
@@ -8304,103 +8304,103 @@
         </is>
       </c>
       <c s="10" r="D259">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E259">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G259">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E260">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E261">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E262">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
@@ -8408,30 +8408,30 @@
         </is>
       </c>
       <c s="12" r="G262">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C263">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E263">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
@@ -8439,80 +8439,80 @@
         </is>
       </c>
       <c s="12" r="G263">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E264">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G264">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E265">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G265">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
@@ -8521,41 +8521,41 @@
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E266">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E267">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8563,30 +8563,30 @@
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E268">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,30 +8594,30 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E269">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
@@ -8645,10 +8645,10 @@
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E270">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8662,74 +8662,74 @@
     <row r="271" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E271">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G271">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E272">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E273">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8749,30 +8749,30 @@
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E274">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
@@ -8803,7 +8803,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E275">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
@@ -8817,24 +8817,24 @@
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E276">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
@@ -8842,30 +8842,30 @@
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E277">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8873,30 +8873,30 @@
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E278">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
@@ -8924,10 +8924,10 @@
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E279">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E280">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E281">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E282">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E283">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9065,12 +9065,12 @@
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E284">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9090,30 +9090,30 @@
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E285">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9121,30 +9121,30 @@
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E286">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
@@ -9163,7 +9163,7 @@
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
@@ -9175,7 +9175,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E287">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
@@ -9194,19 +9194,19 @@
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D288">
         <v>44469</v>
       </c>
       <c s="11" r="E288">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
@@ -9220,24 +9220,24 @@
     <row r="289" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C289">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E289">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9245,30 +9245,30 @@
         </is>
       </c>
       <c s="12" r="G289">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C290">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E290">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9276,18 +9276,18 @@
         </is>
       </c>
       <c s="12" r="G290">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E291">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
@@ -9307,18 +9307,18 @@
         </is>
       </c>
       <c s="12" r="G291">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
@@ -9327,49 +9327,49 @@
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E292">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C293">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E293">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G293">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="0">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E294">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
@@ -9406,32 +9406,32 @@
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E295">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E296">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c s="10" r="D297">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E297">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c s="10" r="D298">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E298">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
@@ -9530,12 +9530,12 @@
     <row r="299" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
@@ -9547,7 +9547,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E299">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
@@ -9561,24 +9561,24 @@
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E300">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c s="12" r="G300">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="0">
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E301">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
@@ -9623,24 +9623,24 @@
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E302">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
@@ -9648,100 +9648,100 @@
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E303">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E304">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E305">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
@@ -9764,11 +9764,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E306">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G306">
@@ -9778,12 +9778,12 @@
     <row r="307" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
@@ -9792,29 +9792,29 @@
         </is>
       </c>
       <c s="10" r="D307">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E307">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G307">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
@@ -9823,69 +9823,69 @@
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E308">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G308">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E309">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G309">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E310">
         <v>59</v>
@@ -9896,100 +9896,100 @@
         </is>
       </c>
       <c s="12" r="G310">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E311">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G311">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Elgin</t>
         </is>
       </c>
       <c s="10" r="D312">
-        <v>43914</v>
+        <v>44197</v>
       </c>
       <c s="11" r="E312">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44099</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">7241</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">SP+</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D313">
-        <v>43903</v>
+        <v>43914</v>
       </c>
       <c s="11" r="E313">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44091</v>
+        <v>44099</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
@@ -10000,19 +10000,19 @@
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D314">
         <v>43903</v>
       </c>
       <c s="11" r="E314">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
@@ -10031,19 +10031,19 @@
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
+          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D315">
         <v>43903</v>
       </c>
       <c s="11" r="E315">
-        <v>111</v>
+        <v>358</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
@@ -10057,32 +10057,32 @@
     <row r="316" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">7217</t>
+          <t xml:space="preserve">7218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">PF Chang's</t>
+          <t xml:space="preserve">Sodexo - Medford SD</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D316">
-        <v>44092</v>
+        <v>43903</v>
       </c>
       <c s="11" r="E316">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F316">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G316">
-        <v>44092</v>
+        <v>44091</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="0">
@@ -10093,12 +10093,12 @@
       </c>
       <c s="9" t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
+          <t xml:space="preserve">PF Chang's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C317">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D317">
@@ -10119,32 +10119,32 @@
     <row r="318" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">7215</t>
+          <t xml:space="preserve">7217</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
+          <t xml:space="preserve">PF Chang's - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44137</v>
+        <v>44092</v>
       </c>
       <c s="11" r="E318">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G318">
-        <v>44077</v>
+        <v>44092</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="0">
@@ -10155,19 +10155,19 @@
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
+          <t xml:space="preserve">LAGS Medical Center - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D319">
         <v>44137</v>
       </c>
       <c s="11" r="E319">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
@@ -10181,12 +10181,12 @@
     <row r="320" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">7211</t>
+          <t xml:space="preserve">7215</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">Bon Appetit</t>
+          <t xml:space="preserve">LAGS Medical Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
@@ -10195,18 +10195,18 @@
         </is>
       </c>
       <c s="10" r="D320">
-        <v>44104</v>
+        <v>44137</v>
       </c>
       <c s="11" r="E320">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G320">
-        <v>44075</v>
+        <v>44077</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="0">
@@ -10229,11 +10229,11 @@
         <v>44104</v>
       </c>
       <c s="11" r="E321">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G321">
@@ -10243,24 +10243,24 @@
     <row r="322" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">7209</t>
+          <t xml:space="preserve">7211</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
+          <t xml:space="preserve">Bon Appetit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D322">
-        <v>44143</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E322">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
@@ -10268,159 +10268,189 @@
         </is>
       </c>
       <c s="12" r="G322">
-        <v>44082</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">7207</t>
+          <t xml:space="preserve">7209</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">PGE - Boardman</t>
+          <t xml:space="preserve">Dave &amp; Buster's</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
         <is>
-          <t xml:space="preserve">Boardman</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D323">
-        <v>44140</v>
+        <v>44143</v>
       </c>
       <c s="11" r="E323">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G323">
-        <v>44075</v>
+        <v>44082</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">PGE - Boardman</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D324"/>
-      <c s="13" t="str" r="E324"/>
+          <t xml:space="preserve">Boardman</t>
+        </is>
+      </c>
+      <c s="10" r="D324">
+        <v>44140</v>
+      </c>
+      <c s="11" r="E324">
+        <v>22</v>
+      </c>
       <c s="9" t="inlineStr" r="F324">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G324">
-        <v>44909</v>
+        <v>44075</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D325"/>
       <c s="13" t="str" r="E325"/>
       <c s="9" t="inlineStr" r="F325">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G325">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="326" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A326">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B326">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C326">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D326"/>
       <c s="13" t="str" r="E326"/>
       <c s="9" t="inlineStr" r="F326">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G326">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="327" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A327">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B327">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C327">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D327"/>
+      <c s="13" t="str" r="E327"/>
+      <c s="9" t="inlineStr" r="F327">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G326">
+      <c s="12" r="G327">
         <v>45887</v>
       </c>
     </row>
-    <row r="327" ht="3.55" customHeight="0">
-      <c s="14" t="inlineStr" r="A327">
+    <row r="328" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B327">
+      <c s="14" t="inlineStr" r="B328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C327">
+      <c s="14" t="inlineStr" r="C328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D327">
+      <c s="14" t="inlineStr" r="D328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E327">
+      <c s="14" t="inlineStr" r="E328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F327">
+      <c s="14" t="inlineStr" r="F328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G327">
+      <c s="14" t="inlineStr" r="G328">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="328" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10430,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/23/2026 9:08:03 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/23/2026 7:24:15 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/23/2016 to 9/23/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/24/2016 to 9/24/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/23/2026 7:24:15 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/24/2026 9:26:35 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/24/2026 9:26:35 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/24/2026 7:44:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/24/2016 to 9/24/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/25/2016 to 9/25/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/24/2026 7:44:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/25/2026 9:27:03 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/25/2026 9:27:03 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/25/2026 7:45:51 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/25/2016 to 9/25/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/26/2016 to 9/26/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/25/2026 7:45:51 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/26/2026 7:48:38 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/26/2016 to 9/26/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/27/2016 to 9/27/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/26/2026 7:48:38 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/27/2026 9:26:30 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/27/2026 9:26:30 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/27/2026 7:49:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/27/2016 to 9/27/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/28/2016 to 9/28/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/27/2026 7:49:39 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/28/2026 12:18:33 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/28/2026 12:18:33 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/28/2026 8:29:57 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/28/2016 to 9/28/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/29/2016 to 9/29/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/28/2026 8:29:57 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/29/2026 10:46:15 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/29/2026 10:46:15 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/29/2026 8:12:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/29/2016 to 9/29/2026</t>
+          <t xml:space="preserve">WARNs Received: 9/30/2016 to 9/30/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/29/2026 8:12:18 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/30/2026 10:32:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/30/2026 10:32:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/30/2026 8:24:48 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 9/30/2016 to 9/30/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/1/2016 to 10/1/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 9/30/2026 8:24:48 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/1/2026 11:02:42 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/1/2026 11:02:42 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/1/2026 8:21:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/1/2016 to 10/1/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/2/2016 to 10/2/2026</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/1/2026 8:21:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/2/2026 2:51:12 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10460,7 +10460,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/2/2026 2:51:12 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/2/2026 10:22:24 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -4885,12 +4885,12 @@
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D149">
@@ -4916,12 +4916,12 @@
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D150">
@@ -4947,12 +4947,12 @@
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D151">
@@ -7272,7 +7272,7 @@
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
@@ -7284,7 +7284,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7303,7 +7303,7 @@
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
@@ -7315,7 +7315,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7396,7 +7396,7 @@
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
@@ -7408,7 +7408,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E230">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
@@ -7427,7 +7427,7 @@
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
@@ -7439,7 +7439,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E231">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
@@ -9964,493 +9964,122 @@
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7241</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">SP+</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D313">
-        <v>43914</v>
-      </c>
-      <c s="11" r="E313">
-        <v>89</v>
-      </c>
+          <t xml:space="preserve">ELGIN                         </t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D313"/>
+      <c s="13" t="str" r="E313"/>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44099</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Sodexo - Gresham-Barlow SD  </t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Gresham</t>
-        </is>
-      </c>
-      <c s="10" r="D314">
-        <v>43903</v>
-      </c>
-      <c s="11" r="E314">
-        <v>85</v>
-      </c>
+          <t xml:space="preserve">Mesa, AZ</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D314"/>
+      <c s="13" t="str" r="E314"/>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G314">
-        <v>44091</v>
+        <v>45125</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7218</t>
+          <t xml:space="preserve">9324</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Sodexo - Salem-Keizer SD</t>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Salem</t>
-        </is>
-      </c>
-      <c s="10" r="D315">
-        <v>43903</v>
-      </c>
-      <c s="11" r="E315">
-        <v>358</v>
-      </c>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D315"/>
+      <c s="13" t="str" r="E315"/>
       <c s="9" t="inlineStr" r="F315">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G315">
-        <v>44091</v>
-      </c>
-    </row>
-    <row r="316" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A316">
-        <is>
-          <t xml:space="preserve">7218</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B316">
-        <is>
-          <t xml:space="preserve">Sodexo - Medford SD</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C316">
-        <is>
-          <t xml:space="preserve">Medford</t>
-        </is>
-      </c>
-      <c s="10" r="D316">
-        <v>43903</v>
-      </c>
-      <c s="11" r="E316">
-        <v>111</v>
-      </c>
-      <c s="9" t="inlineStr" r="F316">
-        <is>
-          <t xml:space="preserve">Temporary Layoff</t>
-        </is>
-      </c>
-      <c s="12" r="G316">
-        <v>44091</v>
-      </c>
-    </row>
-    <row r="317" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A317">
-        <is>
-          <t xml:space="preserve">7217</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B317">
-        <is>
-          <t xml:space="preserve">PF Chang's</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C317">
-        <is>
-          <t xml:space="preserve">Hillsboro</t>
-        </is>
-      </c>
-      <c s="10" r="D317">
-        <v>44092</v>
-      </c>
-      <c s="11" r="E317">
-        <v>75</v>
-      </c>
-      <c s="9" t="inlineStr" r="F317">
-        <is>
-          <t xml:space="preserve">Other</t>
-        </is>
-      </c>
-      <c s="12" r="G317">
-        <v>44092</v>
-      </c>
-    </row>
-    <row r="318" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A318">
-        <is>
-          <t xml:space="preserve">7217</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B318">
-        <is>
-          <t xml:space="preserve">PF Chang's - Eugene</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C318">
-        <is>
-          <t xml:space="preserve">Eugene</t>
-        </is>
-      </c>
-      <c s="10" r="D318">
-        <v>44092</v>
-      </c>
-      <c s="11" r="E318">
-        <v>75</v>
-      </c>
-      <c s="9" t="inlineStr" r="F318">
-        <is>
-          <t xml:space="preserve">Other</t>
-        </is>
-      </c>
-      <c s="12" r="G318">
-        <v>44092</v>
-      </c>
-    </row>
-    <row r="319" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A319">
-        <is>
-          <t xml:space="preserve">7215</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B319">
-        <is>
-          <t xml:space="preserve">LAGS Medical Center - Salem</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C319">
-        <is>
-          <t xml:space="preserve">Salem</t>
-        </is>
-      </c>
-      <c s="10" r="D319">
-        <v>44137</v>
-      </c>
-      <c s="11" r="E319">
-        <v>4</v>
-      </c>
-      <c s="9" t="inlineStr" r="F319">
-        <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
-        </is>
-      </c>
-      <c s="12" r="G319">
-        <v>44077</v>
-      </c>
-    </row>
-    <row r="320" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A320">
-        <is>
-          <t xml:space="preserve">7215</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B320">
-        <is>
-          <t xml:space="preserve">LAGS Medical Center - Portland</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C320">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D320">
-        <v>44137</v>
-      </c>
-      <c s="11" r="E320">
-        <v>7</v>
-      </c>
-      <c s="9" t="inlineStr" r="F320">
-        <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
-        </is>
-      </c>
-      <c s="12" r="G320">
-        <v>44077</v>
-      </c>
-    </row>
-    <row r="321" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A321">
-        <is>
-          <t xml:space="preserve">7211</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B321">
-        <is>
-          <t xml:space="preserve">Bon Appetit</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C321">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D321">
-        <v>44104</v>
-      </c>
-      <c s="11" r="E321">
-        <v>224</v>
-      </c>
-      <c s="9" t="inlineStr" r="F321">
-        <is>
-          <t xml:space="preserve">Other</t>
-        </is>
-      </c>
-      <c s="12" r="G321">
-        <v>44075</v>
-      </c>
-    </row>
-    <row r="322" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A322">
-        <is>
-          <t xml:space="preserve">7211</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B322">
-        <is>
-          <t xml:space="preserve">Bon Appetit</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C322">
-        <is>
-          <t xml:space="preserve">Portland</t>
-        </is>
-      </c>
-      <c s="10" r="D322">
-        <v>44104</v>
-      </c>
-      <c s="11" r="E322">
-        <v>170</v>
-      </c>
-      <c s="9" t="inlineStr" r="F322">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G322">
-        <v>44075</v>
-      </c>
-    </row>
-    <row r="323" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A323">
-        <is>
-          <t xml:space="preserve">7209</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B323">
-        <is>
-          <t xml:space="preserve">Dave &amp; Buster's</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C323">
-        <is>
-          <t xml:space="preserve">Happy Valley</t>
-        </is>
-      </c>
-      <c s="10" r="D323">
-        <v>44143</v>
-      </c>
-      <c s="11" r="E323">
-        <v>84</v>
-      </c>
-      <c s="9" t="inlineStr" r="F323">
-        <is>
-          <t xml:space="preserve">Reduction</t>
-        </is>
-      </c>
-      <c s="12" r="G323">
-        <v>44082</v>
-      </c>
-    </row>
-    <row r="324" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A324">
-        <is>
-          <t xml:space="preserve">7207</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B324">
-        <is>
-          <t xml:space="preserve">PGE - Boardman</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C324">
-        <is>
-          <t xml:space="preserve">Boardman</t>
-        </is>
-      </c>
-      <c s="10" r="D324">
-        <v>44140</v>
-      </c>
-      <c s="11" r="E324">
-        <v>22</v>
-      </c>
-      <c s="9" t="inlineStr" r="F324">
-        <is>
-          <t xml:space="preserve">Permanent closure</t>
-        </is>
-      </c>
-      <c s="12" r="G324">
-        <v>44075</v>
-      </c>
-    </row>
-    <row r="325" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A325">
-        <is>
-          <t xml:space="preserve">8470</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B325">
-        <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C325">
-        <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D325"/>
-      <c s="13" t="str" r="E325"/>
-      <c s="9" t="inlineStr" r="F325">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G325">
-        <v>44909</v>
-      </c>
-    </row>
-    <row r="326" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A326">
-        <is>
-          <t xml:space="preserve">8592</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B326">
-        <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C326">
-        <is>
-          <t xml:space="preserve">Mesa, AZ</t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D326"/>
-      <c s="13" t="str" r="E326"/>
-      <c s="9" t="inlineStr" r="F326">
-        <is>
-          <t xml:space="preserve">Permanent closure</t>
-        </is>
-      </c>
-      <c s="12" r="G326">
-        <v>45125</v>
-      </c>
-    </row>
-    <row r="327" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A327">
-        <is>
-          <t xml:space="preserve">9324</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="B327">
-        <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C327">
-        <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D327"/>
-      <c s="13" t="str" r="E327"/>
-      <c s="9" t="inlineStr" r="F327">
-        <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
-        </is>
-      </c>
-      <c s="12" r="G327">
         <v>45887</v>
       </c>
     </row>
-    <row r="328" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A328">
+    <row r="316" ht="3.55" customHeight="0">
+      <c s="14" t="inlineStr" r="A316">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B328">
+      <c s="14" t="inlineStr" r="B316">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C328">
+      <c s="14" t="inlineStr" r="C316">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D328">
+      <c s="14" t="inlineStr" r="D316">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E328">
+      <c s="14" t="inlineStr" r="E316">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F328">
+      <c s="14" t="inlineStr" r="F316">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G328">
+      <c s="14" t="inlineStr" r="G316">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
+    <row r="317" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10460,7 +10089,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/2/2026 10:22:24 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/2/2026 8:08:58 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/2/2016 to 10/2/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/3/2016 to 10/3/2026</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/2/2026 8:08:58 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/3/2026 8:30:42 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10089,7 +10089,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/3/2026 8:30:42 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/3/2026 8:37:21 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/3/2016 to 10/3/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/4/2016 to 10/4/2026</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/3/2026 8:37:21 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/4/2026 9:29:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10089,7 +10089,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/4/2026 9:29:22 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/4/2026 8:18:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/4/2016 to 10/4/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/5/2016 to 10/5/2026</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/4/2026 8:18:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/5/2026 9:12:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/5/2016 to 10/5/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/6/2016 to 10/6/2026</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/5/2026 9:12:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/6/2026 10:58:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,63 +385,63 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9612</t>
+          <t xml:space="preserve">9637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Lombard Street Facility</t>
+          <t xml:space="preserve">Medford Delivery Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D4">
-        <v>46349</v>
+        <v>46363</v>
       </c>
       <c s="11" r="E4">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G4">
-        <v>46288</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">9591</t>
+          <t xml:space="preserve">9612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">Tualatin Oregon Facility</t>
+          <t xml:space="preserve">Lombard Street Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D5">
-        <v>46477</v>
+        <v>46349</v>
       </c>
       <c s="11" r="E5">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G5">
-        <v>46266</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="0">
@@ -461,10 +461,10 @@
         </is>
       </c>
       <c s="10" r="D6">
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c s="11" r="E6">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c s="10" r="D7">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E7">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c s="10" r="D8">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E8">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c s="10" r="D9">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
@@ -571,24 +571,24 @@
     <row r="10" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">9590</t>
+          <t xml:space="preserve">9591</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">J.R. Johnson, LLC</t>
+          <t xml:space="preserve">Tualatin Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D10">
         <v>46326</v>
       </c>
       <c s="11" r="E10">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
@@ -596,69 +596,69 @@
         </is>
       </c>
       <c s="12" r="G10">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">9588</t>
+          <t xml:space="preserve">9590</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
+          <t xml:space="preserve">J.R. Johnson, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D11">
-        <v>46314</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E11">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G11">
-        <v>46254</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">9556</t>
+          <t xml:space="preserve">9588</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">JeniusBank</t>
+          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D12">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c s="11" r="E12">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G12">
-        <v>46244</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="0">
@@ -669,19 +669,19 @@
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">JeniusBank</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c s="10" r="D13">
         <v>46304</v>
       </c>
       <c s="11" r="E13">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F13">
         <is>
@@ -695,21 +695,21 @@
     <row r="14" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">9555</t>
+          <t xml:space="preserve">9556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">Bowtech, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46446</v>
+        <v>46304</v>
       </c>
       <c s="11" r="E14">
         <v>1</v>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c s="12" r="G14">
-        <v>46230</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="0">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c s="10" r="D16">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E16">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c s="10" r="D17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c s="10" r="D18">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E18">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -850,24 +850,24 @@
     <row r="19" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">9553</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D19">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E19">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
@@ -875,34 +875,34 @@
         </is>
       </c>
       <c s="12" r="G19">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D20">
-        <v>46266</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E20">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G20">
@@ -912,94 +912,94 @@
     <row r="21" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D21">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E21">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G21">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E22">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G22">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E23">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G23">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="0">
@@ -1010,19 +1010,19 @@
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D24">
         <v>46206</v>
       </c>
       <c s="11" r="E24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
@@ -1041,19 +1041,19 @@
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D25">
         <v>46206</v>
       </c>
       <c s="11" r="E25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
@@ -1067,32 +1067,32 @@
     <row r="26" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A26">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D26">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E26">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G26">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="0">
@@ -1103,23 +1103,23 @@
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D27">
         <v>46234</v>
       </c>
       <c s="11" r="E27">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G27">
@@ -1134,19 +1134,19 @@
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D28">
         <v>46234</v>
       </c>
       <c s="11" r="E28">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
@@ -1165,12 +1165,12 @@
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D29">
@@ -1196,19 +1196,19 @@
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D30">
         <v>46234</v>
       </c>
       <c s="11" r="E30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
@@ -1222,55 +1222,55 @@
     <row r="31" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D31">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E31">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G31">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D32">
-        <v>46333</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E32">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c s="12" r="G32">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="0">
@@ -1289,23 +1289,23 @@
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D33">
-        <v>46234</v>
+        <v>46333</v>
       </c>
       <c s="11" r="E33">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G33">
@@ -1320,19 +1320,19 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D34">
         <v>46234</v>
       </c>
       <c s="11" r="E34">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F34">
         <is>
@@ -1351,19 +1351,19 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D35">
         <v>46234</v>
       </c>
       <c s="11" r="E35">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F35">
         <is>
@@ -1382,19 +1382,19 @@
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D36">
         <v>46234</v>
       </c>
       <c s="11" r="E36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
@@ -1413,19 +1413,19 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D37">
         <v>46234</v>
       </c>
       <c s="11" r="E37">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F37">
         <is>
@@ -1439,86 +1439,86 @@
     <row r="38" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A38">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D38">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E38">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G38">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D39">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E39">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G39">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D40">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E40">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
@@ -1526,49 +1526,49 @@
         </is>
       </c>
       <c s="12" r="G40">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D41">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E41">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F41">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G41">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
@@ -1577,18 +1577,18 @@
         </is>
       </c>
       <c s="10" r="D42">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E42">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G42">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="0">
@@ -1599,7 +1599,7 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
@@ -1625,24 +1625,24 @@
     <row r="44" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D44">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E44">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
@@ -1650,38 +1650,38 @@
         </is>
       </c>
       <c s="12" r="G44">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D45">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E45">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G45">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="0">
@@ -1692,19 +1692,19 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D46">
         <v>46131</v>
       </c>
       <c s="11" r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
@@ -1718,63 +1718,63 @@
     <row r="47" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D47">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E47">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G47">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D48">
         <v>46117</v>
       </c>
       <c s="11" r="E48">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G48">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="0">
@@ -1785,19 +1785,19 @@
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D49">
         <v>46117</v>
       </c>
       <c s="11" r="E49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F49">
         <is>
@@ -1816,12 +1816,12 @@
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D50">
@@ -1847,12 +1847,12 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D51">
@@ -1878,12 +1878,12 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D52">
@@ -1909,12 +1909,12 @@
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D53">
@@ -1940,12 +1940,12 @@
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D54">
@@ -1971,12 +1971,12 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D55">
@@ -2002,7 +2002,7 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
@@ -2033,7 +2033,7 @@
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
@@ -2064,12 +2064,12 @@
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D58">
@@ -2095,12 +2095,12 @@
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D59">
@@ -2126,12 +2126,12 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D60">
@@ -2157,7 +2157,7 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
@@ -2188,19 +2188,19 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D62">
         <v>46117</v>
       </c>
       <c s="11" r="E62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F62">
         <is>
@@ -2219,19 +2219,19 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D63">
         <v>46117</v>
       </c>
       <c s="11" r="E63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2250,19 +2250,19 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D64">
         <v>46117</v>
       </c>
       <c s="11" r="E64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F64">
         <is>
@@ -2281,12 +2281,12 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D65">
@@ -2312,12 +2312,12 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D66">
@@ -2338,24 +2338,24 @@
     <row r="67" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A67">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D67">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E67">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F67">
         <is>
@@ -2374,19 +2374,19 @@
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D68">
         <v>46112</v>
       </c>
       <c s="11" r="E68">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2405,19 +2405,19 @@
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D69">
         <v>46112</v>
       </c>
       <c s="11" r="E69">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
@@ -2431,24 +2431,24 @@
     <row r="70" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A70">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D70">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E70">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
@@ -2456,30 +2456,30 @@
         </is>
       </c>
       <c s="12" r="G70">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D71">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E71">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
@@ -2487,30 +2487,30 @@
         </is>
       </c>
       <c s="12" r="G71">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D72">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E72">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c s="12" r="G72">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="0">
@@ -2529,7 +2529,7 @@
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
@@ -2541,7 +2541,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E73">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
@@ -2560,19 +2560,19 @@
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D74">
         <v>46014</v>
       </c>
       <c s="11" r="E74">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
@@ -2586,43 +2586,43 @@
     <row r="75" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A75">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D75">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E75">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G75">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
@@ -2631,29 +2631,29 @@
         </is>
       </c>
       <c s="10" r="D76">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E76">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G76">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c s="10" r="D77">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E77">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2679,63 +2679,63 @@
     <row r="78" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D78">
         <v>46054</v>
       </c>
       <c s="11" r="E78">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G78">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D79">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E79">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G79">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="0">
@@ -2746,19 +2746,19 @@
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D80">
         <v>45916</v>
       </c>
       <c s="11" r="E80">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
@@ -2777,7 +2777,7 @@
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
@@ -2789,7 +2789,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E81">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
@@ -2820,7 +2820,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E82">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
@@ -2834,24 +2834,24 @@
     <row r="83" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A83">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D83">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E83">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c s="12" r="G83">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="0">
@@ -2870,23 +2870,23 @@
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D84">
         <v>46022</v>
       </c>
       <c s="11" r="E84">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G84">
@@ -2901,19 +2901,19 @@
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D85">
         <v>46022</v>
       </c>
       <c s="11" r="E85">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
@@ -2932,19 +2932,19 @@
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D86">
         <v>46022</v>
       </c>
       <c s="11" r="E86">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
@@ -2963,19 +2963,19 @@
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D87">
         <v>46022</v>
       </c>
       <c s="11" r="E87">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
@@ -2989,55 +2989,55 @@
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D88">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E88">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G88">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D89">
         <v>46017</v>
       </c>
       <c s="11" r="E89">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
@@ -3051,28 +3051,28 @@
     <row r="90" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D90">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E90">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G90">
@@ -3096,14 +3096,14 @@
         </is>
       </c>
       <c s="10" r="D91">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E91">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G91">
@@ -3113,86 +3113,86 @@
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D92">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E92">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G92">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D93">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E93">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G93">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D94">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E94">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
@@ -3200,18 +3200,18 @@
         </is>
       </c>
       <c s="12" r="G94">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E95">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
@@ -3231,38 +3231,38 @@
         </is>
       </c>
       <c s="12" r="G95">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E96">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
@@ -3282,14 +3282,14 @@
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E97">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G97">
@@ -3299,24 +3299,24 @@
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D98">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E98">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
@@ -3324,34 +3324,34 @@
         </is>
       </c>
       <c s="12" r="G98">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D99">
         <v>45976</v>
       </c>
       <c s="11" r="E99">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G99">
@@ -3361,63 +3361,63 @@
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D100">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E100">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G100">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D101">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E101">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G101">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="0">
@@ -3428,7 +3428,7 @@
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
@@ -3440,7 +3440,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E102">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
@@ -3454,12 +3454,12 @@
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
@@ -3468,41 +3468,41 @@
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E103">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E104">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
@@ -3510,18 +3510,18 @@
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
@@ -3530,49 +3530,49 @@
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E105">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E106">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
@@ -3583,19 +3583,19 @@
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D107">
         <v>45912</v>
       </c>
       <c s="11" r="E107">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
@@ -3609,63 +3609,63 @@
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D108">
         <v>45912</v>
       </c>
       <c s="11" r="E108">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G108">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D109">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E109">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G109">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="0">
@@ -3676,19 +3676,19 @@
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D110">
         <v>45853</v>
       </c>
       <c s="11" r="E110">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
@@ -3719,7 +3719,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E111">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
@@ -3750,7 +3750,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E112">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
@@ -3764,86 +3764,86 @@
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E113">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E114">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E115">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E116">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E117">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
@@ -3919,24 +3919,24 @@
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E118">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
@@ -3944,30 +3944,30 @@
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D119">
         <v>45838</v>
       </c>
       <c s="11" r="E119">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
@@ -3981,94 +3981,94 @@
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D120">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E120">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D121">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E121">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G121">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E122">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G122">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="0">
@@ -4079,19 +4079,19 @@
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D123">
         <v>45866</v>
       </c>
       <c s="11" r="E123">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
@@ -4105,55 +4105,55 @@
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E124">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E125">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
@@ -4161,85 +4161,85 @@
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E126">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E127">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D128">
@@ -4250,69 +4250,69 @@
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G128">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D129">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E129">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G129">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E130">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G130">
@@ -4322,43 +4322,43 @@
     <row r="131" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E131">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G131">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
@@ -4367,103 +4367,103 @@
         </is>
       </c>
       <c s="10" r="D132">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E132">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G132">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E133">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G133">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E134">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G134">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E135">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
@@ -4471,38 +4471,38 @@
         </is>
       </c>
       <c s="12" r="G135">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E136">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G136">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="0">
@@ -4513,19 +4513,19 @@
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D137">
         <v>45707</v>
       </c>
       <c s="11" r="E137">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
@@ -4539,63 +4539,63 @@
     <row r="138" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E138">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G138">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E139">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G139">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="0">
@@ -4606,19 +4606,19 @@
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D140">
         <v>45696</v>
       </c>
       <c s="11" r="E140">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
@@ -4632,86 +4632,86 @@
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E141">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E142">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D143">
         <v>45931</v>
       </c>
       <c s="11" r="E143">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
@@ -4725,43 +4725,43 @@
     <row r="144" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E144">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G144">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
@@ -4770,18 +4770,18 @@
         </is>
       </c>
       <c s="10" r="D145">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E145">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G145">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="0">
@@ -4792,19 +4792,19 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D146">
         <v>45726</v>
       </c>
       <c s="11" r="E146">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4823,19 +4823,19 @@
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E147">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
@@ -4854,19 +4854,19 @@
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D148">
         <v>45725</v>
       </c>
       <c s="11" r="E148">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
@@ -4885,19 +4885,19 @@
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D149">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E149">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
@@ -4916,12 +4916,12 @@
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D150">
@@ -4947,12 +4947,12 @@
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D151">
@@ -4978,7 +4978,7 @@
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E152">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
@@ -5009,19 +5009,19 @@
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E153">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E154">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
@@ -5071,19 +5071,19 @@
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E155">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
@@ -5097,12 +5097,12 @@
     <row r="156" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A156">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
@@ -5111,72 +5111,72 @@
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E156">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G156">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="157" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E157">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G157">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E158">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
@@ -5184,100 +5184,100 @@
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E159">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G159">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D160">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E160">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G160">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D161">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E161">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G161">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="0">
@@ -5288,19 +5288,19 @@
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D162">
         <v>45611</v>
       </c>
       <c s="11" r="E162">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c s="9" t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C163">
@@ -5331,7 +5331,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E163">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5350,7 +5350,7 @@
       </c>
       <c s="9" t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C164">
@@ -5362,7 +5362,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E164">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5376,28 +5376,28 @@
     <row r="165" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C165">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E165">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G165">
@@ -5407,24 +5407,24 @@
     <row r="166" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E166">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
@@ -5432,38 +5432,38 @@
         </is>
       </c>
       <c s="12" r="G166">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E167">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G167">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="0">
@@ -5474,23 +5474,23 @@
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D168">
         <v>45544</v>
       </c>
       <c s="11" r="E168">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G168">
@@ -5500,55 +5500,55 @@
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E169">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E170">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E171">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
@@ -5607,14 +5607,14 @@
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E172">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G172">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
@@ -5669,14 +5669,14 @@
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E174">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G174">
@@ -5686,24 +5686,24 @@
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E175">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c s="12" r="G175">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="0">
@@ -5731,14 +5731,14 @@
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E176">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G176">
@@ -5748,24 +5748,24 @@
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E177">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E178">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
@@ -5804,18 +5804,18 @@
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E179">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5835,30 +5835,30 @@
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D180">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E180">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c s="12" r="G180">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="0">
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E181">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E182">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
@@ -5934,32 +5934,32 @@
     <row r="183" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A183">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B183">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C183">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E183">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G183">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="184" ht="18" customHeight="0">
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E184">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
@@ -6027,43 +6027,43 @@
     <row r="186" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E186">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G186">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E187">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
@@ -6083,111 +6083,111 @@
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D188">
         <v>45471</v>
       </c>
       <c s="11" r="E188">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E189">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E190">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
@@ -6196,134 +6196,134 @@
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E191">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G191">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D192">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E192">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G192">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D193">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E193">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G193">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E194">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G194">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E195">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6331,18 +6331,18 @@
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
@@ -6351,41 +6351,41 @@
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E196">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E197">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c s="12" r="G197">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="0">
@@ -6404,7 +6404,7 @@
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
@@ -6416,7 +6416,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E198">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
@@ -6430,24 +6430,24 @@
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E199">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c s="12" r="G199">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D200">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E200">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G200">
@@ -6497,19 +6497,19 @@
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D201">
         <v>45382</v>
       </c>
       <c s="11" r="E201">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
@@ -6528,19 +6528,19 @@
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D202">
         <v>45382</v>
       </c>
       <c s="11" r="E202">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
@@ -6559,7 +6559,7 @@
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
@@ -6571,7 +6571,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
@@ -6590,12 +6590,12 @@
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D204">
@@ -6616,32 +6616,32 @@
     <row r="205" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E205">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G205">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="0">
@@ -6652,23 +6652,23 @@
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D206">
         <v>45366</v>
       </c>
       <c s="11" r="E206">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G206">
@@ -6678,55 +6678,55 @@
     <row r="207" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E207">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G207">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D208">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E208">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c s="12" r="G208">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="0">
@@ -6745,19 +6745,19 @@
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D209">
         <v>45275</v>
       </c>
       <c s="11" r="E209">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6776,19 +6776,19 @@
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D210">
         <v>45275</v>
       </c>
       <c s="11" r="E210">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6807,19 +6807,19 @@
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D211">
         <v>45275</v>
       </c>
       <c s="11" r="E211">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6833,24 +6833,24 @@
     <row r="212" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A212">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D212">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E212">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6858,30 +6858,30 @@
         </is>
       </c>
       <c s="12" r="G212">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E213">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
@@ -6889,30 +6889,30 @@
         </is>
       </c>
       <c s="12" r="G213">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E214">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c s="12" r="G214">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="0">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E215">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E216">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
@@ -6988,24 +6988,24 @@
     <row r="217" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E217">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c s="12" r="G217">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
@@ -7036,7 +7036,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E218">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7050,12 +7050,12 @@
     <row r="219" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
@@ -7067,7 +7067,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E219">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7081,24 +7081,24 @@
     <row r="220" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D220">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E220">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7106,61 +7106,61 @@
         </is>
       </c>
       <c s="12" r="G220">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="221" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E221">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G221">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E222">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c s="12" r="G222">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="0">
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E223">
         <v>2</v>
@@ -7219,14 +7219,14 @@
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E224">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G224">
@@ -7241,7 +7241,7 @@
       </c>
       <c s="9" t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C225">
@@ -7253,11 +7253,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E225">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G225">
@@ -7272,7 +7272,7 @@
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E226">
         <v>3</v>
@@ -7303,7 +7303,7 @@
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
@@ -7315,7 +7315,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c s="9" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C228">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E229">
         <v>1</v>
@@ -7396,7 +7396,7 @@
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
@@ -7405,14 +7405,14 @@
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E230">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G230">
@@ -7427,7 +7427,7 @@
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
@@ -7439,7 +7439,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E231">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
@@ -7453,86 +7453,86 @@
     <row r="232" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E232">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G232">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E233">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G233">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D234">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E234">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
@@ -7546,24 +7546,24 @@
     <row r="235" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D235">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E235">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F235">
         <is>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c s="12" r="G235">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="0">
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E236">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
@@ -7608,24 +7608,24 @@
     <row r="237" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E237">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c s="12" r="G237">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="0">
@@ -7644,19 +7644,19 @@
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E238">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
@@ -7670,32 +7670,32 @@
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E239">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G239">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="0">
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E240">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7732,24 +7732,24 @@
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E241">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
@@ -7757,30 +7757,30 @@
         </is>
       </c>
       <c s="12" r="G241">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E242">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
@@ -7788,123 +7788,123 @@
         </is>
       </c>
       <c s="12" r="G242">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E243">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G243">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E244">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G244">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E245">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G245">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E246">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
@@ -7912,30 +7912,30 @@
         </is>
       </c>
       <c s="12" r="G246">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E247">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
@@ -7943,61 +7943,61 @@
         </is>
       </c>
       <c s="12" r="G247">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E248">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G248">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E249">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
@@ -8005,30 +8005,30 @@
         </is>
       </c>
       <c s="12" r="G249">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D250">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E250">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c s="12" r="G250">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="0">
@@ -8047,12 +8047,12 @@
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D251">
@@ -8078,12 +8078,12 @@
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D252">
@@ -8109,12 +8109,12 @@
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D253">
@@ -8140,12 +8140,12 @@
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D254">
@@ -8166,86 +8166,86 @@
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E255">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G255">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E256">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G256">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E257">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8259,24 +8259,24 @@
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D258">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E258">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
@@ -8284,30 +8284,30 @@
         </is>
       </c>
       <c s="12" r="G258">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D259">
         <v>45079</v>
       </c>
       <c s="11" r="E259">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8321,12 +8321,12 @@
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
@@ -8335,103 +8335,103 @@
         </is>
       </c>
       <c s="10" r="D260">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E260">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E261">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E262">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G262">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C263">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E263">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
@@ -8439,30 +8439,30 @@
         </is>
       </c>
       <c s="12" r="G263">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E264">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
@@ -8470,80 +8470,80 @@
         </is>
       </c>
       <c s="12" r="G264">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E265">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G265">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E266">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
@@ -8552,41 +8552,41 @@
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E267">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E268">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,30 +8594,30 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E269">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8625,30 +8625,30 @@
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E270">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E271">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
@@ -8693,74 +8693,74 @@
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E272">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E273">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E274">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8780,30 +8780,30 @@
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E275">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
@@ -8834,7 +8834,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E276">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
@@ -8848,24 +8848,24 @@
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E277">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8873,30 +8873,30 @@
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E278">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8904,30 +8904,30 @@
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C279">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E279">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c s="12" r="G279">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="0">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E280">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E281">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E282">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E283">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E284">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9096,12 +9096,12 @@
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E285">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9121,30 +9121,30 @@
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E286">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9152,30 +9152,30 @@
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E287">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
@@ -9194,7 +9194,7 @@
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
@@ -9206,7 +9206,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E288">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
@@ -9225,19 +9225,19 @@
       </c>
       <c s="9" t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C289">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D289">
         <v>44469</v>
       </c>
       <c s="11" r="E289">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9251,24 +9251,24 @@
     <row r="290" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A290">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C290">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E290">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9276,30 +9276,30 @@
         </is>
       </c>
       <c s="12" r="G290">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E291">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
@@ -9307,18 +9307,18 @@
         </is>
       </c>
       <c s="12" r="G291">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
@@ -9327,10 +9327,10 @@
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E292">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
@@ -9338,18 +9338,18 @@
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C293">
@@ -9358,49 +9358,49 @@
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E293">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G293">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E294">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E295">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
@@ -9437,32 +9437,32 @@
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E296">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c s="10" r="D297">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E297">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c s="10" r="D298">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E298">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c s="10" r="D299">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E299">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
@@ -9561,12 +9561,12 @@
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
@@ -9578,7 +9578,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E300">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
@@ -9592,24 +9592,24 @@
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E301">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c s="12" r="G301">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="0">
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E302">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
@@ -9654,24 +9654,24 @@
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E303">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
@@ -9679,100 +9679,100 @@
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E304">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E305">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D306">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E306">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G306">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
@@ -9795,11 +9795,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E307">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G307">
@@ -9809,12 +9809,12 @@
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
@@ -9823,29 +9823,29 @@
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E308">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G308">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
@@ -9854,69 +9854,69 @@
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E309">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G309">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E310">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G310">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E311">
         <v>59</v>
@@ -9927,159 +9927,189 @@
         </is>
       </c>
       <c s="12" r="G311">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D312">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E312">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D313"/>
-      <c s="13" t="str" r="E313"/>
+          <t xml:space="preserve">Elgin</t>
+        </is>
+      </c>
+      <c s="10" r="D313">
+        <v>44197</v>
+      </c>
+      <c s="11" r="E313">
+        <v>229</v>
+      </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44909</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D314"/>
       <c s="13" t="str" r="E314"/>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G314">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D315"/>
       <c s="13" t="str" r="E315"/>
       <c s="9" t="inlineStr" r="F315">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G315">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="316" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A316">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B316">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C316">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D316"/>
+      <c s="13" t="str" r="E316"/>
+      <c s="9" t="inlineStr" r="F316">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G315">
+      <c s="12" r="G316">
         <v>45887</v>
       </c>
     </row>
-    <row r="316" ht="3.55" customHeight="0">
-      <c s="14" t="inlineStr" r="A316">
+    <row r="317" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A317">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B316">
+      <c s="14" t="inlineStr" r="B317">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C316">
+      <c s="14" t="inlineStr" r="C317">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D316">
+      <c s="14" t="inlineStr" r="D317">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E316">
+      <c s="14" t="inlineStr" r="E317">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F316">
+      <c s="14" t="inlineStr" r="F317">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G316">
+      <c s="14" t="inlineStr" r="G317">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="317" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10089,7 +10119,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/6/2026 10:58:06 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/6/2026 8:34:55 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/6/2016 to 10/6/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/7/2016 to 10/7/2026</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10119,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/6/2026 8:34:55 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/7/2026 11:28:45 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46446</v>
+        <v>46444</v>
       </c>
       <c s="11" r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c s="10" r="D16">
-        <v>46387</v>
+        <v>46416</v>
       </c>
       <c s="11" r="E16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c s="10" r="D17">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E17">
         <v>4</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c s="10" r="D18">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c s="10" r="D19">
-        <v>46295</v>
+        <v>46332</v>
       </c>
       <c s="11" r="E19">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
@@ -881,24 +881,24 @@
     <row r="20" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">9553</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D20">
-        <v>46298</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E20">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
@@ -906,61 +906,61 @@
         </is>
       </c>
       <c s="12" r="G20">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D21">
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E21">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G21">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46325</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E22">
-        <v>387</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
@@ -968,30 +968,30 @@
         </is>
       </c>
       <c s="12" r="G22">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E23">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
@@ -999,69 +999,69 @@
         </is>
       </c>
       <c s="12" r="G23">
-        <v>46199</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A24">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D24">
-        <v>46206</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E24">
-        <v>4</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G24">
-        <v>46197</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A25">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B25">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D25">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E25">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G25">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="0">
@@ -1072,19 +1072,19 @@
       </c>
       <c s="9" t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D26">
         <v>46206</v>
       </c>
       <c s="11" r="E26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
@@ -1098,55 +1098,55 @@
     <row r="27" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A27">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D27">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E27">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G27">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D28">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E28">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c s="12" r="G28">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="0">
@@ -1165,23 +1165,23 @@
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D29">
         <v>46234</v>
       </c>
       <c s="11" r="E29">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G29">
@@ -1196,19 +1196,19 @@
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D30">
         <v>46234</v>
       </c>
       <c s="11" r="E30">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
@@ -1227,19 +1227,19 @@
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D31">
         <v>46234</v>
       </c>
       <c s="11" r="E31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
@@ -1253,94 +1253,94 @@
     <row r="32" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D32">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E32">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G32">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D33">
-        <v>46333</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E33">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G33">
-        <v>46160</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A34">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D34">
-        <v>46234</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E34">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G34">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="0">
@@ -1351,23 +1351,23 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D35">
-        <v>46234</v>
+        <v>46333</v>
       </c>
       <c s="11" r="E35">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F35">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G35">
@@ -1382,19 +1382,19 @@
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D36">
         <v>46234</v>
       </c>
       <c s="11" r="E36">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
@@ -1413,12 +1413,12 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D37">
@@ -1444,19 +1444,19 @@
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D38">
         <v>46234</v>
       </c>
       <c s="11" r="E38">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F38">
         <is>
@@ -1470,55 +1470,55 @@
     <row r="39" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A39">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D39">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E39">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G39">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D40">
-        <v>46201</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E40">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
@@ -1526,92 +1526,92 @@
         </is>
       </c>
       <c s="12" r="G40">
-        <v>46141</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D41">
-        <v>46295</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E41">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F41">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G41">
-        <v>46114</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D42">
-        <v>46203</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E42">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G42">
-        <v>46108</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A43">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D43">
-        <v>46178</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E43">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F43">
         <is>
@@ -1619,18 +1619,18 @@
         </is>
       </c>
       <c s="12" r="G43">
-        <v>46118</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A44">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
@@ -1639,41 +1639,41 @@
         </is>
       </c>
       <c s="10" r="D44">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E44">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G44">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A45">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D45">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E45">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
@@ -1681,162 +1681,162 @@
         </is>
       </c>
       <c s="12" r="G45">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A46">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D46">
-        <v>46131</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E46">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G46">
-        <v>46066</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D47">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E47">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G47">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D48">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E48">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G48">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D49">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F49">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G49">
-        <v>46051</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D50">
         <v>46117</v>
       </c>
       <c s="11" r="E50">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F50">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G50">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="0">
@@ -1847,19 +1847,19 @@
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D51">
         <v>46117</v>
       </c>
       <c s="11" r="E51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F51">
         <is>
@@ -1878,7 +1878,7 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
@@ -1909,12 +1909,12 @@
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D53">
@@ -1940,12 +1940,12 @@
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D54">
@@ -1971,12 +1971,12 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D55">
@@ -2002,12 +2002,12 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D56">
@@ -2033,12 +2033,12 @@
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D57">
@@ -2064,7 +2064,7 @@
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
@@ -2095,12 +2095,12 @@
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D59">
@@ -2126,12 +2126,12 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D60">
@@ -2157,12 +2157,12 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D61">
@@ -2188,12 +2188,12 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D62">
@@ -2219,19 +2219,19 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D63">
         <v>46117</v>
       </c>
       <c s="11" r="E63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F63">
         <is>
@@ -2250,7 +2250,7 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
@@ -2281,12 +2281,12 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D65">
@@ -2312,19 +2312,19 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D66">
         <v>46117</v>
       </c>
       <c s="11" r="E66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F66">
         <is>
@@ -2343,12 +2343,12 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D67">
@@ -2369,24 +2369,24 @@
     <row r="68" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A68">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D68">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E68">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F68">
         <is>
@@ -2400,24 +2400,24 @@
     <row r="69" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A69">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D69">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E69">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F69">
         <is>
@@ -2436,19 +2436,19 @@
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D70">
         <v>46112</v>
       </c>
       <c s="11" r="E70">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F70">
         <is>
@@ -2462,24 +2462,24 @@
     <row r="71" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A71">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D71">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E71">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
@@ -2487,30 +2487,30 @@
         </is>
       </c>
       <c s="12" r="G71">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A72">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D72">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E72">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2518,30 +2518,30 @@
         </is>
       </c>
       <c s="12" r="G72">
-        <v>46020</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A73">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D73">
-        <v>46014</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E73">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
@@ -2549,30 +2549,30 @@
         </is>
       </c>
       <c s="12" r="G73">
-        <v>46014</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A74">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D74">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E74">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c s="12" r="G74">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="0">
@@ -2591,19 +2591,19 @@
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D75">
         <v>46014</v>
       </c>
       <c s="11" r="E75">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F75">
         <is>
@@ -2617,55 +2617,55 @@
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D76">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E76">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G76">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D77">
-        <v>46053</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E77">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2673,18 +2673,18 @@
         </is>
       </c>
       <c s="12" r="G77">
-        <v>45992</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A78">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
@@ -2693,111 +2693,111 @@
         </is>
       </c>
       <c s="10" r="D78">
-        <v>46054</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E78">
-        <v>310</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G78">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D79">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E79">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G79">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D80">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E80">
-        <v>41</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G80">
-        <v>45974</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D81">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E81">
-        <v>510</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G81">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="0">
@@ -2808,19 +2808,19 @@
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D82">
         <v>45916</v>
       </c>
       <c s="11" r="E82">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
@@ -2839,7 +2839,7 @@
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
@@ -2851,7 +2851,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E83">
-        <v>76</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
@@ -2865,24 +2865,24 @@
     <row r="84" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D84">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E84">
-        <v>153</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
@@ -2890,38 +2890,38 @@
         </is>
       </c>
       <c s="12" r="G84">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D85">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E85">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G85">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="0">
@@ -2932,23 +2932,23 @@
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D86">
         <v>46022</v>
       </c>
       <c s="11" r="E86">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G86">
@@ -2963,19 +2963,19 @@
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D87">
         <v>46022</v>
       </c>
       <c s="11" r="E87">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
@@ -2994,19 +2994,19 @@
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D88">
         <v>46022</v>
       </c>
       <c s="11" r="E88">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
@@ -3020,12 +3020,12 @@
     <row r="89" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
@@ -3034,29 +3034,29 @@
         </is>
       </c>
       <c s="10" r="D89">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E89">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G89">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A90">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
@@ -3065,45 +3065,45 @@
         </is>
       </c>
       <c s="10" r="D90">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E90">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G90">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A91">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D91">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E91">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G91">
@@ -3113,28 +3113,28 @@
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D92">
         <v>46017</v>
       </c>
       <c s="11" r="E92">
-        <v>263</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G92">
@@ -3144,117 +3144,117 @@
     <row r="93" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D93">
-        <v>45993</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G93">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A94">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D94">
-        <v>46022</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E94">
-        <v>56</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G94">
-        <v>45917</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A95">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D95">
-        <v>45978</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E95">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G95">
-        <v>45943</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A96">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D96">
-        <v>45989</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E96">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
@@ -3262,61 +3262,61 @@
         </is>
       </c>
       <c s="12" r="G96">
-        <v>45930</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D97">
-        <v>45940</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E97">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G97">
-        <v>45925</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D98">
-        <v>45925</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E98">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
@@ -3324,92 +3324,92 @@
         </is>
       </c>
       <c s="12" r="G98">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D99">
-        <v>45976</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E99">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G99">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D100">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E100">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G100">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D101">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E101">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
@@ -3417,18 +3417,18 @@
         </is>
       </c>
       <c s="12" r="G101">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
@@ -3437,60 +3437,60 @@
         </is>
       </c>
       <c s="10" r="D102">
-        <v>45949</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E102">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G102">
-        <v>45889</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E103">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
@@ -3499,196 +3499,196 @@
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E104">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45874</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E105">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45867</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45920</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E106">
-        <v>249</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45854</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45912</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E107">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45849</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E108">
-        <v>32</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G108">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D109">
         <v>45912</v>
       </c>
       <c s="11" r="E109">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G109">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D110">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E110">
-        <v>194</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
@@ -3696,38 +3696,38 @@
         </is>
       </c>
       <c s="12" r="G110">
-        <v>45845</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D111">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E111">
-        <v>1544</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G111">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="0">
@@ -3738,19 +3738,19 @@
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D112">
         <v>45853</v>
       </c>
       <c s="11" r="E112">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
@@ -3769,7 +3769,7 @@
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
@@ -3781,7 +3781,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E113">
-        <v>597</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
@@ -3795,117 +3795,117 @@
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E114">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45901</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E115">
-        <v>62</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45839</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45982</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E116">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45832</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D117">
-        <v>45968</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E117">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45894</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E118">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
@@ -3950,24 +3950,24 @@
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D119">
-        <v>45838</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E119">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
@@ -3975,30 +3975,30 @@
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A120">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D120">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E120">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
@@ -4006,61 +4006,61 @@
         </is>
       </c>
       <c s="12" r="G120">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A121">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D121">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E121">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G121">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45807</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E122">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
@@ -4068,30 +4068,30 @@
         </is>
       </c>
       <c s="12" r="G122">
-        <v>45804</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45866</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E123">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
@@ -4099,185 +4099,185 @@
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45806</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E124">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E125">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A126">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B126">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C126">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45838</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E126">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G126">
-        <v>45778</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45769</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E127">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45769</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D128">
         <v>45838</v>
       </c>
       <c s="11" r="E128">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G128">
-        <v>45768</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D129">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E129">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
@@ -4285,61 +4285,61 @@
         </is>
       </c>
       <c s="12" r="G129">
-        <v>45763</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E130">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G130">
-        <v>45742</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45810</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E131">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
@@ -4347,30 +4347,30 @@
         </is>
       </c>
       <c s="12" r="G131">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D132">
-        <v>45808</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E132">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
@@ -4378,30 +4378,30 @@
         </is>
       </c>
       <c s="12" r="G132">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45834</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E133">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
@@ -4409,49 +4409,49 @@
         </is>
       </c>
       <c s="12" r="G133">
-        <v>45774</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E134">
-        <v>244</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G134">
-        <v>45744</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
@@ -4460,165 +4460,165 @@
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45706</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E135">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G135">
-        <v>45706</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45734</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E136">
-        <v>56</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G136">
-        <v>45666</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45707</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E137">
-        <v>429</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G137">
-        <v>45646</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E138">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G138">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E139">
-        <v>87</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G139">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45696</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E140">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
@@ -4626,111 +4626,111 @@
         </is>
       </c>
       <c s="12" r="G140">
-        <v>45636</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E141">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E142">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45931</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E143">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G143">
-        <v>45629</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
@@ -4739,72 +4739,72 @@
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E144">
-        <v>221</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G144">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D145">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E145">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G145">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D146">
-        <v>45726</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E146">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4812,38 +4812,38 @@
         </is>
       </c>
       <c s="12" r="G146">
-        <v>45610</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E147">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G147">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="0">
@@ -4854,19 +4854,19 @@
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E148">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
@@ -4885,19 +4885,19 @@
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D149">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E149">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
@@ -4916,19 +4916,19 @@
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D150">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E150">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
@@ -4947,19 +4947,19 @@
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E151">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
@@ -4978,12 +4978,12 @@
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D152">
@@ -5009,19 +5009,19 @@
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E153">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5040,16 +5040,16 @@
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45714</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E154">
         <v>9</v>
@@ -5071,19 +5071,19 @@
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45703</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E155">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
@@ -5102,19 +5102,19 @@
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45690</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E156">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
@@ -5128,55 +5128,55 @@
     <row r="157" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A157">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45657</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E157">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G157">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="158" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A158">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45640</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E158">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
@@ -5184,92 +5184,92 @@
         </is>
       </c>
       <c s="12" r="G158">
-        <v>45580</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="159" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A159">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D159">
         <v>45657</v>
       </c>
       <c s="11" r="E159">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G159">
-        <v>45595</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="160" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A160">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D160">
-        <v>45584</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E160">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F160">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G160">
-        <v>45584</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="161" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A161">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D161">
-        <v>45664</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E161">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5277,30 +5277,30 @@
         </is>
       </c>
       <c s="12" r="G161">
-        <v>45582</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="162" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A162">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D162">
-        <v>45611</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E162">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5308,38 +5308,38 @@
         </is>
       </c>
       <c s="12" r="G162">
-        <v>45580</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="163" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A163">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C163">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E163">
-        <v>514</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G163">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="164" ht="18" customHeight="0">
@@ -5350,19 +5350,19 @@
       </c>
       <c s="9" t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C164">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D164">
         <v>45611</v>
       </c>
       <c s="11" r="E164">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c s="9" t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C165">
@@ -5393,7 +5393,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E165">
-        <v>634</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
@@ -5407,28 +5407,28 @@
     <row r="166" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E166">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G166">
@@ -5438,12 +5438,12 @@
     <row r="167" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
@@ -5452,103 +5452,103 @@
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45621</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E167">
-        <v>150</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G167">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45544</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E168">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45541</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E169">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E170">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
@@ -5556,61 +5556,61 @@
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45654</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E171">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G171">
-        <v>45496</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A172">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C172">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D172">
-        <v>45612</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E172">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c s="12" r="G172">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="173" ht="18" customHeight="0">
@@ -5638,14 +5638,14 @@
         </is>
       </c>
       <c s="10" r="D173">
-        <v>45584</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E173">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G173">
@@ -5669,14 +5669,14 @@
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45569</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E174">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G174">
@@ -5700,14 +5700,14 @@
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45555</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E175">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G175">
@@ -5717,117 +5717,117 @@
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C176">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45653</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E176">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45505</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E177">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45534</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E178">
-        <v>297</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45513</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E179">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5835,18 +5835,18 @@
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45450</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45504</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E180">
-        <v>37</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5866,30 +5866,30 @@
         </is>
       </c>
       <c s="12" r="G180">
-        <v>45441</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A181">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B181">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C181">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D181">
-        <v>46229</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E181">
-        <v>200</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
@@ -5897,30 +5897,30 @@
         </is>
       </c>
       <c s="12" r="G181">
-        <v>45440</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="182" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A182">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B182">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C182">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45688</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E182">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c s="12" r="G182">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="183" ht="18" customHeight="0">
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45506</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E183">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
@@ -5965,63 +5965,63 @@
     <row r="184" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45483</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E184">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G184">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45401</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E185">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G185">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="0">
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45366</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E186">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
@@ -6058,117 +6058,117 @@
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45473</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E187">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45471</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E188">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45404</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E189">
-        <v>740</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45401</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E190">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
@@ -6176,61 +6176,61 @@
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45384</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A191">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B191">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C191">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45443</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E191">
-        <v>171</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G191">
-        <v>45380</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="192" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D192">
-        <v>45439</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E192">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
@@ -6238,92 +6238,92 @@
         </is>
       </c>
       <c s="12" r="G192">
-        <v>45379</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D193">
-        <v>45436</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E193">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G193">
-        <v>45372</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A194">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B194">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C194">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45433</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E194">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G194">
-        <v>45373</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45417</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E195">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6331,123 +6331,123 @@
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45358</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45352</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E196">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45345</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45401</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E197">
-        <v>350</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G197">
-        <v>45335</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45337</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E198">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G198">
-        <v>45337</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E199">
-        <v>58</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
@@ -6455,30 +6455,30 @@
         </is>
       </c>
       <c s="12" r="G199">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D200">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E200">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
@@ -6486,65 +6486,65 @@
         </is>
       </c>
       <c s="12" r="G200">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D201">
-        <v>45382</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E201">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G201">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D202">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E202">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G202">
@@ -6559,19 +6559,19 @@
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D203">
         <v>45382</v>
       </c>
       <c s="11" r="E203">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
@@ -6590,19 +6590,19 @@
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D204">
         <v>45382</v>
       </c>
       <c s="11" r="E204">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
@@ -6621,19 +6621,19 @@
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D205">
         <v>45382</v>
       </c>
       <c s="11" r="E205">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
@@ -6647,148 +6647,148 @@
     <row r="206" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E206">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G206">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E207">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G207">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D208">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E208">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G208">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D209">
-        <v>45275</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E209">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G209">
-        <v>45224</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D210">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E210">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6796,7 +6796,7 @@
         </is>
       </c>
       <c s="12" r="G210">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="211" ht="18" customHeight="0">
@@ -6807,19 +6807,19 @@
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D211">
         <v>45275</v>
       </c>
       <c s="11" r="E211">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6838,19 +6838,19 @@
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D212">
         <v>45275</v>
       </c>
       <c s="11" r="E212">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6864,24 +6864,24 @@
     <row r="213" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A213">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D213">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E213">
-        <v>463</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
@@ -6889,30 +6889,30 @@
         </is>
       </c>
       <c s="12" r="G213">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="214" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45294</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E214">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
@@ -6920,30 +6920,30 @@
         </is>
       </c>
       <c s="12" r="G214">
-        <v>45217</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45473</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E215">
-        <v>23</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
@@ -6951,30 +6951,30 @@
         </is>
       </c>
       <c s="12" r="G215">
-        <v>45200</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45382</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E216">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c s="12" r="G216">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="0">
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45291</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E217">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7019,24 +7019,24 @@
     <row r="218" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D218">
-        <v>45290</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E218">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7044,30 +7044,30 @@
         </is>
       </c>
       <c s="12" r="G218">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A219">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D219">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E219">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7075,18 +7075,18 @@
         </is>
       </c>
       <c s="12" r="G219">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="220" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A220">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
@@ -7098,7 +7098,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E220">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7112,24 +7112,24 @@
     <row r="221" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E221">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
@@ -7137,92 +7137,92 @@
         </is>
       </c>
       <c s="12" r="G221">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45237</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E222">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G222">
-        <v>45176</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45387</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E223">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G223">
-        <v>45160</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45317</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E224">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c s="12" r="G224">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="0">
@@ -7250,14 +7250,14 @@
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45303</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E225">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G225">
@@ -7272,7 +7272,7 @@
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7312,14 +7312,14 @@
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E227">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G227">
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c s="10" r="D228">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E228">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E229">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7396,7 +7396,7 @@
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45247</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
@@ -7427,7 +7427,7 @@
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
@@ -7436,14 +7436,14 @@
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45219</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E231">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G231">
@@ -7467,14 +7467,14 @@
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E232">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G232">
@@ -7484,117 +7484,117 @@
     <row r="233" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A233">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E233">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G233">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="234" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A234">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D234">
-        <v>45199</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E234">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G234">
-        <v>45148</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="235" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A235">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D235">
         <v>45213</v>
       </c>
       <c s="11" r="E235">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F235">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G235">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="236" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A236">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45283</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E236">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
@@ -7602,30 +7602,30 @@
         </is>
       </c>
       <c s="12" r="G236">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="237" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A237">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45192</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E237">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
@@ -7633,30 +7633,30 @@
         </is>
       </c>
       <c s="12" r="G237">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="238" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A238">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45137</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E238">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
@@ -7664,30 +7664,30 @@
         </is>
       </c>
       <c s="12" r="G238">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="239" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A239">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45107</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E239">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
@@ -7695,92 +7695,92 @@
         </is>
       </c>
       <c s="12" r="G239">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="240" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A240">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45233</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E240">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G240">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45205</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E241">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G241">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45175</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E242">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
@@ -7788,30 +7788,30 @@
         </is>
       </c>
       <c s="12" r="G242">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>45091</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E243">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
@@ -7819,154 +7819,154 @@
         </is>
       </c>
       <c s="12" r="G243">
-        <v>45091</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>45128</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E244">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G244">
-        <v>45090</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>45170</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E245">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G245">
-        <v>45085</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>45106</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E246">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G246">
-        <v>45083</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45107</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E247">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G247">
-        <v>45070</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45115</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E248">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
@@ -7974,92 +7974,92 @@
         </is>
       </c>
       <c s="12" r="G248">
-        <v>45055</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>45105</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E249">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G249">
-        <v>45044</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D250">
-        <v>45135</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E250">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G250">
-        <v>45041</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D251">
-        <v>45124</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E251">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
@@ -8067,30 +8067,30 @@
         </is>
       </c>
       <c s="12" r="G251">
-        <v>45030</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D252">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E252">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c s="12" r="G252">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="0">
@@ -8109,12 +8109,12 @@
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D253">
@@ -8140,12 +8140,12 @@
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D254">
@@ -8171,12 +8171,12 @@
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D255">
@@ -8197,55 +8197,55 @@
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E256">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G256">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>45077</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E257">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8253,61 +8253,61 @@
         </is>
       </c>
       <c s="12" r="G257">
-        <v>44998</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D258">
-        <v>45058</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E258">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G258">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D259">
-        <v>45079</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E259">
-        <v>379</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8315,18 +8315,18 @@
         </is>
       </c>
       <c s="12" r="G259">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c s="10" r="D260">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E260">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
@@ -8346,92 +8346,92 @@
         </is>
       </c>
       <c s="12" r="G260">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A261">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D261">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E261">
-        <v>101</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F261">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G261">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="262" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A262">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D262">
-        <v>44939</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E262">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F262">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G262">
-        <v>44937</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="263" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A263">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C263">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D263">
-        <v>44890</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E263">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F263">
         <is>
@@ -8439,61 +8439,61 @@
         </is>
       </c>
       <c s="12" r="G263">
-        <v>44827</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="264" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D264">
-        <v>44907</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E264">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G264">
-        <v>44846</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D265">
-        <v>44911</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E265">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
@@ -8501,61 +8501,61 @@
         </is>
       </c>
       <c s="12" r="G265">
-        <v>44845</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D266">
-        <v>44869</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E266">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44812</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D267">
-        <v>44866</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E267">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8563,30 +8563,30 @@
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44803</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>44856</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E268">
-        <v>225</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,61 +8594,61 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44795</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D269">
-        <v>44815</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E269">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44755</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44802</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E270">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
@@ -8656,30 +8656,30 @@
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44741</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44865</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E271">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
@@ -8687,30 +8687,30 @@
         </is>
       </c>
       <c s="12" r="G271">
-        <v>44699</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44805</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E272">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44712</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E273">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44600</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E274">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8780,61 +8780,61 @@
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44600</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44652</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E275">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44578</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44620</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E276">
-        <v>226</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
@@ -8842,30 +8842,30 @@
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44568</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E277">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8873,30 +8873,30 @@
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E278">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8904,30 +8904,30 @@
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C279">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44531</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E279">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8935,30 +8935,30 @@
         </is>
       </c>
       <c s="12" r="G279">
-        <v>44470</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C280">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44799</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E280">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8966,30 +8966,30 @@
         </is>
       </c>
       <c s="12" r="G280">
-        <v>44449</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C281">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44743</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E281">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c s="12" r="G281">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="0">
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44680</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E282">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44652</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E283">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44575</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E284">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44512</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E285">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9127,12 +9127,12 @@
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
@@ -9141,10 +9141,10 @@
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44469</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E286">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9152,30 +9152,30 @@
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44482</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E287">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
@@ -9183,18 +9183,18 @@
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44421</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
@@ -9206,7 +9206,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E288">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
@@ -9214,30 +9214,30 @@
         </is>
       </c>
       <c s="12" r="G288">
-        <v>44407</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C289">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E289">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c s="12" r="G289">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="0">
@@ -9256,19 +9256,19 @@
       </c>
       <c s="9" t="inlineStr" r="B290">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C290">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D290">
         <v>44469</v>
       </c>
       <c s="11" r="E290">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9282,24 +9282,24 @@
     <row r="291" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A291">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B291">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C291">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E291">
-        <v>402</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
@@ -9307,30 +9307,30 @@
         </is>
       </c>
       <c s="12" r="G291">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="292" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A292">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B292">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C292">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D292">
         <v>44469</v>
       </c>
       <c s="11" r="E292">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
@@ -9338,30 +9338,30 @@
         </is>
       </c>
       <c s="12" r="G292">
-        <v>44383</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="293" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A293">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B293">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C293">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44348</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E293">
-        <v>70</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
@@ -9369,18 +9369,18 @@
         </is>
       </c>
       <c s="12" r="G293">
-        <v>44308</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
@@ -9389,142 +9389,142 @@
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44347</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E294">
-        <v>260</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44291</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44311</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E295">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44253</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44256</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E296">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D297">
-        <v>44358</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E297">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G297">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A298">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D298">
-        <v>44330</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E298">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G298">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="299" ht="18" customHeight="0">
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c s="10" r="D299">
-        <v>44323</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E299">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44288</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E300">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
@@ -9592,12 +9592,12 @@
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E301">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
@@ -9623,24 +9623,24 @@
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E302">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
@@ -9648,30 +9648,30 @@
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44264</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E303">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
@@ -9679,30 +9679,30 @@
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44242</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E304">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
@@ -9710,80 +9710,80 @@
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>44270</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E305">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44168</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D306">
-        <v>44214</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E306">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G306">
-        <v>44160</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A307">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B307">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C307">
@@ -9792,41 +9792,41 @@
         </is>
       </c>
       <c s="10" r="D307">
-        <v>44211</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E307">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G307">
-        <v>44151</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="308" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A308">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B308">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C308">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E308">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
@@ -9834,18 +9834,18 @@
         </is>
       </c>
       <c s="12" r="G308">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
@@ -9854,29 +9854,29 @@
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E309">
-        <v>280</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G309">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
@@ -9885,14 +9885,14 @@
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44214</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E310">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G310">
@@ -9902,43 +9902,43 @@
     <row r="311" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44186</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E311">
-        <v>59</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G311">
-        <v>44127</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
@@ -9947,119 +9947,127 @@
         </is>
       </c>
       <c s="10" r="D312">
-        <v>44104</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E312">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44104</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D313">
-        <v>44197</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E313">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44151</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D314"/>
-      <c s="13" t="str" r="E314"/>
+          <t xml:space="preserve">Portland</t>
+        </is>
+      </c>
+      <c s="10" r="D314">
+        <v>44104</v>
+      </c>
+      <c s="11" r="E314">
+        <v>59</v>
+      </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G314">
-        <v>44909</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D315"/>
-      <c s="13" t="str" r="E315"/>
+          <t xml:space="preserve">Elgin</t>
+        </is>
+      </c>
+      <c s="10" r="D315">
+        <v>44197</v>
+      </c>
+      <c s="11" r="E315">
+        <v>229</v>
+      </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
           <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G315">
-        <v>45125</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D316"/>
@@ -10070,41 +10078,95 @@
         </is>
       </c>
       <c s="12" r="G316">
+        <v>44909</v>
+      </c>
+    </row>
+    <row r="317" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A317">
+        <is>
+          <t xml:space="preserve">8592</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B317">
+        <is>
+          <t xml:space="preserve">Rise Services, Inc.</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C317">
+        <is>
+          <t xml:space="preserve">Mesa, AZ</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D317"/>
+      <c s="13" t="str" r="E317"/>
+      <c s="9" t="inlineStr" r="F317">
+        <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G317">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="318" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A318">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B318">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C318">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D318"/>
+      <c s="13" t="str" r="E318"/>
+      <c s="9" t="inlineStr" r="F318">
+        <is>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+        </is>
+      </c>
+      <c s="12" r="G318">
         <v>45887</v>
       </c>
     </row>
-    <row r="317" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A317">
+    <row r="319" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A319">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B317">
+      <c s="14" t="inlineStr" r="B319">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C317">
+      <c s="14" t="inlineStr" r="C319">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D317">
+      <c s="14" t="inlineStr" r="D319">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E317">
+      <c s="14" t="inlineStr" r="E319">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F317">
+      <c s="14" t="inlineStr" r="F319">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G317">
+      <c s="14" t="inlineStr" r="G319">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -10119,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/7/2026 11:28:45 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/7/2026 8:46:29 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/7/2016 to 10/7/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/8/2016 to 10/8/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/7/2026 8:46:29 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/8/2026 11:38:59 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/8/2026 11:38:59 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/8/2026 8:53:03 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/8/2016 to 10/8/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/9/2016 to 10/9/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/8/2026 8:53:03 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/9/2026 11:04:04 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/9/2026 11:04:04 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/9/2026 8:32:19 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/9/2016 to 10/9/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/10/2016 to 10/10/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/9/2026 8:32:19 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/10/2026 9:55:27 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/10/2026 9:55:27 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/10/2026 8:05:17 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/10/2016 to 10/10/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/11/2016 to 10/11/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/10/2026 8:05:17 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/11/2026 10:19:26 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/11/2026 10:19:26 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/11/2026 8:31:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/11/2016 to 10/11/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/12/2016 to 10/12/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/11/2026 8:31:30 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/12/2026 1:55:55 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/12/2026 1:55:55 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/12/2026 9:46:13 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/12/2016 to 10/12/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/13/2016 to 10/13/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/12/2026 9:46:13 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/13/2026 12:09:20 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/13/2026 12:09:20 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/13/2026 7:55:01 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/13/2016 to 10/13/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/14/2016 to 10/14/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/13/2026 7:55:01 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/14/2026 9:32:26 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/14/2016 to 10/14/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/15/2016 to 10/15/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/14/2026 9:32:26 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/15/2026 9:17:27 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/15/2026 9:17:27 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/15/2026 7:26:27 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/15/2016 to 10/15/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/16/2016 to 10/16/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/15/2026 7:26:27 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/16/2026 9:07:21 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/16/2026 9:07:21 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/16/2026 7:21:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/16/2016 to 10/16/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/17/2016 to 10/17/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/16/2026 7:21:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/17/2026 7:58:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/17/2026 7:58:16 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/17/2026 7:20:19 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/17/2016 to 10/17/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/18/2016 to 10/18/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/17/2026 7:20:19 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/18/2026 8:26:41 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/18/2026 8:26:41 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/18/2026 7:37:23 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/18/2016 to 10/18/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/19/2016 to 10/19/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/18/2026 7:37:23 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/19/2026 11:19:39 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/19/2026 11:19:39 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/19/2026 7:52:56 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/19/2016 to 10/19/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/20/2016 to 10/20/2026</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/19/2026 7:52:56 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/20/2026 9:21:51 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10181,7 +10181,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/20/2026 9:21:51 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/20/2026 7:47:22 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/21/2026 9:37:47 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/21/2026 7:42:46 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/21/2016 to 10/21/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/22/2016 to 10/22/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/21/2026 7:42:46 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/22/2026 9:35:21 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/22/2026 9:35:21 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/22/2026 7:49:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/22/2016 to 10/22/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/23/2016 to 10/23/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/22/2026 7:49:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/23/2026 7:06:48 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/23/2026 7:06:48 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/23/2026 7:45:02 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/23/2016 to 10/23/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/24/2016 to 10/24/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/23/2026 7:45:02 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/24/2026 8:26:41 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/24/2026 8:26:41 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/24/2026 7:33:32 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/24/2016 to 10/24/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/25/2016 to 10/25/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/24/2026 7:33:32 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/25/2026 8:41:07 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/25/2026 8:41:07 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/25/2026 7:34:24 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/25/2016 to 10/25/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/26/2016 to 10/26/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/25/2026 7:34:24 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/26/2026 11:13:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/26/2026 11:13:56 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/26/2026 8:11:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/26/2016 to 10/26/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/27/2016 to 10/27/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/26/2026 8:11:10 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/27/2026 10:22:25 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/27/2026 10:22:25 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/27/2026 8:17:48 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/27/2016 to 10/27/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/28/2016 to 10/28/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/27/2026 8:17:48 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/28/2026 10:57:14 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/28/2026 10:57:14 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/28/2026 8:41:43 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/28/2016 to 10/28/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/29/2016 to 10/29/2026</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/28/2026 8:41:43 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/29/2026 11:09:46 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -385,24 +385,24 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9646</t>
+          <t xml:space="preserve">9649</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employee(s)</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D4">
         <v>46387</v>
       </c>
       <c s="11" r="E4">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
@@ -410,7 +410,7 @@
         </is>
       </c>
       <c s="12" r="G4">
-        <v>46315</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="0">
@@ -421,19 +421,19 @@
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">Bend - Site</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D5">
         <v>46387</v>
       </c>
       <c s="11" r="E5">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
@@ -452,19 +452,19 @@
       </c>
       <c s="9" t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Bend - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D6">
         <v>46387</v>
       </c>
       <c s="11" r="E6">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
@@ -483,19 +483,19 @@
       </c>
       <c s="9" t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">Salem - Site</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D7">
         <v>46387</v>
       </c>
       <c s="11" r="E7">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
@@ -514,19 +514,19 @@
       </c>
       <c s="9" t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">Medford - Site</t>
+          <t xml:space="preserve">Salem - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D8">
         <v>46387</v>
       </c>
       <c s="11" r="E8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -545,12 +545,12 @@
       </c>
       <c s="9" t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">Hood River - Site</t>
+          <t xml:space="preserve">Medford - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D9">
@@ -571,94 +571,94 @@
     <row r="10" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">9637</t>
+          <t xml:space="preserve">9646</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">Medford Delivery Facility</t>
+          <t xml:space="preserve">Hood River - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D10">
-        <v>46363</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E10">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G10">
-        <v>46301</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">9612</t>
+          <t xml:space="preserve">9637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">Lombard Street Facility</t>
+          <t xml:space="preserve">Medford Delivery Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D11">
-        <v>46349</v>
+        <v>46363</v>
       </c>
       <c s="11" r="E11">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G11">
-        <v>46288</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">9591</t>
+          <t xml:space="preserve">9612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">Tualatin Oregon Facility</t>
+          <t xml:space="preserve">Lombard Street Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D12">
-        <v>46477</v>
+        <v>46349</v>
       </c>
       <c s="11" r="E12">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G12">
-        <v>46266</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="0">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c s="10" r="D13">
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c s="11" r="E13">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F13">
         <is>
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E14">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E15">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c s="10" r="D16">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E16">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -788,24 +788,24 @@
     <row r="17" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">9590</t>
+          <t xml:space="preserve">9591</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B17">
         <is>
-          <t xml:space="preserve">J.R. Johnson, LLC</t>
+          <t xml:space="preserve">Tualatin Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D17">
         <v>46326</v>
       </c>
       <c s="11" r="E17">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -813,69 +813,69 @@
         </is>
       </c>
       <c s="12" r="G17">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">9588</t>
+          <t xml:space="preserve">9590</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
+          <t xml:space="preserve">J.R. Johnson, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D18">
-        <v>46314</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E18">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G18">
-        <v>46254</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">9556</t>
+          <t xml:space="preserve">9588</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">JeniusBank</t>
+          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D19">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c s="11" r="E19">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G19">
-        <v>46244</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="0">
@@ -886,19 +886,19 @@
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">JeniusBank</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c s="10" r="D20">
         <v>46304</v>
       </c>
       <c s="11" r="E20">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
@@ -912,24 +912,24 @@
     <row r="21" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">9555</t>
+          <t xml:space="preserve">9556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Bowtech, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D21">
-        <v>46444</v>
+        <v>46304</v>
       </c>
       <c s="11" r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c s="12" r="G21">
-        <v>46230</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="0">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46416</v>
+        <v>46444</v>
       </c>
       <c s="11" r="E22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46387</v>
+        <v>46416</v>
       </c>
       <c s="11" r="E23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c s="10" r="D24">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c s="10" r="D25">
-        <v>46332</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c s="10" r="D26">
-        <v>46326</v>
+        <v>46332</v>
       </c>
       <c s="11" r="E26">
         <v>5</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c s="10" r="D27">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F27">
         <is>
@@ -1129,24 +1129,24 @@
     <row r="28" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A28">
         <is>
-          <t xml:space="preserve">9553</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B28">
         <is>
-          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D28">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E28">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
@@ -1154,34 +1154,34 @@
         </is>
       </c>
       <c s="12" r="G28">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D29">
-        <v>46266</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E29">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G29">
@@ -1191,94 +1191,94 @@
     <row r="30" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D30">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E30">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G30">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D31">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E31">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G31">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D32">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E32">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G32">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="0">
@@ -1289,19 +1289,19 @@
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D33">
         <v>46206</v>
       </c>
       <c s="11" r="E33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F33">
         <is>
@@ -1320,19 +1320,19 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D34">
         <v>46206</v>
       </c>
       <c s="11" r="E34">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F34">
         <is>
@@ -1346,32 +1346,32 @@
     <row r="35" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A35">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D35">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E35">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F35">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G35">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="0">
@@ -1382,23 +1382,23 @@
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D36">
         <v>46234</v>
       </c>
       <c s="11" r="E36">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G36">
@@ -1413,19 +1413,19 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D37">
         <v>46234</v>
       </c>
       <c s="11" r="E37">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F37">
         <is>
@@ -1444,12 +1444,12 @@
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D38">
@@ -1475,19 +1475,19 @@
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D39">
         <v>46234</v>
       </c>
       <c s="11" r="E39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F39">
         <is>
@@ -1501,55 +1501,55 @@
     <row r="40" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A40">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D40">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E40">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G40">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D41">
-        <v>46333</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E41">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F41">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c s="12" r="G41">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="0">
@@ -1568,23 +1568,23 @@
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D42">
-        <v>46234</v>
+        <v>46333</v>
       </c>
       <c s="11" r="E42">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G42">
@@ -1599,19 +1599,19 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D43">
         <v>46234</v>
       </c>
       <c s="11" r="E43">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F43">
         <is>
@@ -1630,19 +1630,19 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D44">
         <v>46234</v>
       </c>
       <c s="11" r="E44">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
@@ -1661,19 +1661,19 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D45">
         <v>46234</v>
       </c>
       <c s="11" r="E45">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
@@ -1692,19 +1692,19 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D46">
         <v>46234</v>
       </c>
       <c s="11" r="E46">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
@@ -1718,86 +1718,86 @@
     <row r="47" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A47">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D47">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E47">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G47">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D48">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E48">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G48">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D49">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E49">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F49">
         <is>
@@ -1805,49 +1805,49 @@
         </is>
       </c>
       <c s="12" r="G49">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D50">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E50">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F50">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G50">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
@@ -1856,18 +1856,18 @@
         </is>
       </c>
       <c s="10" r="D51">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E51">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F51">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G51">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="0">
@@ -1878,7 +1878,7 @@
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
@@ -1904,24 +1904,24 @@
     <row r="53" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A53">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D53">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E53">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F53">
         <is>
@@ -1929,38 +1929,38 @@
         </is>
       </c>
       <c s="12" r="G53">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D54">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E54">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F54">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G54">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="0">
@@ -1971,19 +1971,19 @@
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D55">
         <v>46131</v>
       </c>
       <c s="11" r="E55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F55">
         <is>
@@ -1997,63 +1997,63 @@
     <row r="56" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A56">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D56">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E56">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F56">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G56">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D57">
         <v>46117</v>
       </c>
       <c s="11" r="E57">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G57">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="0">
@@ -2064,19 +2064,19 @@
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D58">
         <v>46117</v>
       </c>
       <c s="11" r="E58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F58">
         <is>
@@ -2095,12 +2095,12 @@
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D59">
@@ -2126,12 +2126,12 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D60">
@@ -2157,12 +2157,12 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D61">
@@ -2188,12 +2188,12 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D62">
@@ -2219,12 +2219,12 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D63">
@@ -2250,12 +2250,12 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D64">
@@ -2281,7 +2281,7 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
@@ -2312,7 +2312,7 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
@@ -2343,12 +2343,12 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D67">
@@ -2374,12 +2374,12 @@
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D68">
@@ -2405,12 +2405,12 @@
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D69">
@@ -2436,7 +2436,7 @@
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
@@ -2467,19 +2467,19 @@
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D71">
         <v>46117</v>
       </c>
       <c s="11" r="E71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F71">
         <is>
@@ -2498,19 +2498,19 @@
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D72">
         <v>46117</v>
       </c>
       <c s="11" r="E72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2529,19 +2529,19 @@
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D73">
         <v>46117</v>
       </c>
       <c s="11" r="E73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
@@ -2560,12 +2560,12 @@
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D74">
@@ -2591,12 +2591,12 @@
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D75">
@@ -2617,24 +2617,24 @@
     <row r="76" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A76">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D76">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E76">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F76">
         <is>
@@ -2653,19 +2653,19 @@
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D77">
         <v>46112</v>
       </c>
       <c s="11" r="E77">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2684,19 +2684,19 @@
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D78">
         <v>46112</v>
       </c>
       <c s="11" r="E78">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
@@ -2710,24 +2710,24 @@
     <row r="79" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A79">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D79">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E79">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
@@ -2735,30 +2735,30 @@
         </is>
       </c>
       <c s="12" r="G79">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D80">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E80">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
@@ -2766,30 +2766,30 @@
         </is>
       </c>
       <c s="12" r="G80">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D81">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E81">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c s="12" r="G81">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="0">
@@ -2808,7 +2808,7 @@
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
@@ -2820,7 +2820,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E82">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
@@ -2839,19 +2839,19 @@
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D83">
         <v>46014</v>
       </c>
       <c s="11" r="E83">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
@@ -2865,43 +2865,43 @@
     <row r="84" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A84">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D84">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E84">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G84">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
@@ -2910,29 +2910,29 @@
         </is>
       </c>
       <c s="10" r="D85">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E85">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G85">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c s="10" r="D86">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E86">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
@@ -2958,63 +2958,63 @@
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D87">
         <v>46054</v>
       </c>
       <c s="11" r="E87">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G87">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D88">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E88">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G88">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="0">
@@ -3025,19 +3025,19 @@
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D89">
         <v>45916</v>
       </c>
       <c s="11" r="E89">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
@@ -3056,7 +3056,7 @@
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
@@ -3068,7 +3068,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E90">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
@@ -3087,7 +3087,7 @@
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
@@ -3099,7 +3099,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E91">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
@@ -3113,24 +3113,24 @@
     <row r="92" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A92">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D92">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E92">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c s="12" r="G92">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="0">
@@ -3149,23 +3149,23 @@
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D93">
         <v>46022</v>
       </c>
       <c s="11" r="E93">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G93">
@@ -3180,19 +3180,19 @@
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D94">
         <v>46022</v>
       </c>
       <c s="11" r="E94">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
@@ -3211,19 +3211,19 @@
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D95">
         <v>46022</v>
       </c>
       <c s="11" r="E95">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
@@ -3242,19 +3242,19 @@
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D96">
         <v>46022</v>
       </c>
       <c s="11" r="E96">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
@@ -3268,55 +3268,55 @@
     <row r="97" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A97">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D97">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E97">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G97">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D98">
         <v>46017</v>
       </c>
       <c s="11" r="E98">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
@@ -3330,28 +3330,28 @@
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D99">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E99">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G99">
@@ -3375,14 +3375,14 @@
         </is>
       </c>
       <c s="10" r="D100">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E100">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G100">
@@ -3392,86 +3392,86 @@
     <row r="101" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A101">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B101">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C101">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D101">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E101">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G101">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D102">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E102">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G102">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D103">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E103">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
@@ -3479,18 +3479,18 @@
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E104">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
@@ -3510,38 +3510,38 @@
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E105">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
@@ -3561,14 +3561,14 @@
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E106">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G106">
@@ -3578,24 +3578,24 @@
     <row r="107" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A107">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B107">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C107">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E107">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
@@ -3603,34 +3603,34 @@
         </is>
       </c>
       <c s="12" r="G107">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D108">
         <v>45976</v>
       </c>
       <c s="11" r="E108">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G108">
@@ -3640,63 +3640,63 @@
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D109">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E109">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G109">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D110">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E110">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G110">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="0">
@@ -3707,7 +3707,7 @@
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
@@ -3719,7 +3719,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E111">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
@@ -3733,12 +3733,12 @@
     <row r="112" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A112">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
@@ -3747,41 +3747,41 @@
         </is>
       </c>
       <c s="10" r="D112">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E112">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G112">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E113">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
@@ -3789,18 +3789,18 @@
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
@@ -3809,49 +3809,49 @@
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E114">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E115">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
@@ -3862,19 +3862,19 @@
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D116">
         <v>45912</v>
       </c>
       <c s="11" r="E116">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
@@ -3888,63 +3888,63 @@
     <row r="117" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A117">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D117">
         <v>45912</v>
       </c>
       <c s="11" r="E117">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G117">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D118">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E118">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
@@ -3955,19 +3955,19 @@
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D119">
         <v>45853</v>
       </c>
       <c s="11" r="E119">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
@@ -3986,7 +3986,7 @@
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
@@ -3998,7 +3998,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E120">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
@@ -4017,7 +4017,7 @@
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
@@ -4029,7 +4029,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E121">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
@@ -4043,86 +4043,86 @@
     <row r="122" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A122">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D122">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E122">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G122">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E123">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E124">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E125">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E126">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
@@ -4198,24 +4198,24 @@
     <row r="127" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A127">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B127">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C127">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E127">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
@@ -4223,30 +4223,30 @@
         </is>
       </c>
       <c s="12" r="G127">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D128">
         <v>45838</v>
       </c>
       <c s="11" r="E128">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
@@ -4260,94 +4260,94 @@
     <row r="129" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D129">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E129">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G129">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E130">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G130">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E131">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G131">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="0">
@@ -4358,19 +4358,19 @@
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D132">
         <v>45866</v>
       </c>
       <c s="11" r="E132">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
@@ -4384,55 +4384,55 @@
     <row r="133" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A133">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D133">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E133">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G133">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E134">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
@@ -4440,85 +4440,85 @@
         </is>
       </c>
       <c s="12" r="G134">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E135">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G135">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E136">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G136">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D137">
@@ -4529,69 +4529,69 @@
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G137">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D138">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E138">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G138">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E139">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G139">
@@ -4601,43 +4601,43 @@
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E140">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G140">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
@@ -4646,103 +4646,103 @@
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E141">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E142">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E143">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G143">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E144">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
@@ -4750,38 +4750,38 @@
         </is>
       </c>
       <c s="12" r="G144">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D145">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E145">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G145">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="0">
@@ -4792,19 +4792,19 @@
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D146">
         <v>45707</v>
       </c>
       <c s="11" r="E146">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
@@ -4818,63 +4818,63 @@
     <row r="147" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A147">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D147">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E147">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G147">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="148" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E148">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G148">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="0">
@@ -4885,19 +4885,19 @@
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D149">
         <v>45696</v>
       </c>
       <c s="11" r="E149">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
@@ -4911,86 +4911,86 @@
     <row r="150" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A150">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D150">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E150">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G150">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="151" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E151">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G151">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D152">
         <v>45931</v>
       </c>
       <c s="11" r="E152">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
@@ -5004,43 +5004,43 @@
     <row r="153" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D153">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E153">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G153">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="154" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
@@ -5049,18 +5049,18 @@
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E154">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G154">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="0">
@@ -5071,19 +5071,19 @@
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D155">
         <v>45726</v>
       </c>
       <c s="11" r="E155">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
@@ -5102,19 +5102,19 @@
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D156">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E156">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
@@ -5133,19 +5133,19 @@
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D157">
         <v>45725</v>
       </c>
       <c s="11" r="E157">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
@@ -5164,19 +5164,19 @@
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D158">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E158">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
@@ -5195,12 +5195,12 @@
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D159">
@@ -5226,12 +5226,12 @@
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D160">
@@ -5257,7 +5257,7 @@
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c s="10" r="D161">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E161">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F161">
         <is>
@@ -5288,19 +5288,19 @@
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D162">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E162">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c s="9" t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C163">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E163">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5350,19 +5350,19 @@
       </c>
       <c s="9" t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C164">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E164">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5376,12 +5376,12 @@
     <row r="165" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A165">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C165">
@@ -5390,72 +5390,72 @@
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E165">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G165">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="166" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E166">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G166">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E167">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
@@ -5463,100 +5463,100 @@
         </is>
       </c>
       <c s="12" r="G167">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E168">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E169">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E170">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
@@ -5567,19 +5567,19 @@
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D171">
         <v>45611</v>
       </c>
       <c s="11" r="E171">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
@@ -5598,7 +5598,7 @@
       </c>
       <c s="9" t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C172">
@@ -5610,7 +5610,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E172">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
@@ -5629,7 +5629,7 @@
       </c>
       <c s="9" t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C173">
@@ -5641,7 +5641,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E173">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
@@ -5655,28 +5655,28 @@
     <row r="174" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A174">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C174">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D174">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E174">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G174">
@@ -5686,24 +5686,24 @@
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E175">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
@@ -5711,38 +5711,38 @@
         </is>
       </c>
       <c s="12" r="G175">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C176">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E176">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
@@ -5753,23 +5753,23 @@
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D177">
         <v>45544</v>
       </c>
       <c s="11" r="E177">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G177">
@@ -5779,55 +5779,55 @@
     <row r="178" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A178">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D178">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E178">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G178">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E179">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E180">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5886,14 +5886,14 @@
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E181">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G181">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
@@ -5948,14 +5948,14 @@
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E183">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G183">
@@ -5965,24 +5965,24 @@
     <row r="184" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A184">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B184">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C184">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E184">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c s="12" r="G184">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="185" ht="18" customHeight="0">
@@ -6010,14 +6010,14 @@
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E185">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G185">
@@ -6027,24 +6027,24 @@
     <row r="186" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A186">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B186">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C186">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E186">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
@@ -6052,13 +6052,13 @@
         </is>
       </c>
       <c s="12" r="G186">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E187">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
@@ -6083,18 +6083,18 @@
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C188">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E188">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
@@ -6114,30 +6114,30 @@
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D189">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E189">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c s="10" r="D190">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E190">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E191">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
@@ -6213,32 +6213,32 @@
     <row r="192" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A192">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B192">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C192">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D192">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E192">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G192">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="193" ht="18" customHeight="0">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c s="10" r="D193">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E193">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E194">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6306,43 +6306,43 @@
     <row r="195" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A195">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B195">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C195">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E195">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G195">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E196">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
@@ -6362,111 +6362,111 @@
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D197">
         <v>45471</v>
       </c>
       <c s="11" r="E197">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G197">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D198">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E198">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G198">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E199">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G199">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
@@ -6475,134 +6475,134 @@
         </is>
       </c>
       <c s="10" r="D200">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E200">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G200">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D201">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E201">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G201">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D202">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E202">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G202">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D203">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E203">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G203">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E204">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
@@ -6610,18 +6610,18 @@
         </is>
       </c>
       <c s="12" r="G204">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
@@ -6630,41 +6630,41 @@
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E205">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G205">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E206">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c s="12" r="G206">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="0">
@@ -6683,7 +6683,7 @@
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
@@ -6695,7 +6695,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E207">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
@@ -6709,24 +6709,24 @@
     <row r="208" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A208">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D208">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E208">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6734,34 +6734,34 @@
         </is>
       </c>
       <c s="12" r="G208">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D209">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E209">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G209">
@@ -6776,19 +6776,19 @@
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D210">
         <v>45382</v>
       </c>
       <c s="11" r="E210">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
@@ -6807,19 +6807,19 @@
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D211">
         <v>45382</v>
       </c>
       <c s="11" r="E211">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6838,7 +6838,7 @@
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
@@ -6850,7 +6850,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E212">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6869,12 +6869,12 @@
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D213">
@@ -6895,32 +6895,32 @@
     <row r="214" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A214">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D214">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E214">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F214">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G214">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="215" ht="18" customHeight="0">
@@ -6931,23 +6931,23 @@
       </c>
       <c s="9" t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D215">
         <v>45366</v>
       </c>
       <c s="11" r="E215">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G215">
@@ -6957,55 +6957,55 @@
     <row r="216" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A216">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D216">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E216">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G216">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E217">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c s="12" r="G217">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="0">
@@ -7024,19 +7024,19 @@
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D218">
         <v>45275</v>
       </c>
       <c s="11" r="E218">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7055,19 +7055,19 @@
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D219">
         <v>45275</v>
       </c>
       <c s="11" r="E219">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7086,19 +7086,19 @@
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D220">
         <v>45275</v>
       </c>
       <c s="11" r="E220">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7112,24 +7112,24 @@
     <row r="221" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A221">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D221">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E221">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
@@ -7137,30 +7137,30 @@
         </is>
       </c>
       <c s="12" r="G221">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="222" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E222">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
@@ -7168,30 +7168,30 @@
         </is>
       </c>
       <c s="12" r="G222">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E223">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c s="12" r="G223">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="0">
@@ -7219,10 +7219,10 @@
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E224">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E225">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
@@ -7267,24 +7267,24 @@
     <row r="226" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A226">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E226">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7292,18 +7292,18 @@
         </is>
       </c>
       <c s="12" r="G226">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="227" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
@@ -7315,7 +7315,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E227">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7329,12 +7329,12 @@
     <row r="228" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C228">
@@ -7346,7 +7346,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E228">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7360,24 +7360,24 @@
     <row r="229" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D229">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E229">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7385,61 +7385,61 @@
         </is>
       </c>
       <c s="12" r="G229">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="230" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E230">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G230">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E231">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E232">
         <v>2</v>
@@ -7498,14 +7498,14 @@
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E233">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F233">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G233">
@@ -7520,7 +7520,7 @@
       </c>
       <c s="9" t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C234">
@@ -7532,11 +7532,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E234">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G234">
@@ -7551,7 +7551,7 @@
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c s="10" r="D235">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E235">
         <v>3</v>
@@ -7582,7 +7582,7 @@
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
@@ -7594,7 +7594,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F236">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
@@ -7622,10 +7622,10 @@
         </is>
       </c>
       <c s="10" r="D237">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E238">
         <v>1</v>
@@ -7675,7 +7675,7 @@
       </c>
       <c s="9" t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C239">
@@ -7684,14 +7684,14 @@
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E239">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F239">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G239">
@@ -7706,7 +7706,7 @@
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
@@ -7718,7 +7718,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E240">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
@@ -7732,86 +7732,86 @@
     <row r="241" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A241">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D241">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E241">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G241">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E242">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G242">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E243">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
@@ -7825,24 +7825,24 @@
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E244">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c s="12" r="G244">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="245" ht="18" customHeight="0">
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c s="10" r="D245">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E245">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
@@ -7887,24 +7887,24 @@
     <row r="246" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A246">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B246">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C246">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D246">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E246">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c s="12" r="G246">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="247" ht="18" customHeight="0">
@@ -7923,19 +7923,19 @@
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E247">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
@@ -7949,32 +7949,32 @@
     <row r="248" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A248">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E248">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G248">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="0">
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c s="10" r="D249">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E249">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
@@ -8011,24 +8011,24 @@
     <row r="250" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A250">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B250">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C250">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D250">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E250">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
@@ -8036,30 +8036,30 @@
         </is>
       </c>
       <c s="12" r="G250">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D251">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E251">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
@@ -8067,123 +8067,123 @@
         </is>
       </c>
       <c s="12" r="G251">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D252">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E252">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G252">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D253">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E253">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G253">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E254">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G254">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E255">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
@@ -8191,30 +8191,30 @@
         </is>
       </c>
       <c s="12" r="G255">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E256">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
@@ -8222,61 +8222,61 @@
         </is>
       </c>
       <c s="12" r="G256">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E257">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G257">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D258">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E258">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
@@ -8284,30 +8284,30 @@
         </is>
       </c>
       <c s="12" r="G258">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D259">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E259">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c s="12" r="G259">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
@@ -8326,12 +8326,12 @@
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D260">
@@ -8357,12 +8357,12 @@
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D261">
@@ -8388,12 +8388,12 @@
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D262">
@@ -8419,12 +8419,12 @@
       </c>
       <c s="9" t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C263">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D263">
@@ -8445,86 +8445,86 @@
     <row r="264" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A264">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D264">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E264">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F264">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G264">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D265">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E265">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G265">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D266">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E266">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
@@ -8538,24 +8538,24 @@
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D267">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E267">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8563,30 +8563,30 @@
         </is>
       </c>
       <c s="12" r="G267">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D268">
         <v>45079</v>
       </c>
       <c s="11" r="E268">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8600,12 +8600,12 @@
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
@@ -8614,103 +8614,103 @@
         </is>
       </c>
       <c s="10" r="D269">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E269">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G269">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D270">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E270">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E271">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G271">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E272">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
@@ -8718,30 +8718,30 @@
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E273">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8749,80 +8749,80 @@
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E274">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E275">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
@@ -8831,41 +8831,41 @@
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E276">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E277">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
@@ -8873,30 +8873,30 @@
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E278">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8904,30 +8904,30 @@
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C279">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E279">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c s="12" r="G279">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="0">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E280">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8972,74 +8972,74 @@
     <row r="281" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A281">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B281">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C281">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E281">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G281">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="282" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C282">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E282">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G282">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C283">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E283">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
@@ -9059,30 +9059,30 @@
         </is>
       </c>
       <c s="12" r="G283">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E284">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
@@ -9113,7 +9113,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E285">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9127,24 +9127,24 @@
     <row r="286" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A286">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B286">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C286">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D286">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E286">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9152,30 +9152,30 @@
         </is>
       </c>
       <c s="12" r="G286">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E287">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
@@ -9183,30 +9183,30 @@
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D288">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E288">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c s="12" r="G288">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="0">
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E289">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E290">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E291">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
@@ -9327,10 +9327,10 @@
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E292">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E293">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
@@ -9375,12 +9375,12 @@
     <row r="294" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A294">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B294">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C294">
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E294">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
@@ -9400,30 +9400,30 @@
         </is>
       </c>
       <c s="12" r="G294">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E295">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
@@ -9431,30 +9431,30 @@
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E296">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
@@ -9473,7 +9473,7 @@
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
@@ -9485,7 +9485,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E297">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
@@ -9504,19 +9504,19 @@
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D298">
         <v>44469</v>
       </c>
       <c s="11" r="E298">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
@@ -9530,24 +9530,24 @@
     <row r="299" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A299">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D299">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E299">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
@@ -9555,30 +9555,30 @@
         </is>
       </c>
       <c s="12" r="G299">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E300">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
@@ -9586,18 +9586,18 @@
         </is>
       </c>
       <c s="12" r="G300">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E301">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
@@ -9617,18 +9617,18 @@
         </is>
       </c>
       <c s="12" r="G301">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
@@ -9637,49 +9637,49 @@
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E302">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E303">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E304">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
@@ -9716,32 +9716,32 @@
     <row r="305" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A305">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B305">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C305">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D305">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E305">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G305">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="306" ht="18" customHeight="0">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c s="10" r="D306">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E306">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c s="10" r="D307">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E307">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E308">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
@@ -9840,12 +9840,12 @@
     <row r="309" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A309">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B309">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C309">
@@ -9857,7 +9857,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E309">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
@@ -9871,24 +9871,24 @@
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D310">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E310">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c s="12" r="G310">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="311" ht="18" customHeight="0">
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E311">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
@@ -9933,24 +9933,24 @@
     <row r="312" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A312">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B312">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C312">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D312">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E312">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
@@ -9958,100 +9958,100 @@
         </is>
       </c>
       <c s="12" r="G312">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D313">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E313">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D314">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E314">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G314">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D315">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E315">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G315">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="0">
@@ -10074,11 +10074,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E316">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F316">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G316">
@@ -10088,12 +10088,12 @@
     <row r="317" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A317">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B317">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C317">
@@ -10102,29 +10102,29 @@
         </is>
       </c>
       <c s="10" r="D317">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E317">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F317">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G317">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="318" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
@@ -10133,69 +10133,69 @@
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E318">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G318">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E319">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G319">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D320">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E320">
         <v>59</v>
@@ -10206,159 +10206,189 @@
         </is>
       </c>
       <c s="12" r="G320">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D321">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E321">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F321">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G321">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D322"/>
-      <c s="13" t="str" r="E322"/>
+          <t xml:space="preserve">Elgin</t>
+        </is>
+      </c>
+      <c s="10" r="D322">
+        <v>44197</v>
+      </c>
+      <c s="11" r="E322">
+        <v>229</v>
+      </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G322">
-        <v>44909</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D323"/>
       <c s="13" t="str" r="E323"/>
       <c s="9" t="inlineStr" r="F323">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G323">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D324"/>
       <c s="13" t="str" r="E324"/>
       <c s="9" t="inlineStr" r="F324">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G324">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="325" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A325">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B325">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C325">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D325"/>
+      <c s="13" t="str" r="E325"/>
+      <c s="9" t="inlineStr" r="F325">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G324">
+      <c s="12" r="G325">
         <v>45887</v>
       </c>
     </row>
-    <row r="325" ht="3.55" customHeight="0">
-      <c s="14" t="inlineStr" r="A325">
+    <row r="326" ht="3.6" customHeight="0">
+      <c s="14" t="inlineStr" r="A326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B325">
+      <c s="14" t="inlineStr" r="B326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C325">
+      <c s="14" t="inlineStr" r="C326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D325">
+      <c s="14" t="inlineStr" r="D326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E325">
+      <c s="14" t="inlineStr" r="E326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F325">
+      <c s="14" t="inlineStr" r="F326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G325">
+      <c s="14" t="inlineStr" r="G326">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="326" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10368,7 +10398,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/29/2026 11:09:46 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/29/2026 8:45:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -341,7 +341,7 @@
     <row r="2" ht="18" customHeight="1">
       <c s="2" t="inlineStr" r="B2">
         <is>
-          <t xml:space="preserve">WARNs Received: 10/29/2016 to 10/29/2026</t>
+          <t xml:space="preserve">WARNs Received: 10/30/2016 to 10/30/2026</t>
         </is>
       </c>
     </row>
@@ -385,24 +385,24 @@
     <row r="4" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">9649</t>
+          <t xml:space="preserve">9650</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employee(s)</t>
+          <t xml:space="preserve">Endeavors, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">San Antonio, TX</t>
         </is>
       </c>
       <c s="10" r="D4">
         <v>46387</v>
       </c>
       <c s="11" r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F4">
         <is>
@@ -416,24 +416,24 @@
     <row r="5" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">9646</t>
+          <t xml:space="preserve">9649</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B5">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employee(s)</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D5">
         <v>46387</v>
       </c>
       <c s="11" r="E5">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F5">
         <is>
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c s="12" r="G5">
-        <v>46315</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="0">
@@ -452,19 +452,19 @@
       </c>
       <c s="9" t="inlineStr" r="B6">
         <is>
-          <t xml:space="preserve">Bend - Site</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D6">
         <v>46387</v>
       </c>
       <c s="11" r="E6">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F6">
         <is>
@@ -483,19 +483,19 @@
       </c>
       <c s="9" t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Bend - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D7">
         <v>46387</v>
       </c>
       <c s="11" r="E7">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F7">
         <is>
@@ -514,19 +514,19 @@
       </c>
       <c s="9" t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">Salem - Site</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D8">
         <v>46387</v>
       </c>
       <c s="11" r="E8">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F8">
         <is>
@@ -545,19 +545,19 @@
       </c>
       <c s="9" t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">Medford - Site</t>
+          <t xml:space="preserve">Salem - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D9">
         <v>46387</v>
       </c>
       <c s="11" r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F9">
         <is>
@@ -576,12 +576,12 @@
       </c>
       <c s="9" t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">Hood River - Site</t>
+          <t xml:space="preserve">Medford - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D10">
@@ -602,94 +602,94 @@
     <row r="11" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">9637</t>
+          <t xml:space="preserve">9646</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">Medford Delivery Facility</t>
+          <t xml:space="preserve">Hood River - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D11">
-        <v>46363</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E11">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G11">
-        <v>46301</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">9612</t>
+          <t xml:space="preserve">9637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">Lombard Street Facility</t>
+          <t xml:space="preserve">Medford Delivery Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D12">
-        <v>46349</v>
+        <v>46363</v>
       </c>
       <c s="11" r="E12">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G12">
-        <v>46288</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">9591</t>
+          <t xml:space="preserve">9612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">Tualatin Oregon Facility</t>
+          <t xml:space="preserve">Lombard Street Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D13">
-        <v>46477</v>
+        <v>46349</v>
       </c>
       <c s="11" r="E13">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G13">
-        <v>46266</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="0">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c s="10" r="D14">
-        <v>46446</v>
+        <v>46477</v>
       </c>
       <c s="11" r="E14">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F14">
         <is>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c s="10" r="D15">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c s="11" r="E15">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F15">
         <is>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c s="10" r="D16">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E16">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F16">
         <is>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c s="10" r="D17">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E17">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F17">
         <is>
@@ -819,24 +819,24 @@
     <row r="18" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">9590</t>
+          <t xml:space="preserve">9591</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">J.R. Johnson, LLC</t>
+          <t xml:space="preserve">Tualatin Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D18">
         <v>46326</v>
       </c>
       <c s="11" r="E18">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F18">
         <is>
@@ -844,69 +844,69 @@
         </is>
       </c>
       <c s="12" r="G18">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">9588</t>
+          <t xml:space="preserve">9590</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B19">
         <is>
-          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
+          <t xml:space="preserve">J.R. Johnson, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D19">
-        <v>46314</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E19">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c s="9" t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G19">
-        <v>46254</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">9556</t>
+          <t xml:space="preserve">9588</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">JeniusBank</t>
+          <t xml:space="preserve">Amentum - Hillsboro, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">New York, NY</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D20">
-        <v>46304</v>
+        <v>46314</v>
       </c>
       <c s="11" r="E20">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c s="9" t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G20">
-        <v>46244</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="0">
@@ -917,19 +917,19 @@
       </c>
       <c s="9" t="inlineStr" r="B21">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">JeniusBank</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">New York, NY</t>
         </is>
       </c>
       <c s="10" r="D21">
         <v>46304</v>
       </c>
       <c s="11" r="E21">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F21">
         <is>
@@ -943,24 +943,24 @@
     <row r="22" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">9555</t>
+          <t xml:space="preserve">9556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">Bowtech, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D22">
-        <v>46444</v>
+        <v>46304</v>
       </c>
       <c s="11" r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F22">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c s="12" r="G22">
-        <v>46230</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="0">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c s="10" r="D23">
-        <v>46416</v>
+        <v>46444</v>
       </c>
       <c s="11" r="E23">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F23">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c s="10" r="D24">
-        <v>46387</v>
+        <v>46416</v>
       </c>
       <c s="11" r="E24">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F24">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c s="10" r="D25">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c s="11" r="E25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F25">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c s="10" r="D26">
-        <v>46332</v>
+        <v>46356</v>
       </c>
       <c s="11" r="E26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F26">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c s="10" r="D27">
-        <v>46326</v>
+        <v>46332</v>
       </c>
       <c s="11" r="E27">
         <v>5</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c s="10" r="D28">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c s="11" r="E28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F28">
         <is>
@@ -1160,24 +1160,24 @@
     <row r="29" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A29">
         <is>
-          <t xml:space="preserve">9553</t>
+          <t xml:space="preserve">9555</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
+          <t xml:space="preserve">Bowtech, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D29">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E29">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F29">
         <is>
@@ -1185,34 +1185,34 @@
         </is>
       </c>
       <c s="12" r="G29">
-        <v>46237</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A30">
         <is>
-          <t xml:space="preserve">9550</t>
+          <t xml:space="preserve">9553</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">Avamere Health Services, LLC</t>
+          <t xml:space="preserve">TV Hardware Distribution, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Tigard</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D30">
-        <v>46266</v>
+        <v>46298</v>
       </c>
       <c s="11" r="E30">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G30">
@@ -1222,94 +1222,94 @@
     <row r="31" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A31">
         <is>
-          <t xml:space="preserve">9549</t>
+          <t xml:space="preserve">9550</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B31">
         <is>
-          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
+          <t xml:space="preserve">Avamere Health Services, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tigard</t>
         </is>
       </c>
       <c s="10" r="D31">
-        <v>46325</v>
+        <v>46266</v>
       </c>
       <c s="11" r="E31">
-        <v>387</v>
+        <v>129</v>
       </c>
       <c s="9" t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G31">
-        <v>46233</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A32">
         <is>
-          <t xml:space="preserve">9534</t>
+          <t xml:space="preserve">9549</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B32">
         <is>
-          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
+          <t xml:space="preserve">Portland Truck Manufacturing Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D32">
-        <v>46262</v>
+        <v>46325</v>
       </c>
       <c s="11" r="E32">
-        <v>17</v>
+        <v>387</v>
       </c>
       <c s="9" t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G32">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A33">
         <is>
-          <t xml:space="preserve">9532</t>
+          <t xml:space="preserve">9534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B33">
         <is>
-          <t xml:space="preserve">Adventist Health Tillamook</t>
+          <t xml:space="preserve">Conduent - Oregon Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D33">
-        <v>46206</v>
+        <v>46262</v>
       </c>
       <c s="11" r="E33">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c s="9" t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G33">
-        <v>46197</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="0">
@@ -1320,19 +1320,19 @@
       </c>
       <c s="9" t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">Adventist Health Portland</t>
+          <t xml:space="preserve">Adventist Health Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">Portland, </t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D34">
         <v>46206</v>
       </c>
       <c s="11" r="E34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F34">
         <is>
@@ -1351,19 +1351,19 @@
       </c>
       <c s="9" t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
+          <t xml:space="preserve">Adventist Health Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">The Dalles</t>
+          <t xml:space="preserve">Portland, </t>
         </is>
       </c>
       <c s="10" r="D35">
         <v>46206</v>
       </c>
       <c s="11" r="E35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F35">
         <is>
@@ -1377,32 +1377,32 @@
     <row r="36" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A36">
         <is>
-          <t xml:space="preserve">9517</t>
+          <t xml:space="preserve">9532</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B36">
         <is>
-          <t xml:space="preserve">PacificSource</t>
+          <t xml:space="preserve">Adventist Health Columbia Gorge</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">The Dalles</t>
         </is>
       </c>
       <c s="10" r="D36">
-        <v>46234</v>
+        <v>46206</v>
       </c>
       <c s="11" r="E36">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G36">
-        <v>46169</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="0">
@@ -1413,23 +1413,23 @@
       </c>
       <c s="9" t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">PacificSource - Bend</t>
+          <t xml:space="preserve">PacificSource</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D37">
         <v>46234</v>
       </c>
       <c s="11" r="E37">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G37">
@@ -1444,19 +1444,19 @@
       </c>
       <c s="9" t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">PacificSource - Portland</t>
+          <t xml:space="preserve">PacificSource - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D38">
         <v>46234</v>
       </c>
       <c s="11" r="E38">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F38">
         <is>
@@ -1475,12 +1475,12 @@
       </c>
       <c s="9" t="inlineStr" r="B39">
         <is>
-          <t xml:space="preserve">PacificSource - Salem</t>
+          <t xml:space="preserve">PacificSource - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D39">
@@ -1506,19 +1506,19 @@
       </c>
       <c s="9" t="inlineStr" r="B40">
         <is>
-          <t xml:space="preserve">PacificSource Hood River</t>
+          <t xml:space="preserve">PacificSource - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Hood River</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D40">
         <v>46234</v>
       </c>
       <c s="11" r="E40">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F40">
         <is>
@@ -1532,55 +1532,55 @@
     <row r="41" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A41">
         <is>
-          <t xml:space="preserve">9511</t>
+          <t xml:space="preserve">9517</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
+          <t xml:space="preserve">PacificSource Hood River</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">Hood River</t>
         </is>
       </c>
       <c s="10" r="D41">
-        <v>46228</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E41">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F41">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G41">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A42">
         <is>
-          <t xml:space="preserve">9509</t>
+          <t xml:space="preserve">9511</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Safeway Store 0378 - Newport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D42">
-        <v>46333</v>
+        <v>46228</v>
       </c>
       <c s="11" r="E42">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F42">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c s="12" r="G42">
-        <v>46160</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="0">
@@ -1599,23 +1599,23 @@
       </c>
       <c s="9" t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D43">
-        <v>46234</v>
+        <v>46333</v>
       </c>
       <c s="11" r="E43">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G43">
@@ -1630,19 +1630,19 @@
       </c>
       <c s="9" t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">Bend Depot Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D44">
         <v>46234</v>
       </c>
       <c s="11" r="E44">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F44">
         <is>
@@ -1661,19 +1661,19 @@
       </c>
       <c s="9" t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">Eugene Facility</t>
+          <t xml:space="preserve">Bend Depot Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D45">
         <v>46234</v>
       </c>
       <c s="11" r="E45">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F45">
         <is>
@@ -1692,19 +1692,19 @@
       </c>
       <c s="9" t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">Medford Facility</t>
+          <t xml:space="preserve">Eugene Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D46">
         <v>46234</v>
       </c>
       <c s="11" r="E46">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F46">
         <is>
@@ -1723,19 +1723,19 @@
       </c>
       <c s="9" t="inlineStr" r="B47">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Medford Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D47">
         <v>46234</v>
       </c>
       <c s="11" r="E47">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F47">
         <is>
@@ -1749,86 +1749,86 @@
     <row r="48" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A48">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">Coburg Facility</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Coburg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D48">
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c s="11" r="E48">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c s="9" t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G48">
-        <v>46155</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A49">
         <is>
-          <t xml:space="preserve">9495</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B49">
         <is>
-          <t xml:space="preserve">Prineville, OR Facility</t>
+          <t xml:space="preserve">Coburg Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Coburg</t>
         </is>
       </c>
       <c s="10" r="D49">
-        <v>46201</v>
+        <v>46220</v>
       </c>
       <c s="11" r="E49">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F49">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G49">
-        <v>46141</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A50">
         <is>
-          <t xml:space="preserve">9474</t>
+          <t xml:space="preserve">9495</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B50">
         <is>
-          <t xml:space="preserve">Troutdale Facility</t>
+          <t xml:space="preserve">Prineville, OR Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D50">
-        <v>46295</v>
+        <v>46201</v>
       </c>
       <c s="11" r="E50">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F50">
         <is>
@@ -1836,49 +1836,49 @@
         </is>
       </c>
       <c s="12" r="G50">
-        <v>46114</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A51">
         <is>
-          <t xml:space="preserve">9473</t>
+          <t xml:space="preserve">9474</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B51">
         <is>
-          <t xml:space="preserve">Sunstone Way</t>
+          <t xml:space="preserve">Troutdale Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D51">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c s="11" r="E51">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F51">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G51">
-        <v>46108</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A52">
         <is>
-          <t xml:space="preserve">9470</t>
+          <t xml:space="preserve">9473</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B52">
         <is>
-          <t xml:space="preserve">Direct Marketing Solutions</t>
+          <t xml:space="preserve">Sunstone Way</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C52">
@@ -1887,18 +1887,18 @@
         </is>
       </c>
       <c s="10" r="D52">
-        <v>46178</v>
+        <v>46203</v>
       </c>
       <c s="11" r="E52">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c s="9" t="inlineStr" r="F52">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G52">
-        <v>46118</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="0">
@@ -1909,7 +1909,7 @@
       </c>
       <c s="9" t="inlineStr" r="B53">
         <is>
-          <t xml:space="preserve">Sumner St - Portland</t>
+          <t xml:space="preserve">Direct Marketing Solutions</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C53">
@@ -1935,24 +1935,24 @@
     <row r="54" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A54">
         <is>
-          <t xml:space="preserve">9465</t>
+          <t xml:space="preserve">9470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
+          <t xml:space="preserve">Sumner St - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D54">
-        <v>46173</v>
+        <v>46178</v>
       </c>
       <c s="11" r="E54">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c s="9" t="inlineStr" r="F54">
         <is>
@@ -1960,38 +1960,38 @@
         </is>
       </c>
       <c s="12" r="G54">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A55">
         <is>
-          <t xml:space="preserve">9446</t>
+          <t xml:space="preserve">9465</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B55">
         <is>
-          <t xml:space="preserve">Albany/Millersburg</t>
+          <t xml:space="preserve">Horizon Air - Rogue Valley Internationa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D55">
-        <v>46131</v>
+        <v>46173</v>
       </c>
       <c s="11" r="E55">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F55">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G55">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="0">
@@ -2002,19 +2002,19 @@
       </c>
       <c s="9" t="inlineStr" r="B56">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Albany/Millersburg</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D56">
         <v>46131</v>
       </c>
       <c s="11" r="E56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F56">
         <is>
@@ -2028,63 +2028,63 @@
     <row r="57" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A57">
         <is>
-          <t xml:space="preserve">9436</t>
+          <t xml:space="preserve">9446</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B57">
         <is>
-          <t xml:space="preserve">Riddle Plywood facility </t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">Riddle</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D57">
-        <v>46117</v>
+        <v>46131</v>
       </c>
       <c s="11" r="E57">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G57">
-        <v>46057</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A58">
         <is>
-          <t xml:space="preserve">9434</t>
+          <t xml:space="preserve">9436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B58">
         <is>
-          <t xml:space="preserve">Kroger-00035</t>
+          <t xml:space="preserve">Riddle Plywood facility </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Riddle</t>
         </is>
       </c>
       <c s="10" r="D58">
         <v>46117</v>
       </c>
       <c s="11" r="E58">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c s="9" t="inlineStr" r="F58">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G58">
-        <v>46051</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="0">
@@ -2095,19 +2095,19 @@
       </c>
       <c s="9" t="inlineStr" r="B59">
         <is>
-          <t xml:space="preserve">Kroger-00040</t>
+          <t xml:space="preserve">Kroger-00035</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D59">
         <v>46117</v>
       </c>
       <c s="11" r="E59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F59">
         <is>
@@ -2126,12 +2126,12 @@
       </c>
       <c s="9" t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">Kroger-00063</t>
+          <t xml:space="preserve">Kroger-00040</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D60">
@@ -2157,12 +2157,12 @@
       </c>
       <c s="9" t="inlineStr" r="B61">
         <is>
-          <t xml:space="preserve">Kroger-00075-Prime</t>
+          <t xml:space="preserve">Kroger-00063</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D61">
@@ -2188,12 +2188,12 @@
       </c>
       <c s="9" t="inlineStr" r="B62">
         <is>
-          <t xml:space="preserve">Kroger-00090</t>
+          <t xml:space="preserve">Kroger-00075-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D62">
@@ -2219,12 +2219,12 @@
       </c>
       <c s="9" t="inlineStr" r="B63">
         <is>
-          <t xml:space="preserve">Kroger-00125-Prime</t>
+          <t xml:space="preserve">Kroger-00090</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">North Tabor</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D63">
@@ -2250,12 +2250,12 @@
       </c>
       <c s="9" t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">Kroger-00127-Prime</t>
+          <t xml:space="preserve">Kroger-00125-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">Powell Valley</t>
+          <t xml:space="preserve">North Tabor</t>
         </is>
       </c>
       <c s="10" r="D64">
@@ -2281,12 +2281,12 @@
       </c>
       <c s="9" t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">Kroger-00128-Prime</t>
+          <t xml:space="preserve">Kroger-00127-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Powell Valley</t>
         </is>
       </c>
       <c s="10" r="D65">
@@ -2312,7 +2312,7 @@
       </c>
       <c s="9" t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">Kroger-00135</t>
+          <t xml:space="preserve">Kroger-00128-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C66">
@@ -2343,7 +2343,7 @@
       </c>
       <c s="9" t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">Kroger-00150-Prime</t>
+          <t xml:space="preserve">Kroger-00135</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C67">
@@ -2374,12 +2374,12 @@
       </c>
       <c s="9" t="inlineStr" r="B68">
         <is>
-          <t xml:space="preserve">Kroger-00153</t>
+          <t xml:space="preserve">Kroger-00150-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C68">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D68">
@@ -2405,12 +2405,12 @@
       </c>
       <c s="9" t="inlineStr" r="B69">
         <is>
-          <t xml:space="preserve">Kroger-00240</t>
+          <t xml:space="preserve">Kroger-00153</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C69">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D69">
@@ -2436,12 +2436,12 @@
       </c>
       <c s="9" t="inlineStr" r="B70">
         <is>
-          <t xml:space="preserve">Kroger-00255</t>
+          <t xml:space="preserve">Kroger-00240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C70">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D70">
@@ -2467,7 +2467,7 @@
       </c>
       <c s="9" t="inlineStr" r="B71">
         <is>
-          <t xml:space="preserve">Kroger-00360-Prime</t>
+          <t xml:space="preserve">Kroger-00255</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C71">
@@ -2498,19 +2498,19 @@
       </c>
       <c s="9" t="inlineStr" r="B72">
         <is>
-          <t xml:space="preserve">Kroger-00417</t>
+          <t xml:space="preserve">Kroger-00360-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C72">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D72">
         <v>46117</v>
       </c>
       <c s="11" r="E72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F72">
         <is>
@@ -2529,19 +2529,19 @@
       </c>
       <c s="9" t="inlineStr" r="B73">
         <is>
-          <t xml:space="preserve">Kroger-00600-Prime</t>
+          <t xml:space="preserve">Kroger-00417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C73">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D73">
         <v>46117</v>
       </c>
       <c s="11" r="E73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F73">
         <is>
@@ -2560,19 +2560,19 @@
       </c>
       <c s="9" t="inlineStr" r="B74">
         <is>
-          <t xml:space="preserve">Kroger-00516</t>
+          <t xml:space="preserve">Kroger-00600-Prime</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C74">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D74">
         <v>46117</v>
       </c>
       <c s="11" r="E74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F74">
         <is>
@@ -2591,12 +2591,12 @@
       </c>
       <c s="9" t="inlineStr" r="B75">
         <is>
-          <t xml:space="preserve">Kroger-00660</t>
+          <t xml:space="preserve">Kroger-00516</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C75">
         <is>
-          <t xml:space="preserve">Wood Village</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D75">
@@ -2622,12 +2622,12 @@
       </c>
       <c s="9" t="inlineStr" r="B76">
         <is>
-          <t xml:space="preserve">Lincare-Brookings, OR</t>
+          <t xml:space="preserve">Kroger-00660</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C76">
         <is>
-          <t xml:space="preserve">Brookings</t>
+          <t xml:space="preserve">Wood Village</t>
         </is>
       </c>
       <c s="10" r="D76">
@@ -2648,24 +2648,24 @@
     <row r="77" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A77">
         <is>
-          <t xml:space="preserve">9429</t>
+          <t xml:space="preserve">9434</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B77">
         <is>
-          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
+          <t xml:space="preserve">Lincare-Brookings, OR</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C77">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Brookings</t>
         </is>
       </c>
       <c s="10" r="D77">
-        <v>46112</v>
+        <v>46117</v>
       </c>
       <c s="11" r="E77">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F77">
         <is>
@@ -2684,19 +2684,19 @@
       </c>
       <c s="9" t="inlineStr" r="B78">
         <is>
-          <t xml:space="preserve">Eugene Location</t>
+          <t xml:space="preserve">Three Pirates, LLC dba Point Blank Dist</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C78">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D78">
         <v>46112</v>
       </c>
       <c s="11" r="E78">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c s="9" t="inlineStr" r="F78">
         <is>
@@ -2715,19 +2715,19 @@
       </c>
       <c s="9" t="inlineStr" r="B79">
         <is>
-          <t xml:space="preserve">Bend Location</t>
+          <t xml:space="preserve">Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C79">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D79">
         <v>46112</v>
       </c>
       <c s="11" r="E79">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c s="9" t="inlineStr" r="F79">
         <is>
@@ -2741,24 +2741,24 @@
     <row r="80" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A80">
         <is>
-          <t xml:space="preserve">9420</t>
+          <t xml:space="preserve">9429</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B80">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C80">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D80">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c s="11" r="E80">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c s="9" t="inlineStr" r="F80">
         <is>
@@ -2766,30 +2766,30 @@
         </is>
       </c>
       <c s="12" r="G80">
-        <v>46030</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A81">
         <is>
-          <t xml:space="preserve">9415</t>
+          <t xml:space="preserve">9420</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B81">
         <is>
-          <t xml:space="preserve">Vacuum Technique LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C81">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D81">
-        <v>46142</v>
+        <v>46091</v>
       </c>
       <c s="11" r="E81">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F81">
         <is>
@@ -2797,30 +2797,30 @@
         </is>
       </c>
       <c s="12" r="G81">
-        <v>46020</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A82">
         <is>
-          <t xml:space="preserve">9414</t>
+          <t xml:space="preserve">9415</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B82">
         <is>
-          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
+          <t xml:space="preserve">Vacuum Technique LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C82">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D82">
-        <v>46014</v>
+        <v>46142</v>
       </c>
       <c s="11" r="E82">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F82">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c s="12" r="G82">
-        <v>46014</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="0">
@@ -2839,7 +2839,7 @@
       </c>
       <c s="9" t="inlineStr" r="B83">
         <is>
-          <t xml:space="preserve">Administrative Office</t>
+          <t xml:space="preserve">Solgen Power, LLC dba Purelight Power</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C83">
@@ -2851,7 +2851,7 @@
         <v>46014</v>
       </c>
       <c s="11" r="E83">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F83">
         <is>
@@ -2870,19 +2870,19 @@
       </c>
       <c s="9" t="inlineStr" r="B84">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Administrative Office</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C84">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D84">
         <v>46014</v>
       </c>
       <c s="11" r="E84">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F84">
         <is>
@@ -2896,43 +2896,43 @@
     <row r="85" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A85">
         <is>
-          <t xml:space="preserve">9408</t>
+          <t xml:space="preserve">9414</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B85">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C85">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D85">
-        <v>46059</v>
+        <v>46014</v>
       </c>
       <c s="11" r="E85">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F85">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G85">
-        <v>46000</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A86">
         <is>
-          <t xml:space="preserve">9402</t>
+          <t xml:space="preserve">9408</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B86">
         <is>
-          <t xml:space="preserve">Nordstrom Portland Rack</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C86">
@@ -2941,29 +2941,29 @@
         </is>
       </c>
       <c s="10" r="D86">
-        <v>46053</v>
+        <v>46059</v>
       </c>
       <c s="11" r="E86">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F86">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G86">
-        <v>45992</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A87">
         <is>
-          <t xml:space="preserve">9401</t>
+          <t xml:space="preserve">9402</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B87">
         <is>
-          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
+          <t xml:space="preserve">Nordstrom Portland Rack</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C87">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c s="10" r="D87">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c s="11" r="E87">
-        <v>310</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F87">
         <is>
@@ -2989,63 +2989,63 @@
     <row r="88" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A88">
         <is>
-          <t xml:space="preserve">9392</t>
+          <t xml:space="preserve">9401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B88">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vibra Specialty Hospital of Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C88">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D88">
         <v>46054</v>
       </c>
       <c s="11" r="E88">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c s="9" t="inlineStr" r="F88">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G88">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A89">
         <is>
-          <t xml:space="preserve">9389</t>
+          <t xml:space="preserve">9392</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B89">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C89">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D89">
-        <v>45916</v>
+        <v>46054</v>
       </c>
       <c s="11" r="E89">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F89">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G89">
-        <v>45974</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="0">
@@ -3056,19 +3056,19 @@
       </c>
       <c s="9" t="inlineStr" r="B90">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C90">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D90">
         <v>45916</v>
       </c>
       <c s="11" r="E90">
-        <v>510</v>
+        <v>41</v>
       </c>
       <c s="9" t="inlineStr" r="F90">
         <is>
@@ -3087,7 +3087,7 @@
       </c>
       <c s="9" t="inlineStr" r="B91">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C91">
@@ -3099,7 +3099,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E91">
-        <v>42</v>
+        <v>510</v>
       </c>
       <c s="9" t="inlineStr" r="F91">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c s="9" t="inlineStr" r="B92">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C92">
@@ -3130,7 +3130,7 @@
         <v>45916</v>
       </c>
       <c s="11" r="E92">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F92">
         <is>
@@ -3144,24 +3144,24 @@
     <row r="93" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A93">
         <is>
-          <t xml:space="preserve">9377</t>
+          <t xml:space="preserve">9389</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B93">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C93">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D93">
-        <v>46022</v>
+        <v>45916</v>
       </c>
       <c s="11" r="E93">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F93">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c s="12" r="G93">
-        <v>45954</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="0">
@@ -3180,23 +3180,23 @@
       </c>
       <c s="9" t="inlineStr" r="B94">
         <is>
-          <t xml:space="preserve">Pacific Source - Bend</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C94">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D94">
         <v>46022</v>
       </c>
       <c s="11" r="E94">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c s="9" t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G94">
@@ -3211,19 +3211,19 @@
       </c>
       <c s="9" t="inlineStr" r="B95">
         <is>
-          <t xml:space="preserve">Pacific Source - Medford</t>
+          <t xml:space="preserve">Pacific Source - Bend</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C95">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D95">
         <v>46022</v>
       </c>
       <c s="11" r="E95">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F95">
         <is>
@@ -3242,19 +3242,19 @@
       </c>
       <c s="9" t="inlineStr" r="B96">
         <is>
-          <t xml:space="preserve">Pacific Source - Portland</t>
+          <t xml:space="preserve">Pacific Source - Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C96">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D96">
         <v>46022</v>
       </c>
       <c s="11" r="E96">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F96">
         <is>
@@ -3273,19 +3273,19 @@
       </c>
       <c s="9" t="inlineStr" r="B97">
         <is>
-          <t xml:space="preserve">Pacific Source - Salem</t>
+          <t xml:space="preserve">Pacific Source - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C97">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D97">
         <v>46022</v>
       </c>
       <c s="11" r="E97">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c s="9" t="inlineStr" r="F97">
         <is>
@@ -3299,55 +3299,55 @@
     <row r="98" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A98">
         <is>
-          <t xml:space="preserve">9376</t>
+          <t xml:space="preserve">9377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B98">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
+          <t xml:space="preserve">Pacific Source - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C98">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D98">
-        <v>46017</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E98">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c s="9" t="inlineStr" r="F98">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G98">
-        <v>45958</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A99">
         <is>
-          <t xml:space="preserve">9375</t>
+          <t xml:space="preserve">9376</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B99">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
+          <t xml:space="preserve">Wells Fargo and Company - 5th Ave. Port</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C99">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D99">
         <v>46017</v>
       </c>
       <c s="11" r="E99">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c s="9" t="inlineStr" r="F99">
         <is>
@@ -3361,28 +3361,28 @@
     <row r="100" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A100">
         <is>
-          <t xml:space="preserve">9374</t>
+          <t xml:space="preserve">9375</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B100">
         <is>
-          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
+          <t xml:space="preserve">Wells Fargo and Company - Hawthorne Ave</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C100">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D100">
-        <v>46101</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E100">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c s="9" t="inlineStr" r="F100">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G100">
@@ -3406,14 +3406,14 @@
         </is>
       </c>
       <c s="10" r="D101">
-        <v>46017</v>
+        <v>46101</v>
       </c>
       <c s="11" r="E101">
-        <v>263</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F101">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G101">
@@ -3423,86 +3423,86 @@
     <row r="102" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A102">
         <is>
-          <t xml:space="preserve">9363</t>
+          <t xml:space="preserve">9374</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B102">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Wells Fargo and Company - Walker Rd. Hi</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C102">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D102">
-        <v>45993</v>
+        <v>46017</v>
       </c>
       <c s="11" r="E102">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c s="9" t="inlineStr" r="F102">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G102">
-        <v>45933</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A103">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9363</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B103">
         <is>
-          <t xml:space="preserve">Pacific Source</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C103">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D103">
-        <v>46022</v>
+        <v>45993</v>
       </c>
       <c s="11" r="E103">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F103">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G103">
-        <v>45917</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A104">
         <is>
-          <t xml:space="preserve">9357</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B104">
         <is>
-          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
+          <t xml:space="preserve">Pacific Source</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C104">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D104">
-        <v>45978</v>
+        <v>46022</v>
       </c>
       <c s="11" r="E104">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F104">
         <is>
@@ -3510,18 +3510,18 @@
         </is>
       </c>
       <c s="12" r="G104">
-        <v>45943</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A105">
         <is>
-          <t xml:space="preserve">9354</t>
+          <t xml:space="preserve">9357</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B105">
         <is>
-          <t xml:space="preserve">Wells Fargo Center - Portland</t>
+          <t xml:space="preserve">Bags, A Metropolis Company - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C105">
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c s="10" r="D105">
-        <v>45989</v>
+        <v>45978</v>
       </c>
       <c s="11" r="E105">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c s="9" t="inlineStr" r="F105">
         <is>
@@ -3541,38 +3541,38 @@
         </is>
       </c>
       <c s="12" r="G105">
-        <v>45930</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A106">
         <is>
-          <t xml:space="preserve">9350</t>
+          <t xml:space="preserve">9354</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B106">
         <is>
-          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
+          <t xml:space="preserve">Wells Fargo Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C106">
         <is>
-          <t xml:space="preserve">Dillard</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D106">
-        <v>45940</v>
+        <v>45989</v>
       </c>
       <c s="11" r="E106">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F106">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G106">
-        <v>45925</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="0">
@@ -3592,14 +3592,14 @@
         </is>
       </c>
       <c s="10" r="D107">
-        <v>45925</v>
+        <v>45940</v>
       </c>
       <c s="11" r="E107">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F107">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G107">
@@ -3609,24 +3609,24 @@
     <row r="108" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A108">
         <is>
-          <t xml:space="preserve">9346</t>
+          <t xml:space="preserve">9350</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B108">
         <is>
-          <t xml:space="preserve">Hillsboro Facility</t>
+          <t xml:space="preserve">Dillard Hardwood Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C108">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Dillard</t>
         </is>
       </c>
       <c s="10" r="D108">
-        <v>45976</v>
+        <v>45925</v>
       </c>
       <c s="11" r="E108">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F108">
         <is>
@@ -3634,34 +3634,34 @@
         </is>
       </c>
       <c s="12" r="G108">
-        <v>45916</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A109">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9346</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B109">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Hillsboro Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C109">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D109">
         <v>45976</v>
       </c>
       <c s="11" r="E109">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F109">
         <is>
-          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G109">
@@ -3671,63 +3671,63 @@
     <row r="110" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A110">
         <is>
-          <t xml:space="preserve">9344</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B110">
         <is>
-          <t xml:space="preserve">Nike World Headquarters</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C110">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D110">
-        <v>46006</v>
+        <v>45976</v>
       </c>
       <c s="11" r="E110">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Small Layoff  1 – 10 workers</t>
         </is>
       </c>
       <c s="12" r="G110">
-        <v>45915</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A111">
         <is>
-          <t xml:space="preserve">9328</t>
+          <t xml:space="preserve">9344</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B111">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Nike World Headquarters</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C111">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D111">
-        <v>45949</v>
+        <v>46006</v>
       </c>
       <c s="11" r="E111">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c s="9" t="inlineStr" r="F111">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G111">
-        <v>45889</v>
+        <v>45915</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="0">
@@ -3738,7 +3738,7 @@
       </c>
       <c s="9" t="inlineStr" r="B112">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C112">
@@ -3750,7 +3750,7 @@
         <v>45949</v>
       </c>
       <c s="11" r="E112">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F112">
         <is>
@@ -3764,12 +3764,12 @@
     <row r="113" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A113">
         <is>
-          <t xml:space="preserve">9322</t>
+          <t xml:space="preserve">9328</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B113">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C113">
@@ -3778,41 +3778,41 @@
         </is>
       </c>
       <c s="10" r="D113">
-        <v>45943</v>
+        <v>45949</v>
       </c>
       <c s="11" r="E113">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F113">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G113">
-        <v>45881</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A114">
         <is>
-          <t xml:space="preserve">9306</t>
+          <t xml:space="preserve">9322</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B114">
         <is>
-          <t xml:space="preserve">Portland - Production Facility</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C114">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D114">
-        <v>45874</v>
+        <v>45943</v>
       </c>
       <c s="11" r="E114">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F114">
         <is>
@@ -3820,18 +3820,18 @@
         </is>
       </c>
       <c s="12" r="G114">
-        <v>45867</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A115">
         <is>
-          <t xml:space="preserve">9299</t>
+          <t xml:space="preserve">9306</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B115">
         <is>
-          <t xml:space="preserve">Store #128</t>
+          <t xml:space="preserve">Portland - Production Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C115">
@@ -3840,49 +3840,49 @@
         </is>
       </c>
       <c s="10" r="D115">
-        <v>45920</v>
+        <v>45874</v>
       </c>
       <c s="11" r="E115">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F115">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G115">
-        <v>45854</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A116">
         <is>
-          <t xml:space="preserve">9296</t>
+          <t xml:space="preserve">9299</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B116">
         <is>
-          <t xml:space="preserve">Oregon Mutual</t>
+          <t xml:space="preserve">Store #128</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C116">
         <is>
-          <t xml:space="preserve">McMinnville</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D116">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c s="11" r="E116">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c s="9" t="inlineStr" r="F116">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G116">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="0">
@@ -3893,19 +3893,19 @@
       </c>
       <c s="9" t="inlineStr" r="B117">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Oregon Mutual</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C117">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">McMinnville</t>
         </is>
       </c>
       <c s="10" r="D117">
         <v>45912</v>
       </c>
       <c s="11" r="E117">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F117">
         <is>
@@ -3919,63 +3919,63 @@
     <row r="118" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A118">
         <is>
-          <t xml:space="preserve">9294</t>
+          <t xml:space="preserve">9296</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B118">
         <is>
-          <t xml:space="preserve">Outside Van, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C118">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D118">
         <v>45912</v>
       </c>
       <c s="11" r="E118">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c s="9" t="inlineStr" r="F118">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G118">
-        <v>45846</v>
+        <v>45849</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A119">
         <is>
-          <t xml:space="preserve">9293</t>
+          <t xml:space="preserve">9294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B119">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Outside Van, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C119">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D119">
-        <v>45853</v>
+        <v>45912</v>
       </c>
       <c s="11" r="E119">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F119">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G119">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="0">
@@ -3986,19 +3986,19 @@
       </c>
       <c s="9" t="inlineStr" r="B120">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C120">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D120">
         <v>45853</v>
       </c>
       <c s="11" r="E120">
-        <v>1544</v>
+        <v>194</v>
       </c>
       <c s="9" t="inlineStr" r="F120">
         <is>
@@ -4017,7 +4017,7 @@
       </c>
       <c s="9" t="inlineStr" r="B121">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C121">
@@ -4029,7 +4029,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E121">
-        <v>174</v>
+        <v>1544</v>
       </c>
       <c s="9" t="inlineStr" r="F121">
         <is>
@@ -4048,7 +4048,7 @@
       </c>
       <c s="9" t="inlineStr" r="B122">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C122">
@@ -4060,7 +4060,7 @@
         <v>45853</v>
       </c>
       <c s="11" r="E122">
-        <v>597</v>
+        <v>174</v>
       </c>
       <c s="9" t="inlineStr" r="F122">
         <is>
@@ -4074,86 +4074,86 @@
     <row r="123" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A123">
         <is>
-          <t xml:space="preserve">9286</t>
+          <t xml:space="preserve">9293</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B123">
         <is>
-          <t xml:space="preserve">Rogue Valley Transportation District</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C123">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D123">
-        <v>45899</v>
+        <v>45853</v>
       </c>
       <c s="11" r="E123">
-        <v>82</v>
+        <v>597</v>
       </c>
       <c s="9" t="inlineStr" r="F123">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G123">
-        <v>45831</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A124">
         <is>
-          <t xml:space="preserve">9285</t>
+          <t xml:space="preserve">9286</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B124">
         <is>
-          <t xml:space="preserve">Pilot Rock Sawmill</t>
+          <t xml:space="preserve">Rogue Valley Transportation District</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C124">
         <is>
-          <t xml:space="preserve">Pilot Rock</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D124">
-        <v>45901</v>
+        <v>45899</v>
       </c>
       <c s="11" r="E124">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F124">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G124">
-        <v>45839</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A125">
         <is>
-          <t xml:space="preserve">9273</t>
+          <t xml:space="preserve">9285</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B125">
         <is>
-          <t xml:space="preserve">Prineville Facility</t>
+          <t xml:space="preserve">Pilot Rock Sawmill</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C125">
         <is>
-          <t xml:space="preserve">Prineville</t>
+          <t xml:space="preserve">Pilot Rock</t>
         </is>
       </c>
       <c s="10" r="D125">
-        <v>45982</v>
+        <v>45901</v>
       </c>
       <c s="11" r="E125">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F125">
         <is>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c s="12" r="G125">
-        <v>45832</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="0">
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c s="10" r="D126">
-        <v>45968</v>
+        <v>45982</v>
       </c>
       <c s="11" r="E126">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F126">
         <is>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c s="10" r="D127">
-        <v>45894</v>
+        <v>45968</v>
       </c>
       <c s="11" r="E127">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c s="9" t="inlineStr" r="F127">
         <is>
@@ -4229,24 +4229,24 @@
     <row r="128" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A128">
         <is>
-          <t xml:space="preserve">9268</t>
+          <t xml:space="preserve">9273</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B128">
         <is>
-          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
+          <t xml:space="preserve">Prineville Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C128">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Prineville</t>
         </is>
       </c>
       <c s="10" r="D128">
-        <v>45838</v>
+        <v>45894</v>
       </c>
       <c s="11" r="E128">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F128">
         <is>
@@ -4254,30 +4254,30 @@
         </is>
       </c>
       <c s="12" r="G128">
-        <v>45817</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="129" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A129">
         <is>
-          <t xml:space="preserve">9267</t>
+          <t xml:space="preserve">9268</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B129">
         <is>
-          <t xml:space="preserve">Springdale Job Corps Center</t>
+          <t xml:space="preserve">PIVOT Job Corps Center Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C129">
         <is>
-          <t xml:space="preserve">Troutdale</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D129">
         <v>45838</v>
       </c>
       <c s="11" r="E129">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F129">
         <is>
@@ -4291,94 +4291,94 @@
     <row r="130" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A130">
         <is>
-          <t xml:space="preserve">9259</t>
+          <t xml:space="preserve">9267</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B130">
         <is>
-          <t xml:space="preserve">Tongue Point Job Corps Center</t>
+          <t xml:space="preserve">Springdale Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C130">
         <is>
-          <t xml:space="preserve">Astoria</t>
+          <t xml:space="preserve">Troutdale</t>
         </is>
       </c>
       <c s="10" r="D130">
-        <v>45814</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E130">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c s="9" t="inlineStr" r="F130">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G130">
-        <v>45812</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="131" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A131">
         <is>
-          <t xml:space="preserve">9257</t>
+          <t xml:space="preserve">9259</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B131">
         <is>
-          <t xml:space="preserve">ESS Tech, Inc.</t>
+          <t xml:space="preserve">Tongue Point Job Corps Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C131">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Astoria</t>
         </is>
       </c>
       <c s="10" r="D131">
-        <v>45807</v>
+        <v>45814</v>
       </c>
       <c s="11" r="E131">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c s="9" t="inlineStr" r="F131">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G131">
-        <v>45804</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="132" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A132">
         <is>
-          <t xml:space="preserve">9249</t>
+          <t xml:space="preserve">9257</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B132">
         <is>
-          <t xml:space="preserve">Powin LLC</t>
+          <t xml:space="preserve">ESS Tech, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C132">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D132">
-        <v>45866</v>
+        <v>45807</v>
       </c>
       <c s="11" r="E132">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c s="9" t="inlineStr" r="F132">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G132">
-        <v>45806</v>
+        <v>45804</v>
       </c>
     </row>
     <row r="133" ht="18" customHeight="0">
@@ -4389,19 +4389,19 @@
       </c>
       <c s="9" t="inlineStr" r="B133">
         <is>
-          <t xml:space="preserve">Remote Workers</t>
+          <t xml:space="preserve">Powin LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C133">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D133">
         <v>45866</v>
       </c>
       <c s="11" r="E133">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F133">
         <is>
@@ -4415,55 +4415,55 @@
     <row r="134" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A134">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9249</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B134">
         <is>
-          <t xml:space="preserve">Store 0505 - Portland</t>
+          <t xml:space="preserve">Remote Workers</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C134">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D134">
-        <v>45839</v>
+        <v>45866</v>
       </c>
       <c s="11" r="E134">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c s="9" t="inlineStr" r="F134">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G134">
-        <v>45777</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="135" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A135">
         <is>
-          <t xml:space="preserve">9218</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B135">
         <is>
-          <t xml:space="preserve">Chiloquin Facility</t>
+          <t xml:space="preserve">Store 0505 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C135">
         <is>
-          <t xml:space="preserve">Chiloquin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D135">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c s="11" r="E135">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F135">
         <is>
@@ -4471,85 +4471,85 @@
         </is>
       </c>
       <c s="12" r="G135">
-        <v>45778</v>
+        <v>45777</v>
       </c>
     </row>
     <row r="136" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A136">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9218</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B136">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Chiloquin Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C136">
         <is>
-          <t xml:space="preserve">Portand</t>
+          <t xml:space="preserve">Chiloquin</t>
         </is>
       </c>
       <c s="10" r="D136">
-        <v>45769</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E136">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c s="9" t="inlineStr" r="F136">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G136">
-        <v>45769</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="137" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A137">
         <is>
-          <t xml:space="preserve">9207</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B137">
         <is>
-          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C137">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Portand</t>
         </is>
       </c>
       <c s="10" r="D137">
-        <v>45838</v>
+        <v>45769</v>
       </c>
       <c s="11" r="E137">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F137">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G137">
-        <v>45768</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="138" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A138">
         <is>
-          <t xml:space="preserve">9206</t>
+          <t xml:space="preserve">9207</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B138">
         <is>
-          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
+          <t xml:space="preserve">Lignetics, Inc. - Cascade Locks Facilit</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C138">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D138">
@@ -4560,69 +4560,69 @@
       </c>
       <c s="9" t="inlineStr" r="F138">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G138">
-        <v>45763</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="139" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A139">
         <is>
-          <t xml:space="preserve">9204</t>
+          <t xml:space="preserve">9206</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B139">
         <is>
-          <t xml:space="preserve">Safeway Store 4381</t>
+          <t xml:space="preserve">Navajo Incorprated, Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C139">
         <is>
-          <t xml:space="preserve">Baker City</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D139">
-        <v>45802</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E139">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F139">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G139">
-        <v>45742</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="140" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A140">
         <is>
-          <t xml:space="preserve">9199</t>
+          <t xml:space="preserve">9204</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B140">
         <is>
-          <t xml:space="preserve">Oregon - Statewide</t>
+          <t xml:space="preserve">Safeway Store 4381</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C140">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Baker City</t>
         </is>
       </c>
       <c s="10" r="D140">
-        <v>45810</v>
+        <v>45802</v>
       </c>
       <c s="11" r="E140">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c s="9" t="inlineStr" r="F140">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G140">
@@ -4632,43 +4632,43 @@
     <row r="141" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A141">
         <is>
-          <t xml:space="preserve">9198</t>
+          <t xml:space="preserve">9199</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B141">
         <is>
-          <t xml:space="preserve">Portland, Oregon Facility</t>
+          <t xml:space="preserve">Oregon - Statewide</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C141">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D141">
-        <v>45808</v>
+        <v>45810</v>
       </c>
       <c s="11" r="E141">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c s="9" t="inlineStr" r="F141">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G141">
-        <v>45755</v>
+        <v>45742</v>
       </c>
     </row>
     <row r="142" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A142">
         <is>
-          <t xml:space="preserve">9179</t>
+          <t xml:space="preserve">9198</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B142">
         <is>
-          <t xml:space="preserve">Portland Facility</t>
+          <t xml:space="preserve">Portland, Oregon Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C142">
@@ -4677,103 +4677,103 @@
         </is>
       </c>
       <c s="10" r="D142">
-        <v>45834</v>
+        <v>45808</v>
       </c>
       <c s="11" r="E142">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F142">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G142">
-        <v>45774</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A143">
         <is>
-          <t xml:space="preserve">9178</t>
+          <t xml:space="preserve">9179</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B143">
         <is>
-          <t xml:space="preserve">UPS</t>
+          <t xml:space="preserve">Portland Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C143">
         <is>
-          <t xml:space="preserve">Atlanta, GA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D143">
-        <v>45838</v>
+        <v>45834</v>
       </c>
       <c s="11" r="E143">
-        <v>244</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F143">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G143">
-        <v>45744</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="144" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A144">
         <is>
-          <t xml:space="preserve">9131</t>
+          <t xml:space="preserve">9178</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B144">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">UPS</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C144">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Atlanta, GA</t>
         </is>
       </c>
       <c s="10" r="D144">
-        <v>45706</v>
+        <v>45838</v>
       </c>
       <c s="11" r="E144">
-        <v>96</v>
+        <v>244</v>
       </c>
       <c s="9" t="inlineStr" r="F144">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G144">
-        <v>45706</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="145" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A145">
         <is>
-          <t xml:space="preserve">9082</t>
+          <t xml:space="preserve">9131</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B145">
         <is>
-          <t xml:space="preserve">Macy's - Salem Center</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C145">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D145">
-        <v>45734</v>
+        <v>45706</v>
       </c>
       <c s="11" r="E145">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c s="9" t="inlineStr" r="F145">
         <is>
@@ -4781,38 +4781,38 @@
         </is>
       </c>
       <c s="12" r="G145">
-        <v>45666</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="146" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A146">
         <is>
-          <t xml:space="preserve">9068</t>
+          <t xml:space="preserve">9082</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B146">
         <is>
-          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
+          <t xml:space="preserve">Macy's - Salem Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C146">
         <is>
-          <t xml:space="preserve">Mountain View, CA</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D146">
-        <v>45707</v>
+        <v>45734</v>
       </c>
       <c s="11" r="E146">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F146">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G146">
-        <v>45646</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="147" ht="18" customHeight="0">
@@ -4823,19 +4823,19 @@
       </c>
       <c s="9" t="inlineStr" r="B147">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Vimo, Inc. dba GetInsured</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C147">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Mountain View, CA</t>
         </is>
       </c>
       <c s="10" r="D147">
         <v>45707</v>
       </c>
       <c s="11" r="E147">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c s="9" t="inlineStr" r="F147">
         <is>
@@ -4849,63 +4849,63 @@
     <row r="148" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A148">
         <is>
-          <t xml:space="preserve">9057</t>
+          <t xml:space="preserve">9068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B148">
         <is>
-          <t xml:space="preserve">Albertsons Store 0515</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C148">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D148">
-        <v>45695</v>
+        <v>45707</v>
       </c>
       <c s="11" r="E148">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F148">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G148">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="149" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A149">
         <is>
-          <t xml:space="preserve">9056</t>
+          <t xml:space="preserve">9057</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B149">
         <is>
-          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
+          <t xml:space="preserve">Albertsons Store 0515</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C149">
         <is>
-          <t xml:space="preserve">Peoria, IL</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D149">
-        <v>45696</v>
+        <v>45695</v>
       </c>
       <c s="11" r="E149">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F149">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G149">
-        <v>45636</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="150" ht="18" customHeight="0">
@@ -4916,19 +4916,19 @@
       </c>
       <c s="9" t="inlineStr" r="B150">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Natural Fiber Welding, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C150">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Peoria, IL</t>
         </is>
       </c>
       <c s="10" r="D150">
         <v>45696</v>
       </c>
       <c s="11" r="E150">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c s="9" t="inlineStr" r="F150">
         <is>
@@ -4942,86 +4942,86 @@
     <row r="151" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A151">
         <is>
-          <t xml:space="preserve">9050</t>
+          <t xml:space="preserve">9056</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B151">
         <is>
-          <t xml:space="preserve">Cabinet Door Service</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C151">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D151">
-        <v>45616</v>
+        <v>45696</v>
       </c>
       <c s="11" r="E151">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F151">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G151">
-        <v>45615</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="152" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A152">
         <is>
-          <t xml:space="preserve">9049</t>
+          <t xml:space="preserve">9050</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B152">
         <is>
-          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
+          <t xml:space="preserve">Cabinet Door Service</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C152">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D152">
-        <v>45931</v>
+        <v>45616</v>
       </c>
       <c s="11" r="E152">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F152">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G152">
-        <v>45629</v>
+        <v>45615</v>
       </c>
     </row>
     <row r="153" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A153">
         <is>
-          <t xml:space="preserve">9048</t>
+          <t xml:space="preserve">9049</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B153">
         <is>
-          <t xml:space="preserve">Hawthorne Ave - Salem</t>
+          <t xml:space="preserve">Wells Fargo N.A. William Barnhart Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C153">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D153">
         <v>45931</v>
       </c>
       <c s="11" r="E153">
-        <v>221</v>
+        <v>500</v>
       </c>
       <c s="9" t="inlineStr" r="F153">
         <is>
@@ -5035,43 +5035,43 @@
     <row r="154" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A154">
         <is>
-          <t xml:space="preserve">9034</t>
+          <t xml:space="preserve">9048</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B154">
         <is>
-          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
+          <t xml:space="preserve">Hawthorne Ave - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C154">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D154">
-        <v>45674</v>
+        <v>45931</v>
       </c>
       <c s="11" r="E154">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c s="9" t="inlineStr" r="F154">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G154">
-        <v>45611</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="155" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A155">
         <is>
-          <t xml:space="preserve">9029</t>
+          <t xml:space="preserve">9034</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B155">
         <is>
-          <t xml:space="preserve">#4184 - Portland</t>
+          <t xml:space="preserve">The Boeing Company - Oregon Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C155">
@@ -5080,18 +5080,18 @@
         </is>
       </c>
       <c s="10" r="D155">
-        <v>45726</v>
+        <v>45674</v>
       </c>
       <c s="11" r="E155">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F155">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G155">
-        <v>45610</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="156" ht="18" customHeight="0">
@@ -5102,19 +5102,19 @@
       </c>
       <c s="9" t="inlineStr" r="B156">
         <is>
-          <t xml:space="preserve">#4324 - Sandy</t>
+          <t xml:space="preserve">#4184 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C156">
         <is>
-          <t xml:space="preserve">Sandy</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D156">
         <v>45726</v>
       </c>
       <c s="11" r="E156">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c s="9" t="inlineStr" r="F156">
         <is>
@@ -5133,19 +5133,19 @@
       </c>
       <c s="9" t="inlineStr" r="B157">
         <is>
-          <t xml:space="preserve">#3573 - Gresham</t>
+          <t xml:space="preserve">#4324 - Sandy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C157">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Sandy</t>
         </is>
       </c>
       <c s="10" r="D157">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c s="11" r="E157">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F157">
         <is>
@@ -5164,19 +5164,19 @@
       </c>
       <c s="9" t="inlineStr" r="B158">
         <is>
-          <t xml:space="preserve">#3911 - Milwaukie</t>
+          <t xml:space="preserve">#3573 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C158">
         <is>
-          <t xml:space="preserve">Milwaukie</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D158">
         <v>45725</v>
       </c>
       <c s="11" r="E158">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F158">
         <is>
@@ -5195,19 +5195,19 @@
       </c>
       <c s="9" t="inlineStr" r="B159">
         <is>
-          <t xml:space="preserve">#9938 - Portland</t>
+          <t xml:space="preserve">#3911 - Milwaukie</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C159">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Milwaukie</t>
         </is>
       </c>
       <c s="10" r="D159">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c s="11" r="E159">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F159">
         <is>
@@ -5226,12 +5226,12 @@
       </c>
       <c s="9" t="inlineStr" r="B160">
         <is>
-          <t xml:space="preserve">#3574 - Gresham</t>
+          <t xml:space="preserve">#9938 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C160">
         <is>
-          <t xml:space="preserve">Gresham</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D160">
@@ -5257,12 +5257,12 @@
       </c>
       <c s="9" t="inlineStr" r="B161">
         <is>
-          <t xml:space="preserve">#3113 - Beaverton</t>
+          <t xml:space="preserve">#3574 - Gresham</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C161">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Gresham</t>
         </is>
       </c>
       <c s="10" r="D161">
@@ -5288,7 +5288,7 @@
       </c>
       <c s="9" t="inlineStr" r="B162">
         <is>
-          <t xml:space="preserve">#7866 - Beaverton</t>
+          <t xml:space="preserve">#3113 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C162">
@@ -5297,10 +5297,10 @@
         </is>
       </c>
       <c s="10" r="D162">
-        <v>45715</v>
+        <v>45721</v>
       </c>
       <c s="11" r="E162">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F162">
         <is>
@@ -5319,19 +5319,19 @@
       </c>
       <c s="9" t="inlineStr" r="B163">
         <is>
-          <t xml:space="preserve">#4181 - Portland</t>
+          <t xml:space="preserve">#7866 - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C163">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D163">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c s="11" r="E163">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F163">
         <is>
@@ -5350,7 +5350,7 @@
       </c>
       <c s="9" t="inlineStr" r="B164">
         <is>
-          <t xml:space="preserve">Distribution Center - Portland</t>
+          <t xml:space="preserve">#4181 - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C164">
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c s="10" r="D164">
-        <v>45703</v>
+        <v>45714</v>
       </c>
       <c s="11" r="E164">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F164">
         <is>
@@ -5381,19 +5381,19 @@
       </c>
       <c s="9" t="inlineStr" r="B165">
         <is>
-          <t xml:space="preserve">#3612 - Hillsboro</t>
+          <t xml:space="preserve">Distribution Center - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C165">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D165">
-        <v>45690</v>
+        <v>45703</v>
       </c>
       <c s="11" r="E165">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c s="9" t="inlineStr" r="F165">
         <is>
@@ -5407,12 +5407,12 @@
     <row r="166" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A166">
         <is>
-          <t xml:space="preserve">9025</t>
+          <t xml:space="preserve">9029</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B166">
         <is>
-          <t xml:space="preserve">Hillsboro Client Site</t>
+          <t xml:space="preserve">#3612 - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C166">
@@ -5421,72 +5421,72 @@
         </is>
       </c>
       <c s="10" r="D166">
-        <v>45657</v>
+        <v>45690</v>
       </c>
       <c s="11" r="E166">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F166">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G166">
-        <v>45601</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="167" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A167">
         <is>
-          <t xml:space="preserve">9017</t>
+          <t xml:space="preserve">9025</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B167">
         <is>
-          <t xml:space="preserve">True Value Company, L.L.C.</t>
+          <t xml:space="preserve">Hillsboro Client Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C167">
         <is>
-          <t xml:space="preserve">Springfield</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D167">
-        <v>45640</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E167">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c s="9" t="inlineStr" r="F167">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G167">
-        <v>45580</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="168" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A168">
         <is>
-          <t xml:space="preserve">9016</t>
+          <t xml:space="preserve">9017</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B168">
         <is>
-          <t xml:space="preserve">Misfits Markets, Inc. </t>
+          <t xml:space="preserve">True Value Company, L.L.C.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C168">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Springfield</t>
         </is>
       </c>
       <c s="10" r="D168">
-        <v>45657</v>
+        <v>45640</v>
       </c>
       <c s="11" r="E168">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c s="9" t="inlineStr" r="F168">
         <is>
@@ -5494,100 +5494,100 @@
         </is>
       </c>
       <c s="12" r="G168">
-        <v>45595</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="169" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A169">
         <is>
-          <t xml:space="preserve">8987</t>
+          <t xml:space="preserve">9016</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B169">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Misfits Markets, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C169">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D169">
-        <v>45584</v>
+        <v>45657</v>
       </c>
       <c s="11" r="E169">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c s="9" t="inlineStr" r="F169">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G169">
-        <v>45584</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="170" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A170">
         <is>
-          <t xml:space="preserve">8985</t>
+          <t xml:space="preserve">8987</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B170">
         <is>
-          <t xml:space="preserve">Portland - Production and Maintenance P</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C170">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D170">
-        <v>45664</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E170">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c s="9" t="inlineStr" r="F170">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G170">
-        <v>45582</v>
+        <v>45584</v>
       </c>
     </row>
     <row r="171" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A171">
         <is>
-          <t xml:space="preserve">8978</t>
+          <t xml:space="preserve">8985</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B171">
         <is>
-          <t xml:space="preserve">Aloha Facility</t>
+          <t xml:space="preserve">Portland - Production and Maintenance P</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C171">
         <is>
-          <t xml:space="preserve">Aloha</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D171">
-        <v>45611</v>
+        <v>45664</v>
       </c>
       <c s="11" r="E171">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c s="9" t="inlineStr" r="F171">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G171">
-        <v>45580</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="172" ht="18" customHeight="0">
@@ -5598,19 +5598,19 @@
       </c>
       <c s="9" t="inlineStr" r="B172">
         <is>
-          <t xml:space="preserve">Century Blvd., Hillsboro</t>
+          <t xml:space="preserve">Aloha Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C172">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Aloha</t>
         </is>
       </c>
       <c s="10" r="D172">
         <v>45611</v>
       </c>
       <c s="11" r="E172">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c s="9" t="inlineStr" r="F172">
         <is>
@@ -5629,7 +5629,7 @@
       </c>
       <c s="9" t="inlineStr" r="B173">
         <is>
-          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
+          <t xml:space="preserve">Century Blvd., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C173">
@@ -5641,7 +5641,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E173">
-        <v>124</v>
+        <v>514</v>
       </c>
       <c s="9" t="inlineStr" r="F173">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c s="9" t="inlineStr" r="B174">
         <is>
-          <t xml:space="preserve">25th Ave., Hillsboro</t>
+          <t xml:space="preserve">Elam Young Pkwy., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C174">
@@ -5672,7 +5672,7 @@
         <v>45611</v>
       </c>
       <c s="11" r="E174">
-        <v>634</v>
+        <v>124</v>
       </c>
       <c s="9" t="inlineStr" r="F174">
         <is>
@@ -5686,28 +5686,28 @@
     <row r="175" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A175">
         <is>
-          <t xml:space="preserve">8977</t>
+          <t xml:space="preserve">8978</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B175">
         <is>
-          <t xml:space="preserve">Cornerstone Building Brands</t>
+          <t xml:space="preserve">25th Ave., Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C175">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D175">
-        <v>45646</v>
+        <v>45611</v>
       </c>
       <c s="11" r="E175">
-        <v>76</v>
+        <v>634</v>
       </c>
       <c s="9" t="inlineStr" r="F175">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G175">
@@ -5717,24 +5717,24 @@
     <row r="176" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A176">
         <is>
-          <t xml:space="preserve">8956</t>
+          <t xml:space="preserve">8977</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B176">
         <is>
-          <t xml:space="preserve">Hillsboro Worksite</t>
+          <t xml:space="preserve">Cornerstone Building Brands</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C176">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D176">
-        <v>45621</v>
+        <v>45646</v>
       </c>
       <c s="11" r="E176">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F176">
         <is>
@@ -5742,38 +5742,38 @@
         </is>
       </c>
       <c s="12" r="G176">
-        <v>45561</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="177" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A177">
         <is>
-          <t xml:space="preserve">8937</t>
+          <t xml:space="preserve">8956</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B177">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
+          <t xml:space="preserve">Hillsboro Worksite</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C177">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D177">
-        <v>45544</v>
+        <v>45621</v>
       </c>
       <c s="11" r="E177">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F177">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G177">
-        <v>45541</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="178" ht="18" customHeight="0">
@@ -5784,23 +5784,23 @@
       </c>
       <c s="9" t="inlineStr" r="B178">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C178">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D178">
         <v>45544</v>
       </c>
       <c s="11" r="E178">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c s="9" t="inlineStr" r="F178">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G178">
@@ -5810,55 +5810,55 @@
     <row r="179" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A179">
         <is>
-          <t xml:space="preserve">8911</t>
+          <t xml:space="preserve">8937</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B179">
         <is>
-          <t xml:space="preserve">Willamette Falls Paper Company</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C179">
         <is>
-          <t xml:space="preserve">West Linn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D179">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c s="11" r="E179">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F179">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G179">
-        <v>45510</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="180" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A180">
         <is>
-          <t xml:space="preserve">8892</t>
+          <t xml:space="preserve">8911</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B180">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Willamette Falls Paper Company</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C180">
         <is>
-          <t xml:space="preserve">Hillsboro, </t>
+          <t xml:space="preserve">West Linn</t>
         </is>
       </c>
       <c s="10" r="D180">
-        <v>45654</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E180">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F180">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c s="12" r="G180">
-        <v>45496</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="181" ht="18" customHeight="0">
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c s="10" r="D181">
-        <v>45612</v>
+        <v>45654</v>
       </c>
       <c s="11" r="E181">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F181">
         <is>
@@ -5917,14 +5917,14 @@
         </is>
       </c>
       <c s="10" r="D182">
-        <v>45584</v>
+        <v>45612</v>
       </c>
       <c s="11" r="E182">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F182">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G182">
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c s="10" r="D183">
-        <v>45569</v>
+        <v>45584</v>
       </c>
       <c s="11" r="E183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F183">
         <is>
@@ -5979,14 +5979,14 @@
         </is>
       </c>
       <c s="10" r="D184">
-        <v>45555</v>
+        <v>45569</v>
       </c>
       <c s="11" r="E184">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F184">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G184">
@@ -5996,24 +5996,24 @@
     <row r="185" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A185">
         <is>
-          <t xml:space="preserve">8880</t>
+          <t xml:space="preserve">8892</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B185">
         <is>
-          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C185">
         <is>
-          <t xml:space="preserve">Aurora</t>
+          <t xml:space="preserve">Hillsboro, </t>
         </is>
       </c>
       <c s="10" r="D185">
-        <v>45653</v>
+        <v>45555</v>
       </c>
       <c s="11" r="E185">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F185">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c s="12" r="G185">
-        <v>45475</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="186" ht="18" customHeight="0">
@@ -6041,14 +6041,14 @@
         </is>
       </c>
       <c s="10" r="D186">
-        <v>45505</v>
+        <v>45653</v>
       </c>
       <c s="11" r="E186">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F186">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G186">
@@ -6058,24 +6058,24 @@
     <row r="187" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A187">
         <is>
-          <t xml:space="preserve">8876</t>
+          <t xml:space="preserve">8880</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B187">
         <is>
-          <t xml:space="preserve">OHSU</t>
+          <t xml:space="preserve">Hazelnut Growers of Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C187">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Aurora</t>
         </is>
       </c>
       <c s="10" r="D187">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c s="11" r="E187">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c s="9" t="inlineStr" r="F187">
         <is>
@@ -6083,13 +6083,13 @@
         </is>
       </c>
       <c s="12" r="G187">
-        <v>45474</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="188" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A188">
         <is>
-          <t xml:space="preserve">8859</t>
+          <t xml:space="preserve">8876</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B188">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c s="10" r="D188">
-        <v>45513</v>
+        <v>45534</v>
       </c>
       <c s="11" r="E188">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c s="9" t="inlineStr" r="F188">
         <is>
@@ -6114,18 +6114,18 @@
         </is>
       </c>
       <c s="12" r="G188">
-        <v>45450</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="189" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A189">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8859</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B189">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">OHSU</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C189">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c s="10" r="D189">
-        <v>45504</v>
+        <v>45513</v>
       </c>
       <c s="11" r="E189">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c s="9" t="inlineStr" r="F189">
         <is>
@@ -6145,30 +6145,30 @@
         </is>
       </c>
       <c s="12" r="G189">
-        <v>45441</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="190" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A190">
         <is>
-          <t xml:space="preserve">8847</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B190">
         <is>
-          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C190">
         <is>
-          <t xml:space="preserve">Tualatin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D190">
-        <v>46229</v>
+        <v>45504</v>
       </c>
       <c s="11" r="E190">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F190">
         <is>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c s="12" r="G190">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="191" ht="18" customHeight="0">
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c s="10" r="D191">
-        <v>45688</v>
+        <v>46229</v>
       </c>
       <c s="11" r="E191">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c s="9" t="inlineStr" r="F191">
         <is>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c s="10" r="D192">
-        <v>45506</v>
+        <v>45688</v>
       </c>
       <c s="11" r="E192">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F192">
         <is>
@@ -6244,32 +6244,32 @@
     <row r="193" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A193">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8847</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B193">
         <is>
-          <t xml:space="preserve">Lignetics</t>
+          <t xml:space="preserve">Campbell Soup Supply Company, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C193">
         <is>
-          <t xml:space="preserve">Cascade Locks</t>
+          <t xml:space="preserve">Tualatin</t>
         </is>
       </c>
       <c s="10" r="D193">
-        <v>45483</v>
+        <v>45506</v>
       </c>
       <c s="11" r="E193">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c s="9" t="inlineStr" r="F193">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G193">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="194" ht="18" customHeight="0">
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c s="10" r="D194">
-        <v>45401</v>
+        <v>45483</v>
       </c>
       <c s="11" r="E194">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F194">
         <is>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c s="10" r="D195">
-        <v>45366</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F195">
         <is>
@@ -6337,43 +6337,43 @@
     <row r="196" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A196">
         <is>
-          <t xml:space="preserve">8817</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B196">
         <is>
-          <t xml:space="preserve">Multnomah University</t>
+          <t xml:space="preserve">Lignetics</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C196">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Cascade Locks</t>
         </is>
       </c>
       <c s="10" r="D196">
-        <v>45473</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E196">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F196">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G196">
-        <v>45419</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="197" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A197">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8817</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B197">
         <is>
-          <t xml:space="preserve">Portland Manufacturing Site</t>
+          <t xml:space="preserve">Multnomah University</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C197">
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c s="10" r="D197">
-        <v>45471</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E197">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F197">
         <is>
@@ -6393,111 +6393,111 @@
         </is>
       </c>
       <c s="12" r="G197">
-        <v>45404</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="198" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A198">
         <is>
-          <t xml:space="preserve">8794</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B198">
         <is>
-          <t xml:space="preserve">NIKE, Inc.</t>
+          <t xml:space="preserve">Portland Manufacturing Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C198">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D198">
         <v>45471</v>
       </c>
       <c s="11" r="E198">
-        <v>740</v>
+        <v>75</v>
       </c>
       <c s="9" t="inlineStr" r="F198">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G198">
-        <v>45401</v>
+        <v>45404</v>
       </c>
     </row>
     <row r="199" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A199">
         <is>
-          <t xml:space="preserve">8782</t>
+          <t xml:space="preserve">8794</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">Block, Inc.</t>
+          <t xml:space="preserve">NIKE, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">Oakland, CA</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D199">
-        <v>45446</v>
+        <v>45471</v>
       </c>
       <c s="11" r="E199">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c s="9" t="inlineStr" r="F199">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G199">
-        <v>45384</v>
+        <v>45401</v>
       </c>
     </row>
     <row r="200" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A200">
         <is>
-          <t xml:space="preserve">8781</t>
+          <t xml:space="preserve">8782</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">Volta Charging Industries, LLC</t>
+          <t xml:space="preserve">Block, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Oakland, CA</t>
         </is>
       </c>
       <c s="10" r="D200">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c s="11" r="E200">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c s="9" t="inlineStr" r="F200">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G200">
-        <v>45380</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="201" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A201">
         <is>
-          <t xml:space="preserve">8776</t>
+          <t xml:space="preserve">8781</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">Osso VR, Inc.</t>
+          <t xml:space="preserve">Volta Charging Industries, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C201">
@@ -6506,134 +6506,134 @@
         </is>
       </c>
       <c s="10" r="D201">
-        <v>45439</v>
+        <v>45443</v>
       </c>
       <c s="11" r="E201">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F201">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G201">
-        <v>45379</v>
+        <v>45380</v>
       </c>
     </row>
     <row r="202" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A202">
         <is>
-          <t xml:space="preserve">8773</t>
+          <t xml:space="preserve">8776</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">Bionano Genomics, Inc.</t>
+          <t xml:space="preserve">Osso VR, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">San Diego, CA</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D202">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c s="11" r="E202">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F202">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G202">
-        <v>45372</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="203" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A203">
         <is>
-          <t xml:space="preserve">8769</t>
+          <t xml:space="preserve">8773</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
+          <t xml:space="preserve">Bionano Genomics, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">Newport</t>
+          <t xml:space="preserve">San Diego, CA</t>
         </is>
       </c>
       <c s="10" r="D203">
-        <v>45433</v>
+        <v>45436</v>
       </c>
       <c s="11" r="E203">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c s="9" t="inlineStr" r="F203">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G203">
-        <v>45373</v>
+        <v>45372</v>
       </c>
     </row>
     <row r="204" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A204">
         <is>
-          <t xml:space="preserve">8760</t>
+          <t xml:space="preserve">8769</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">Adventist Health of Tillamook</t>
+          <t xml:space="preserve">Bornstein Seafoods, Inc - Newport Facil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">Tillamook</t>
+          <t xml:space="preserve">Newport</t>
         </is>
       </c>
       <c s="10" r="D204">
-        <v>45417</v>
+        <v>45433</v>
       </c>
       <c s="11" r="E204">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F204">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G204">
-        <v>45358</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="205" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A205">
         <is>
-          <t xml:space="preserve">8759</t>
+          <t xml:space="preserve">8760</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">Wieden + Kennedy</t>
+          <t xml:space="preserve">Adventist Health of Tillamook</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Tillamook</t>
         </is>
       </c>
       <c s="10" r="D205">
-        <v>45352</v>
+        <v>45417</v>
       </c>
       <c s="11" r="E205">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c s="9" t="inlineStr" r="F205">
         <is>
@@ -6641,18 +6641,18 @@
         </is>
       </c>
       <c s="12" r="G205">
-        <v>45345</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="206" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A206">
         <is>
-          <t xml:space="preserve">8747</t>
+          <t xml:space="preserve">8759</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">Portland Day Sort</t>
+          <t xml:space="preserve">Wieden + Kennedy</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C206">
@@ -6661,41 +6661,41 @@
         </is>
       </c>
       <c s="10" r="D206">
-        <v>45401</v>
+        <v>45352</v>
       </c>
       <c s="11" r="E206">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c s="9" t="inlineStr" r="F206">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G206">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="207" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A207">
         <is>
-          <t xml:space="preserve">8742</t>
+          <t xml:space="preserve">8747</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">Interfor U.S. Inc</t>
+          <t xml:space="preserve">Portland Day Sort</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C207">
         <is>
-          <t xml:space="preserve">Philomath</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D207">
-        <v>45337</v>
+        <v>45401</v>
       </c>
       <c s="11" r="E207">
-        <v>42</v>
+        <v>350</v>
       </c>
       <c s="9" t="inlineStr" r="F207">
         <is>
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c s="12" r="G207">
-        <v>45337</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="208" ht="18" customHeight="0">
@@ -6714,7 +6714,7 @@
       </c>
       <c s="9" t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
+          <t xml:space="preserve">Interfor U.S. Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C208">
@@ -6726,7 +6726,7 @@
         <v>45337</v>
       </c>
       <c s="11" r="E208">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c s="9" t="inlineStr" r="F208">
         <is>
@@ -6740,24 +6740,24 @@
     <row r="209" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A209">
         <is>
-          <t xml:space="preserve">8725</t>
+          <t xml:space="preserve">8742</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">Remote Workers - Oregon</t>
+          <t xml:space="preserve">Philomath Division - Industrial Way Mil</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Philomath</t>
         </is>
       </c>
       <c s="10" r="D209">
-        <v>45381</v>
+        <v>45337</v>
       </c>
       <c s="11" r="E209">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F209">
         <is>
@@ -6765,34 +6765,34 @@
         </is>
       </c>
       <c s="12" r="G209">
-        <v>45321</v>
+        <v>45337</v>
       </c>
     </row>
     <row r="210" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A210">
         <is>
-          <t xml:space="preserve">8723</t>
+          <t xml:space="preserve">8725</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">RNDC - Portland Location</t>
+          <t xml:space="preserve">Remote Workers - Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D210">
-        <v>45382</v>
+        <v>45381</v>
       </c>
       <c s="11" r="E210">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F210">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G210">
@@ -6807,19 +6807,19 @@
       </c>
       <c s="9" t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">RNDC - Bend Location</t>
+          <t xml:space="preserve">RNDC - Portland Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">Bend</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D211">
         <v>45382</v>
       </c>
       <c s="11" r="E211">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F211">
         <is>
@@ -6838,19 +6838,19 @@
       </c>
       <c s="9" t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #1</t>
+          <t xml:space="preserve">RNDC - Bend Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Bend</t>
         </is>
       </c>
       <c s="10" r="D212">
         <v>45382</v>
       </c>
       <c s="11" r="E212">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F212">
         <is>
@@ -6869,7 +6869,7 @@
       </c>
       <c s="9" t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">RNDC - Medford Location #2</t>
+          <t xml:space="preserve">RNDC - Medford Location #1</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C213">
@@ -6881,7 +6881,7 @@
         <v>45382</v>
       </c>
       <c s="11" r="E213">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F213">
         <is>
@@ -6900,12 +6900,12 @@
       </c>
       <c s="9" t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">RNDC - Eugene Location</t>
+          <t xml:space="preserve">RNDC - Medford Location #2</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D214">
@@ -6926,32 +6926,32 @@
     <row r="215" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A215">
         <is>
-          <t xml:space="preserve">8708</t>
+          <t xml:space="preserve">8723</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
+          <t xml:space="preserve">RNDC - Eugene Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">Madison, WI</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D215">
-        <v>45366</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E215">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F215">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G215">
-        <v>45302</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="216" ht="18" customHeight="0">
@@ -6962,23 +6962,23 @@
       </c>
       <c s="9" t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">Oregon - Remote Employees</t>
+          <t xml:space="preserve">Lost Boys Interactive, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Madison, WI</t>
         </is>
       </c>
       <c s="10" r="D216">
         <v>45366</v>
       </c>
       <c s="11" r="E216">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c s="9" t="inlineStr" r="F216">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G216">
@@ -6988,55 +6988,55 @@
     <row r="217" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A217">
         <is>
-          <t xml:space="preserve">8671</t>
+          <t xml:space="preserve">8708</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">Portland - Site</t>
+          <t xml:space="preserve">Oregon - Remote Employees</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C217">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c s="10" r="D217">
-        <v>45322</v>
+        <v>45366</v>
       </c>
       <c s="11" r="E217">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c s="9" t="inlineStr" r="F217">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G217">
-        <v>45261</v>
+        <v>45302</v>
       </c>
     </row>
     <row r="218" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A218">
         <is>
-          <t xml:space="preserve">8652</t>
+          <t xml:space="preserve">8671</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">Yelloh -  Central Point</t>
+          <t xml:space="preserve">Portland - Site</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">Central Point</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D218">
-        <v>45275</v>
+        <v>45322</v>
       </c>
       <c s="11" r="E218">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F218">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c s="12" r="G218">
-        <v>45224</v>
+        <v>45261</v>
       </c>
     </row>
     <row r="219" ht="18" customHeight="0">
@@ -7055,19 +7055,19 @@
       </c>
       <c s="9" t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">Yelloh - Eugene</t>
+          <t xml:space="preserve">Yelloh -  Central Point</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">Eugen</t>
+          <t xml:space="preserve">Central Point</t>
         </is>
       </c>
       <c s="10" r="D219">
         <v>45275</v>
       </c>
       <c s="11" r="E219">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F219">
         <is>
@@ -7086,19 +7086,19 @@
       </c>
       <c s="9" t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">Yelloh - Salem</t>
+          <t xml:space="preserve">Yelloh - Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">Salem</t>
+          <t xml:space="preserve">Eugen</t>
         </is>
       </c>
       <c s="10" r="D220">
         <v>45275</v>
       </c>
       <c s="11" r="E220">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c s="9" t="inlineStr" r="F220">
         <is>
@@ -7117,19 +7117,19 @@
       </c>
       <c s="9" t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">Yelloh - Tualitin</t>
+          <t xml:space="preserve">Yelloh - Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">Tualitin</t>
+          <t xml:space="preserve">Salem</t>
         </is>
       </c>
       <c s="10" r="D221">
         <v>45275</v>
       </c>
       <c s="11" r="E221">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F221">
         <is>
@@ -7143,24 +7143,24 @@
     <row r="222" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A222">
         <is>
-          <t xml:space="preserve">8648</t>
+          <t xml:space="preserve">8652</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">Peace Health</t>
+          <t xml:space="preserve">Yelloh - Tualitin</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Tualitin</t>
         </is>
       </c>
       <c s="10" r="D222">
-        <v>45280</v>
+        <v>45275</v>
       </c>
       <c s="11" r="E222">
-        <v>463</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F222">
         <is>
@@ -7168,30 +7168,30 @@
         </is>
       </c>
       <c s="12" r="G222">
-        <v>45218</v>
+        <v>45224</v>
       </c>
     </row>
     <row r="223" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A223">
         <is>
-          <t xml:space="preserve">8647</t>
+          <t xml:space="preserve">8648</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">Wilsonville Distribution Center</t>
+          <t xml:space="preserve">Peace Health</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">Wilsonville</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D223">
-        <v>45294</v>
+        <v>45280</v>
       </c>
       <c s="11" r="E223">
-        <v>136</v>
+        <v>463</v>
       </c>
       <c s="9" t="inlineStr" r="F223">
         <is>
@@ -7199,30 +7199,30 @@
         </is>
       </c>
       <c s="12" r="G223">
-        <v>45217</v>
+        <v>45218</v>
       </c>
     </row>
     <row r="224" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A224">
         <is>
-          <t xml:space="preserve">8637</t>
+          <t xml:space="preserve">8647</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">Grace </t>
+          <t xml:space="preserve">Wilsonville Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">Albany</t>
+          <t xml:space="preserve">Wilsonville</t>
         </is>
       </c>
       <c s="10" r="D224">
-        <v>45473</v>
+        <v>45294</v>
       </c>
       <c s="11" r="E224">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c s="9" t="inlineStr" r="F224">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c s="12" r="G224">
-        <v>45200</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="225" ht="18" customHeight="0">
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c s="10" r="D225">
-        <v>45382</v>
+        <v>45473</v>
       </c>
       <c s="11" r="E225">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F225">
         <is>
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c s="10" r="D226">
-        <v>45291</v>
+        <v>45382</v>
       </c>
       <c s="11" r="E226">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c s="9" t="inlineStr" r="F226">
         <is>
@@ -7298,24 +7298,24 @@
     <row r="227" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A227">
         <is>
-          <t xml:space="preserve">8634</t>
+          <t xml:space="preserve">8637</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">T3281 Store</t>
+          <t xml:space="preserve">Grace </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C227">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Albany</t>
         </is>
       </c>
       <c s="10" r="D227">
-        <v>45290</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E227">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c s="9" t="inlineStr" r="F227">
         <is>
@@ -7323,18 +7323,18 @@
         </is>
       </c>
       <c s="12" r="G227">
-        <v>45195</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="228" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A228">
         <is>
-          <t xml:space="preserve">8633</t>
+          <t xml:space="preserve">8634</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">T3358 Store</t>
+          <t xml:space="preserve">T3281 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C228">
@@ -7346,7 +7346,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E228">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F228">
         <is>
@@ -7360,12 +7360,12 @@
     <row r="229" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A229">
         <is>
-          <t xml:space="preserve">8632</t>
+          <t xml:space="preserve">8633</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">T3381 Store</t>
+          <t xml:space="preserve">T3358 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C229">
@@ -7377,7 +7377,7 @@
         <v>45290</v>
       </c>
       <c s="11" r="E229">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F229">
         <is>
@@ -7391,24 +7391,24 @@
     <row r="230" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A230">
         <is>
-          <t xml:space="preserve">8627</t>
+          <t xml:space="preserve">8632</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">American Nursery Services, Inc. </t>
+          <t xml:space="preserve">T3381 Store</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">Newberg</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D230">
-        <v>45291</v>
+        <v>45290</v>
       </c>
       <c s="11" r="E230">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F230">
         <is>
@@ -7416,61 +7416,61 @@
         </is>
       </c>
       <c s="12" r="G230">
-        <v>45174</v>
+        <v>45195</v>
       </c>
     </row>
     <row r="231" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A231">
         <is>
-          <t xml:space="preserve">8622</t>
+          <t xml:space="preserve">8627</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">Divvy Homes, Inc</t>
+          <t xml:space="preserve">American Nursery Services, Inc. </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">San Francisco, CA</t>
+          <t xml:space="preserve">Newberg</t>
         </is>
       </c>
       <c s="10" r="D231">
-        <v>45237</v>
+        <v>45291</v>
       </c>
       <c s="11" r="E231">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c s="9" t="inlineStr" r="F231">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G231">
-        <v>45176</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="232" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A232">
         <is>
-          <t xml:space="preserve">8617</t>
+          <t xml:space="preserve">8622</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Divvy Homes, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">San Francisco, CA</t>
         </is>
       </c>
       <c s="10" r="D232">
-        <v>45387</v>
+        <v>45237</v>
       </c>
       <c s="11" r="E232">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c s="9" t="inlineStr" r="F232">
         <is>
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c s="12" r="G232">
-        <v>45160</v>
+        <v>45176</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="0">
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c s="10" r="D233">
-        <v>45317</v>
+        <v>45387</v>
       </c>
       <c s="11" r="E233">
         <v>2</v>
@@ -7529,14 +7529,14 @@
         </is>
       </c>
       <c s="10" r="D234">
-        <v>45303</v>
+        <v>45317</v>
       </c>
       <c s="11" r="E234">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F234">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G234">
@@ -7551,7 +7551,7 @@
       </c>
       <c s="9" t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C235">
@@ -7563,11 +7563,11 @@
         <v>45303</v>
       </c>
       <c s="11" r="E235">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F235">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G235">
@@ -7582,7 +7582,7 @@
       </c>
       <c s="9" t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C236">
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c s="10" r="D236">
-        <v>45289</v>
+        <v>45303</v>
       </c>
       <c s="11" r="E236">
         <v>3</v>
@@ -7613,7 +7613,7 @@
       </c>
       <c s="9" t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C237">
@@ -7625,7 +7625,7 @@
         <v>45289</v>
       </c>
       <c s="11" r="E237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F237">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c s="9" t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C238">
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c s="10" r="D238">
-        <v>45261</v>
+        <v>45289</v>
       </c>
       <c s="11" r="E238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c s="9" t="inlineStr" r="F238">
         <is>
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c s="10" r="D239">
-        <v>45247</v>
+        <v>45261</v>
       </c>
       <c s="11" r="E239">
         <v>1</v>
@@ -7706,7 +7706,7 @@
       </c>
       <c s="9" t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">Bennett St. - Hillsboro</t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C240">
@@ -7715,14 +7715,14 @@
         </is>
       </c>
       <c s="10" r="D240">
-        <v>45219</v>
+        <v>45247</v>
       </c>
       <c s="11" r="E240">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F240">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G240">
@@ -7737,7 +7737,7 @@
       </c>
       <c s="9" t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">Walker Rd - Hillsboro</t>
+          <t xml:space="preserve">Bennett St. - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C241">
@@ -7749,7 +7749,7 @@
         <v>45219</v>
       </c>
       <c s="11" r="E241">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F241">
         <is>
@@ -7763,86 +7763,86 @@
     <row r="242" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A242">
         <is>
-          <t xml:space="preserve">8612</t>
+          <t xml:space="preserve">8617</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Walker Rd - Hillsboro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D242">
-        <v>45213</v>
+        <v>45219</v>
       </c>
       <c s="11" r="E242">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c s="9" t="inlineStr" r="F242">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G242">
-        <v>45154</v>
+        <v>45160</v>
       </c>
     </row>
     <row r="243" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A243">
         <is>
-          <t xml:space="preserve">8609</t>
+          <t xml:space="preserve">8612</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B243">
         <is>
-          <t xml:space="preserve">Centerra </t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C243">
         <is>
-          <t xml:space="preserve">Herndon, VA</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="10" r="D243">
-        <v>45199</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E243">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F243">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G243">
-        <v>45148</v>
+        <v>45154</v>
       </c>
     </row>
     <row r="244" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A244">
         <is>
-          <t xml:space="preserve">8606</t>
+          <t xml:space="preserve">8609</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B244">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Centerra </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C244">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Herndon, VA</t>
         </is>
       </c>
       <c s="10" r="D244">
-        <v>45213</v>
+        <v>45199</v>
       </c>
       <c s="11" r="E244">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c s="9" t="inlineStr" r="F244">
         <is>
@@ -7856,24 +7856,24 @@
     <row r="245" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A245">
         <is>
-          <t xml:space="preserve">8603</t>
+          <t xml:space="preserve">8606</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B245">
         <is>
-          <t xml:space="preserve">Medford Plant</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C245">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D245">
-        <v>45283</v>
+        <v>45213</v>
       </c>
       <c s="11" r="E245">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F245">
         <is>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c s="12" r="G245">
-        <v>45135</v>
+        <v>45148</v>
       </c>
     </row>
     <row r="246" ht="18" customHeight="0">
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c s="10" r="D246">
-        <v>45192</v>
+        <v>45283</v>
       </c>
       <c s="11" r="E246">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c s="9" t="inlineStr" r="F246">
         <is>
@@ -7918,24 +7918,24 @@
     <row r="247" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A247">
         <is>
-          <t xml:space="preserve">8598</t>
+          <t xml:space="preserve">8603</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B247">
         <is>
-          <t xml:space="preserve">Roseburg-509</t>
+          <t xml:space="preserve">Medford Plant</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C247">
         <is>
-          <t xml:space="preserve">Roseburg</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D247">
-        <v>45137</v>
+        <v>45192</v>
       </c>
       <c s="11" r="E247">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c s="9" t="inlineStr" r="F247">
         <is>
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c s="12" r="G247">
-        <v>45137</v>
+        <v>45135</v>
       </c>
     </row>
     <row r="248" ht="18" customHeight="0">
@@ -7954,19 +7954,19 @@
       </c>
       <c s="9" t="inlineStr" r="B248">
         <is>
-          <t xml:space="preserve">Eugene-506</t>
+          <t xml:space="preserve">Roseburg-509</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C248">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Roseburg</t>
         </is>
       </c>
       <c s="10" r="D248">
-        <v>45107</v>
+        <v>45137</v>
       </c>
       <c s="11" r="E248">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c s="9" t="inlineStr" r="F248">
         <is>
@@ -7980,32 +7980,32 @@
     <row r="249" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A249">
         <is>
-          <t xml:space="preserve">8596</t>
+          <t xml:space="preserve">8598</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B249">
         <is>
-          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
+          <t xml:space="preserve">Eugene-506</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C249">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D249">
-        <v>45233</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E249">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c s="9" t="inlineStr" r="F249">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G249">
-        <v>45138</v>
+        <v>45137</v>
       </c>
     </row>
     <row r="250" ht="18" customHeight="0">
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c s="10" r="D250">
-        <v>45205</v>
+        <v>45233</v>
       </c>
       <c s="11" r="E250">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c s="9" t="inlineStr" r="F250">
         <is>
@@ -8042,24 +8042,24 @@
     <row r="251" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A251">
         <is>
-          <t xml:space="preserve">8583</t>
+          <t xml:space="preserve">8596</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B251">
         <is>
-          <t xml:space="preserve">PBS West, LLC</t>
+          <t xml:space="preserve">DC-25 Portland Distribution Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C251">
         <is>
-          <t xml:space="preserve">Corvallis</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D251">
-        <v>45175</v>
+        <v>45205</v>
       </c>
       <c s="11" r="E251">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c s="9" t="inlineStr" r="F251">
         <is>
@@ -8067,30 +8067,30 @@
         </is>
       </c>
       <c s="12" r="G251">
-        <v>45114</v>
+        <v>45138</v>
       </c>
     </row>
     <row r="252" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A252">
         <is>
-          <t xml:space="preserve">8578</t>
+          <t xml:space="preserve">8583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B252">
         <is>
-          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
+          <t xml:space="preserve">PBS West, LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C252">
         <is>
-          <t xml:space="preserve">Jacksonville</t>
+          <t xml:space="preserve">Corvallis</t>
         </is>
       </c>
       <c s="10" r="D252">
-        <v>45091</v>
+        <v>45175</v>
       </c>
       <c s="11" r="E252">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c s="9" t="inlineStr" r="F252">
         <is>
@@ -8098,123 +8098,123 @@
         </is>
       </c>
       <c s="12" r="G252">
-        <v>45091</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A253">
         <is>
-          <t xml:space="preserve">8577</t>
+          <t xml:space="preserve">8578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B253">
         <is>
-          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
+          <t xml:space="preserve">Jacksonville, Remote Employee Location</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C253">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Jacksonville</t>
         </is>
       </c>
       <c s="10" r="D253">
-        <v>45128</v>
+        <v>45091</v>
       </c>
       <c s="11" r="E253">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F253">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G253">
-        <v>45090</v>
+        <v>45091</v>
       </c>
     </row>
     <row r="254" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A254">
         <is>
-          <t xml:space="preserve">8574</t>
+          <t xml:space="preserve">8577</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B254">
         <is>
-          <t xml:space="preserve">Marquis Spas</t>
+          <t xml:space="preserve">Owens-Brockway Glass Container Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C254">
         <is>
-          <t xml:space="preserve">Independence</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D254">
-        <v>45170</v>
+        <v>45128</v>
       </c>
       <c s="11" r="E254">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c s="9" t="inlineStr" r="F254">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G254">
-        <v>45085</v>
+        <v>45090</v>
       </c>
     </row>
     <row r="255" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A255">
         <is>
-          <t xml:space="preserve">8572</t>
+          <t xml:space="preserve">8574</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B255">
         <is>
-          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
+          <t xml:space="preserve">Marquis Spas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C255">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Independence</t>
         </is>
       </c>
       <c s="10" r="D255">
-        <v>45106</v>
+        <v>45170</v>
       </c>
       <c s="11" r="E255">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c s="9" t="inlineStr" r="F255">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G255">
-        <v>45083</v>
+        <v>45085</v>
       </c>
     </row>
     <row r="256" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A256">
         <is>
-          <t xml:space="preserve">8563</t>
+          <t xml:space="preserve">8572</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B256">
         <is>
-          <t xml:space="preserve">Aspiration Partners</t>
+          <t xml:space="preserve">Aimbridge Employee Service Corp AKA Val</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C256">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D256">
-        <v>45107</v>
+        <v>45106</v>
       </c>
       <c s="11" r="E256">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c s="9" t="inlineStr" r="F256">
         <is>
@@ -8222,30 +8222,30 @@
         </is>
       </c>
       <c s="12" r="G256">
-        <v>45070</v>
+        <v>45083</v>
       </c>
     </row>
     <row r="257" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A257">
         <is>
-          <t xml:space="preserve">8556</t>
+          <t xml:space="preserve">8563</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B257">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
+          <t xml:space="preserve">Aspiration Partners</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C257">
         <is>
-          <t xml:space="preserve">St. Helens</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D257">
-        <v>45115</v>
+        <v>45107</v>
       </c>
       <c s="11" r="E257">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c s="9" t="inlineStr" r="F257">
         <is>
@@ -8253,61 +8253,61 @@
         </is>
       </c>
       <c s="12" r="G257">
-        <v>45055</v>
+        <v>45070</v>
       </c>
     </row>
     <row r="258" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A258">
         <is>
-          <t xml:space="preserve">8551</t>
+          <t xml:space="preserve">8556</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B258">
         <is>
-          <t xml:space="preserve">Makita U.S.A., Inc.</t>
+          <t xml:space="preserve">Cascades Tissue Group - St Helens Paper</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C258">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">St. Helens</t>
         </is>
       </c>
       <c s="10" r="D258">
-        <v>45105</v>
+        <v>45115</v>
       </c>
       <c s="11" r="E258">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c s="9" t="inlineStr" r="F258">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G258">
-        <v>45044</v>
+        <v>45055</v>
       </c>
     </row>
     <row r="259" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A259">
         <is>
-          <t xml:space="preserve">8545</t>
+          <t xml:space="preserve">8551</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B259">
         <is>
-          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
+          <t xml:space="preserve">Makita U.S.A., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C259">
         <is>
-          <t xml:space="preserve">Scappoose</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D259">
-        <v>45135</v>
+        <v>45105</v>
       </c>
       <c s="11" r="E259">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F259">
         <is>
@@ -8315,30 +8315,30 @@
         </is>
       </c>
       <c s="12" r="G259">
-        <v>45041</v>
+        <v>45044</v>
       </c>
     </row>
     <row r="260" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A260">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8545</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B260">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
+          <t xml:space="preserve">Cascades Tissue Group - Scappoose Conve</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C260">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Scappoose</t>
         </is>
       </c>
       <c s="10" r="D260">
-        <v>45124</v>
+        <v>45135</v>
       </c>
       <c s="11" r="E260">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c s="9" t="inlineStr" r="F260">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c s="12" r="G260">
-        <v>45030</v>
+        <v>45041</v>
       </c>
     </row>
     <row r="261" ht="18" customHeight="0">
@@ -8357,12 +8357,12 @@
       </c>
       <c s="9" t="inlineStr" r="B261">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
+          <t xml:space="preserve">David's Bridal, Store # 160, Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C261">
         <is>
-          <t xml:space="preserve">Happy Valley</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D261">
@@ -8388,12 +8388,12 @@
       </c>
       <c s="9" t="inlineStr" r="B262">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
+          <t xml:space="preserve">David's Bridal, Store # 200, Clackamas</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C262">
         <is>
-          <t xml:space="preserve">Eugene</t>
+          <t xml:space="preserve">Happy Valley</t>
         </is>
       </c>
       <c s="10" r="D262">
@@ -8419,12 +8419,12 @@
       </c>
       <c s="9" t="inlineStr" r="B263">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
+          <t xml:space="preserve">David's Bridal, Store # 216, Eugene</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C263">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Eugene</t>
         </is>
       </c>
       <c s="10" r="D263">
@@ -8450,12 +8450,12 @@
       </c>
       <c s="9" t="inlineStr" r="B264">
         <is>
-          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
+          <t xml:space="preserve">David's Bridal, Store # 263 Medford</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C264">
         <is>
-          <t xml:space="preserve">Keizer</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D264">
@@ -8476,86 +8476,86 @@
     <row r="265" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A265">
         <is>
-          <t xml:space="preserve">8534</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B265">
         <is>
-          <t xml:space="preserve">Aspiration Partners, Inc</t>
+          <t xml:space="preserve">David's Bridal, Store # 292 Salem</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C265">
         <is>
-          <t xml:space="preserve">Marina Del Rey, CA</t>
+          <t xml:space="preserve">Keizer</t>
         </is>
       </c>
       <c s="10" r="D265">
-        <v>45072</v>
+        <v>45124</v>
       </c>
       <c s="11" r="E265">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F265">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G265">
-        <v>45009</v>
+        <v>45030</v>
       </c>
     </row>
     <row r="266" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A266">
         <is>
-          <t xml:space="preserve">8533</t>
+          <t xml:space="preserve">8534</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B266">
         <is>
-          <t xml:space="preserve">Client Facility</t>
+          <t xml:space="preserve">Aspiration Partners, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C266">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Marina Del Rey, CA</t>
         </is>
       </c>
       <c s="10" r="D266">
-        <v>45077</v>
+        <v>45072</v>
       </c>
       <c s="11" r="E266">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F266">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G266">
-        <v>44998</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="267" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A267">
         <is>
-          <t xml:space="preserve">8521</t>
+          <t xml:space="preserve">8533</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B267">
         <is>
-          <t xml:space="preserve">Blount Fine Foods</t>
+          <t xml:space="preserve">Client Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C267">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D267">
-        <v>45058</v>
+        <v>45077</v>
       </c>
       <c s="11" r="E267">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c s="9" t="inlineStr" r="F267">
         <is>
@@ -8569,24 +8569,24 @@
     <row r="268" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A268">
         <is>
-          <t xml:space="preserve">8512</t>
+          <t xml:space="preserve">8521</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B268">
         <is>
-          <t xml:space="preserve">Walmart Store #2552</t>
+          <t xml:space="preserve">Blount Fine Foods</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C268">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D268">
-        <v>45079</v>
+        <v>45058</v>
       </c>
       <c s="11" r="E268">
-        <v>379</v>
+        <v>198</v>
       </c>
       <c s="9" t="inlineStr" r="F268">
         <is>
@@ -8594,30 +8594,30 @@
         </is>
       </c>
       <c s="12" r="G268">
-        <v>44979</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="269" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A269">
         <is>
-          <t xml:space="preserve">8510</t>
+          <t xml:space="preserve">8512</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B269">
         <is>
-          <t xml:space="preserve">Walmart Store #5899 </t>
+          <t xml:space="preserve">Walmart Store #2552</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C269">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D269">
         <v>45079</v>
       </c>
       <c s="11" r="E269">
-        <v>201</v>
+        <v>379</v>
       </c>
       <c s="9" t="inlineStr" r="F269">
         <is>
@@ -8631,12 +8631,12 @@
     <row r="270" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A270">
         <is>
-          <t xml:space="preserve">8482</t>
+          <t xml:space="preserve">8510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B270">
         <is>
-          <t xml:space="preserve">Railcar Manufacturing Operations</t>
+          <t xml:space="preserve">Walmart Store #5899 </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C270">
@@ -8645,103 +8645,103 @@
         </is>
       </c>
       <c s="10" r="D270">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c s="11" r="E270">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c s="9" t="inlineStr" r="F270">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G270">
-        <v>44946</v>
+        <v>44979</v>
       </c>
     </row>
     <row r="271" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A271">
         <is>
-          <t xml:space="preserve">8475</t>
+          <t xml:space="preserve">8482</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B271">
         <is>
-          <t xml:space="preserve">Specialized Bicycle Components</t>
+          <t xml:space="preserve">Railcar Manufacturing Operations</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C271">
         <is>
-          <t xml:space="preserve">Morgan Hill, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D271">
-        <v>44939</v>
+        <v>45006</v>
       </c>
       <c s="11" r="E271">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c s="9" t="inlineStr" r="F271">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G271">
-        <v>44937</v>
+        <v>44946</v>
       </c>
     </row>
     <row r="272" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A272">
         <is>
-          <t xml:space="preserve">8438</t>
+          <t xml:space="preserve">8475</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B272">
         <is>
-          <t xml:space="preserve">BayFirst Financial</t>
+          <t xml:space="preserve">Specialized Bicycle Components</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C272">
         <is>
-          <t xml:space="preserve">St. Petersburg, FL</t>
+          <t xml:space="preserve">Morgan Hill, CA</t>
         </is>
       </c>
       <c s="10" r="D272">
-        <v>44890</v>
+        <v>44939</v>
       </c>
       <c s="11" r="E272">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c s="9" t="inlineStr" r="F272">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G272">
-        <v>44827</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="273" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A273">
         <is>
-          <t xml:space="preserve">8437</t>
+          <t xml:space="preserve">8438</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B273">
         <is>
-          <t xml:space="preserve">Laird Superfood, Inc</t>
+          <t xml:space="preserve">BayFirst Financial</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C273">
         <is>
-          <t xml:space="preserve">Sisters</t>
+          <t xml:space="preserve">St. Petersburg, FL</t>
         </is>
       </c>
       <c s="10" r="D273">
-        <v>44907</v>
+        <v>44890</v>
       </c>
       <c s="11" r="E273">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c s="9" t="inlineStr" r="F273">
         <is>
@@ -8749,30 +8749,30 @@
         </is>
       </c>
       <c s="12" r="G273">
-        <v>44846</v>
+        <v>44827</v>
       </c>
     </row>
     <row r="274" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A274">
         <is>
-          <t xml:space="preserve">8435</t>
+          <t xml:space="preserve">8437</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B274">
         <is>
-          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
+          <t xml:space="preserve">Laird Superfood, Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C274">
         <is>
-          <t xml:space="preserve">Clackamas</t>
+          <t xml:space="preserve">Sisters</t>
         </is>
       </c>
       <c s="10" r="D274">
-        <v>44911</v>
+        <v>44907</v>
       </c>
       <c s="11" r="E274">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c s="9" t="inlineStr" r="F274">
         <is>
@@ -8780,80 +8780,80 @@
         </is>
       </c>
       <c s="12" r="G274">
-        <v>44845</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="275" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A275">
         <is>
-          <t xml:space="preserve">8426</t>
+          <t xml:space="preserve">8435</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B275">
         <is>
-          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
+          <t xml:space="preserve">Beauty Systems Group, LLC, DBA CosmoPro</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C275">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Clackamas</t>
         </is>
       </c>
       <c s="10" r="D275">
-        <v>44869</v>
+        <v>44911</v>
       </c>
       <c s="11" r="E275">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F275">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G275">
-        <v>44812</v>
+        <v>44845</v>
       </c>
     </row>
     <row r="276" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A276">
         <is>
-          <t xml:space="preserve">8424</t>
+          <t xml:space="preserve">8426</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B276">
         <is>
-          <t xml:space="preserve">DENNIS Uniform</t>
+          <t xml:space="preserve">Tegra, DBA Latitudes LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C276">
         <is>
-          <t xml:space="preserve">Portland </t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D276">
-        <v>44866</v>
+        <v>44869</v>
       </c>
       <c s="11" r="E276">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c s="9" t="inlineStr" r="F276">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G276">
-        <v>44803</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="277" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A277">
         <is>
-          <t xml:space="preserve">8417</t>
+          <t xml:space="preserve">8424</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B277">
         <is>
-          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
+          <t xml:space="preserve">DENNIS Uniform</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C277">
@@ -8862,41 +8862,41 @@
         </is>
       </c>
       <c s="10" r="D277">
-        <v>44856</v>
+        <v>44866</v>
       </c>
       <c s="11" r="E277">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c s="9" t="inlineStr" r="F277">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G277">
-        <v>44795</v>
+        <v>44803</v>
       </c>
     </row>
     <row r="278" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A278">
         <is>
-          <t xml:space="preserve">8394</t>
+          <t xml:space="preserve">8417</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B278">
         <is>
-          <t xml:space="preserve">RR Donnelley</t>
+          <t xml:space="preserve">Columbia Steel Casting Co., Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C278">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Portland </t>
         </is>
       </c>
       <c s="10" r="D278">
-        <v>44815</v>
+        <v>44856</v>
       </c>
       <c s="11" r="E278">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c s="9" t="inlineStr" r="F278">
         <is>
@@ -8904,30 +8904,30 @@
         </is>
       </c>
       <c s="12" r="G278">
-        <v>44755</v>
+        <v>44795</v>
       </c>
     </row>
     <row r="279" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A279">
         <is>
-          <t xml:space="preserve">8388</t>
+          <t xml:space="preserve">8394</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B279">
         <is>
-          <t xml:space="preserve">Center for Autism and Related Disorders</t>
+          <t xml:space="preserve">RR Donnelley</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C279">
         <is>
-          <t xml:space="preserve">Plano, TX</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D279">
-        <v>44802</v>
+        <v>44815</v>
       </c>
       <c s="11" r="E279">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c s="9" t="inlineStr" r="F279">
         <is>
@@ -8935,30 +8935,30 @@
         </is>
       </c>
       <c s="12" r="G279">
-        <v>44741</v>
+        <v>44755</v>
       </c>
     </row>
     <row r="280" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A280">
         <is>
-          <t xml:space="preserve">8377</t>
+          <t xml:space="preserve">8388</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B280">
         <is>
-          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
+          <t xml:space="preserve">Center for Autism and Related Disorders</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C280">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Plano, TX</t>
         </is>
       </c>
       <c s="10" r="D280">
-        <v>44865</v>
+        <v>44802</v>
       </c>
       <c s="11" r="E280">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c s="9" t="inlineStr" r="F280">
         <is>
@@ -8966,7 +8966,7 @@
         </is>
       </c>
       <c s="12" r="G280">
-        <v>44699</v>
+        <v>44741</v>
       </c>
     </row>
     <row r="281" ht="18" customHeight="0">
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c s="10" r="D281">
-        <v>44805</v>
+        <v>44865</v>
       </c>
       <c s="11" r="E281">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F281">
         <is>
@@ -9003,74 +9003,74 @@
     <row r="282" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A282">
         <is>
-          <t xml:space="preserve">8356</t>
+          <t xml:space="preserve">8377</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B282">
         <is>
-          <t xml:space="preserve">ARS-Fresno, LLC.</t>
+          <t xml:space="preserve">Dr. Martens Airway USA, LLC - Anchor Pa</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C282">
         <is>
-          <t xml:space="preserve">Carlsbad, CA</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D282">
-        <v>44712</v>
+        <v>44805</v>
       </c>
       <c s="11" r="E282">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F282">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G282">
-        <v>44650</v>
+        <v>44699</v>
       </c>
     </row>
     <row r="283" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A283">
         <is>
-          <t xml:space="preserve">8341</t>
+          <t xml:space="preserve">8356</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B283">
         <is>
-          <t xml:space="preserve">Peloton</t>
+          <t xml:space="preserve">ARS-Fresno, LLC.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C283">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Carlsbad, CA</t>
         </is>
       </c>
       <c s="10" r="D283">
-        <v>44600</v>
+        <v>44712</v>
       </c>
       <c s="11" r="E283">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c s="9" t="inlineStr" r="F283">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G283">
-        <v>44600</v>
+        <v>44650</v>
       </c>
     </row>
     <row r="284" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A284">
         <is>
-          <t xml:space="preserve">8335</t>
+          <t xml:space="preserve">8341</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B284">
         <is>
-          <t xml:space="preserve">Boyd Corporation</t>
+          <t xml:space="preserve">Peloton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C284">
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c s="10" r="D284">
-        <v>44652</v>
+        <v>44600</v>
       </c>
       <c s="11" r="E284">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c s="9" t="inlineStr" r="F284">
         <is>
@@ -9090,30 +9090,30 @@
         </is>
       </c>
       <c s="12" r="G284">
-        <v>44578</v>
+        <v>44600</v>
       </c>
     </row>
     <row r="285" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A285">
         <is>
-          <t xml:space="preserve">8330</t>
+          <t xml:space="preserve">8335</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B285">
         <is>
-          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
+          <t xml:space="preserve">Boyd Corporation</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C285">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D285">
-        <v>44620</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E285">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c s="9" t="inlineStr" r="F285">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c s="12" r="G285">
-        <v>44568</v>
+        <v>44578</v>
       </c>
     </row>
     <row r="286" ht="18" customHeight="0">
@@ -9144,7 +9144,7 @@
         <v>44620</v>
       </c>
       <c s="11" r="E286">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c s="9" t="inlineStr" r="F286">
         <is>
@@ -9158,24 +9158,24 @@
     <row r="287" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A287">
         <is>
-          <t xml:space="preserve">8319</t>
+          <t xml:space="preserve">8330</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B287">
         <is>
-          <t xml:space="preserve">Hematology Oncology Associates PC</t>
+          <t xml:space="preserve">GP Downs LLC dba The Flying Lark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C287">
         <is>
-          <t xml:space="preserve">Medford</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D287">
-        <v>44561</v>
+        <v>44620</v>
       </c>
       <c s="11" r="E287">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c s="9" t="inlineStr" r="F287">
         <is>
@@ -9183,30 +9183,30 @@
         </is>
       </c>
       <c s="12" r="G287">
-        <v>44491</v>
+        <v>44568</v>
       </c>
     </row>
     <row r="288" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A288">
         <is>
-          <t xml:space="preserve">8294</t>
+          <t xml:space="preserve">8319</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B288">
         <is>
-          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
+          <t xml:space="preserve">Hematology Oncology Associates PC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C288">
         <is>
-          <t xml:space="preserve">Lake Oswego</t>
+          <t xml:space="preserve">Medford</t>
         </is>
       </c>
       <c s="10" r="D288">
-        <v>44531</v>
+        <v>44561</v>
       </c>
       <c s="11" r="E288">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F288">
         <is>
@@ -9214,30 +9214,30 @@
         </is>
       </c>
       <c s="12" r="G288">
-        <v>44470</v>
+        <v>44491</v>
       </c>
     </row>
     <row r="289" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A289">
         <is>
-          <t xml:space="preserve">8281</t>
+          <t xml:space="preserve">8294</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B289">
         <is>
-          <t xml:space="preserve">Sulzer</t>
+          <t xml:space="preserve">Eclipse Senior Living Support Center</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C289">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Lake Oswego</t>
         </is>
       </c>
       <c s="10" r="D289">
-        <v>44799</v>
+        <v>44531</v>
       </c>
       <c s="11" r="E289">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c s="9" t="inlineStr" r="F289">
         <is>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c s="12" r="G289">
-        <v>44449</v>
+        <v>44470</v>
       </c>
     </row>
     <row r="290" ht="18" customHeight="0">
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c s="10" r="D290">
-        <v>44743</v>
+        <v>44799</v>
       </c>
       <c s="11" r="E290">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c s="9" t="inlineStr" r="F290">
         <is>
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c s="10" r="D291">
-        <v>44680</v>
+        <v>44743</v>
       </c>
       <c s="11" r="E291">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c s="9" t="inlineStr" r="F291">
         <is>
@@ -9327,10 +9327,10 @@
         </is>
       </c>
       <c s="10" r="D292">
-        <v>44652</v>
+        <v>44680</v>
       </c>
       <c s="11" r="E292">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F292">
         <is>
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c s="10" r="D293">
-        <v>44575</v>
+        <v>44652</v>
       </c>
       <c s="11" r="E293">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c s="9" t="inlineStr" r="F293">
         <is>
@@ -9389,10 +9389,10 @@
         </is>
       </c>
       <c s="10" r="D294">
-        <v>44512</v>
+        <v>44575</v>
       </c>
       <c s="11" r="E294">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c s="9" t="inlineStr" r="F294">
         <is>
@@ -9406,12 +9406,12 @@
     <row r="295" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A295">
         <is>
-          <t xml:space="preserve">8274</t>
+          <t xml:space="preserve">8281</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B295">
         <is>
-          <t xml:space="preserve">4 Leaf LLC</t>
+          <t xml:space="preserve">Sulzer</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C295">
@@ -9420,10 +9420,10 @@
         </is>
       </c>
       <c s="10" r="D295">
-        <v>44469</v>
+        <v>44512</v>
       </c>
       <c s="11" r="E295">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c s="9" t="inlineStr" r="F295">
         <is>
@@ -9431,30 +9431,30 @@
         </is>
       </c>
       <c s="12" r="G295">
-        <v>44456</v>
+        <v>44449</v>
       </c>
     </row>
     <row r="296" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A296">
         <is>
-          <t xml:space="preserve">8260</t>
+          <t xml:space="preserve">8274</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B296">
         <is>
-          <t xml:space="preserve">Lifeways - Umatilla County</t>
+          <t xml:space="preserve">4 Leaf LLC</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C296">
         <is>
-          <t xml:space="preserve">Pendleton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D296">
-        <v>44482</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E296">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c s="9" t="inlineStr" r="F296">
         <is>
@@ -9462,30 +9462,30 @@
         </is>
       </c>
       <c s="12" r="G296">
-        <v>44421</v>
+        <v>44456</v>
       </c>
     </row>
     <row r="297" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A297">
         <is>
-          <t xml:space="preserve">8254</t>
+          <t xml:space="preserve">8260</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B297">
         <is>
-          <t xml:space="preserve">First Transit - Portland</t>
+          <t xml:space="preserve">Lifeways - Umatilla County</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C297">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Pendleton</t>
         </is>
       </c>
       <c s="10" r="D297">
-        <v>44469</v>
+        <v>44482</v>
       </c>
       <c s="11" r="E297">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c s="9" t="inlineStr" r="F297">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c s="12" r="G297">
-        <v>44407</v>
+        <v>44421</v>
       </c>
     </row>
     <row r="298" ht="18" customHeight="0">
@@ -9504,7 +9504,7 @@
       </c>
       <c s="9" t="inlineStr" r="B298">
         <is>
-          <t xml:space="preserve">First Transit - Multnomah</t>
+          <t xml:space="preserve">First Transit - Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C298">
@@ -9516,7 +9516,7 @@
         <v>44469</v>
       </c>
       <c s="11" r="E298">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c s="9" t="inlineStr" r="F298">
         <is>
@@ -9535,19 +9535,19 @@
       </c>
       <c s="9" t="inlineStr" r="B299">
         <is>
-          <t xml:space="preserve">First Transit - Beaverton</t>
+          <t xml:space="preserve">First Transit - Multnomah</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C299">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D299">
         <v>44469</v>
       </c>
       <c s="11" r="E299">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c s="9" t="inlineStr" r="F299">
         <is>
@@ -9561,24 +9561,24 @@
     <row r="300" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A300">
         <is>
-          <t xml:space="preserve">8251</t>
+          <t xml:space="preserve">8254</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B300">
         <is>
-          <t xml:space="preserve">Aramark</t>
+          <t xml:space="preserve">First Transit - Beaverton</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C300">
         <is>
-          <t xml:space="preserve">Nashville, TN</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D300">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E300">
-        <v>402</v>
+        <v>99</v>
       </c>
       <c s="9" t="inlineStr" r="F300">
         <is>
@@ -9586,30 +9586,30 @@
         </is>
       </c>
       <c s="12" r="G300">
-        <v>44399</v>
+        <v>44407</v>
       </c>
     </row>
     <row r="301" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A301">
         <is>
-          <t xml:space="preserve">8240</t>
+          <t xml:space="preserve">8251</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B301">
         <is>
-          <t xml:space="preserve">Mentor Oregon</t>
+          <t xml:space="preserve">Aramark</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C301">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Nashville, TN</t>
         </is>
       </c>
       <c s="10" r="D301">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c s="11" r="E301">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c s="9" t="inlineStr" r="F301">
         <is>
@@ -9617,18 +9617,18 @@
         </is>
       </c>
       <c s="12" r="G301">
-        <v>44383</v>
+        <v>44399</v>
       </c>
     </row>
     <row r="302" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A302">
         <is>
-          <t xml:space="preserve">8106</t>
+          <t xml:space="preserve">8240</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B302">
         <is>
-          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
+          <t xml:space="preserve">Mentor Oregon</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C302">
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c s="10" r="D302">
-        <v>44348</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E302">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F302">
         <is>
@@ -9648,18 +9648,18 @@
         </is>
       </c>
       <c s="12" r="G302">
-        <v>44308</v>
+        <v>44383</v>
       </c>
     </row>
     <row r="303" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A303">
         <is>
-          <t xml:space="preserve">8099</t>
+          <t xml:space="preserve">8106</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B303">
         <is>
-          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
+          <t xml:space="preserve">Thriftbooks - Portland Processing Cente</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C303">
@@ -9668,49 +9668,49 @@
         </is>
       </c>
       <c s="10" r="D303">
-        <v>44347</v>
+        <v>44348</v>
       </c>
       <c s="11" r="E303">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c s="9" t="inlineStr" r="F303">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G303">
-        <v>44291</v>
+        <v>44308</v>
       </c>
     </row>
     <row r="304" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A304">
         <is>
-          <t xml:space="preserve">8068</t>
+          <t xml:space="preserve">8099</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B304">
         <is>
-          <t xml:space="preserve">PERFORMANT</t>
+          <t xml:space="preserve">DSU-Peterbuilt &amp; GMC Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C304">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D304">
-        <v>44311</v>
+        <v>44347</v>
       </c>
       <c s="11" r="E304">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c s="9" t="inlineStr" r="F304">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G304">
-        <v>44253</v>
+        <v>44291</v>
       </c>
     </row>
     <row r="305" ht="18" customHeight="0">
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c s="10" r="D305">
-        <v>44256</v>
+        <v>44311</v>
       </c>
       <c s="11" r="E305">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c s="9" t="inlineStr" r="F305">
         <is>
@@ -9747,32 +9747,32 @@
     <row r="306" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A306">
         <is>
-          <t xml:space="preserve">7843</t>
+          <t xml:space="preserve">8068</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B306">
         <is>
-          <t xml:space="preserve">Simple</t>
+          <t xml:space="preserve">PERFORMANT</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C306">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D306">
-        <v>44358</v>
+        <v>44256</v>
       </c>
       <c s="11" r="E306">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c s="9" t="inlineStr" r="F306">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G306">
-        <v>44225</v>
+        <v>44253</v>
       </c>
     </row>
     <row r="307" ht="18" customHeight="0">
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c s="10" r="D307">
-        <v>44330</v>
+        <v>44358</v>
       </c>
       <c s="11" r="E307">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c s="9" t="inlineStr" r="F307">
         <is>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c s="10" r="D308">
-        <v>44323</v>
+        <v>44330</v>
       </c>
       <c s="11" r="E308">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c s="9" t="inlineStr" r="F308">
         <is>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c s="10" r="D309">
-        <v>44288</v>
+        <v>44323</v>
       </c>
       <c s="11" r="E309">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c s="9" t="inlineStr" r="F309">
         <is>
@@ -9871,12 +9871,12 @@
     <row r="310" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A310">
         <is>
-          <t xml:space="preserve">7842</t>
+          <t xml:space="preserve">7843</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B310">
         <is>
-          <t xml:space="preserve">azlo</t>
+          <t xml:space="preserve">Simple</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C310">
@@ -9888,7 +9888,7 @@
         <v>44288</v>
       </c>
       <c s="11" r="E310">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c s="9" t="inlineStr" r="F310">
         <is>
@@ -9902,24 +9902,24 @@
     <row r="311" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A311">
         <is>
-          <t xml:space="preserve">7811</t>
+          <t xml:space="preserve">7842</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B311">
         <is>
-          <t xml:space="preserve">SunPower</t>
+          <t xml:space="preserve">azlo</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C311">
         <is>
-          <t xml:space="preserve">Hillsboro</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D311">
-        <v>44469</v>
+        <v>44288</v>
       </c>
       <c s="11" r="E311">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c s="9" t="inlineStr" r="F311">
         <is>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c s="12" r="G311">
-        <v>44203</v>
+        <v>44225</v>
       </c>
     </row>
     <row r="312" ht="18" customHeight="0">
@@ -9947,10 +9947,10 @@
         </is>
       </c>
       <c s="10" r="D312">
-        <v>44264</v>
+        <v>44469</v>
       </c>
       <c s="11" r="E312">
-        <v>172</v>
+        <v>9</v>
       </c>
       <c s="9" t="inlineStr" r="F312">
         <is>
@@ -9964,24 +9964,24 @@
     <row r="313" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A313">
         <is>
-          <t xml:space="preserve">7796</t>
+          <t xml:space="preserve">7811</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B313">
         <is>
-          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
+          <t xml:space="preserve">SunPower</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C313">
         <is>
-          <t xml:space="preserve">Grants Pass</t>
+          <t xml:space="preserve">Hillsboro</t>
         </is>
       </c>
       <c s="10" r="D313">
-        <v>44242</v>
+        <v>44264</v>
       </c>
       <c s="11" r="E313">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c s="9" t="inlineStr" r="F313">
         <is>
@@ -9989,100 +9989,100 @@
         </is>
       </c>
       <c s="12" r="G313">
-        <v>44180</v>
+        <v>44203</v>
       </c>
     </row>
     <row r="314" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A314">
         <is>
-          <t xml:space="preserve">7583</t>
+          <t xml:space="preserve">7796</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B314">
         <is>
-          <t xml:space="preserve">Southwest Airlines</t>
+          <t xml:space="preserve">NPL - Central Point - Grants Pass</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C314">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Grants Pass</t>
         </is>
       </c>
       <c s="10" r="D314">
-        <v>44270</v>
+        <v>44242</v>
       </c>
       <c s="11" r="E314">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c s="9" t="inlineStr" r="F314">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G314">
-        <v>44168</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="315" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A315">
         <is>
-          <t xml:space="preserve">7578</t>
+          <t xml:space="preserve">7583</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B315">
         <is>
-          <t xml:space="preserve">Villasport</t>
+          <t xml:space="preserve">Southwest Airlines</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C315">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D315">
-        <v>44214</v>
+        <v>44270</v>
       </c>
       <c s="11" r="E315">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c s="9" t="inlineStr" r="F315">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G315">
-        <v>44160</v>
+        <v>44168</v>
       </c>
     </row>
     <row r="316" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A316">
         <is>
-          <t xml:space="preserve">7510</t>
+          <t xml:space="preserve">7578</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B316">
         <is>
-          <t xml:space="preserve">Providence</t>
+          <t xml:space="preserve">Villasport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C316">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D316">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E316">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c s="9" t="inlineStr" r="F316">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G316">
-        <v>44151</v>
+        <v>44160</v>
       </c>
     </row>
     <row r="317" ht="18" customHeight="0">
@@ -10105,11 +10105,11 @@
         <v>44211</v>
       </c>
       <c s="11" r="E317">
-        <v>5</v>
+        <v>177</v>
       </c>
       <c s="9" t="inlineStr" r="F317">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c s="12" r="G317">
@@ -10119,12 +10119,12 @@
     <row r="318" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A318">
         <is>
-          <t xml:space="preserve">7508</t>
+          <t xml:space="preserve">7510</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B318">
         <is>
-          <t xml:space="preserve">Elmer's Restaurants</t>
+          <t xml:space="preserve">Providence</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C318">
@@ -10133,29 +10133,29 @@
         </is>
       </c>
       <c s="10" r="D318">
-        <v>44148</v>
+        <v>44211</v>
       </c>
       <c s="11" r="E318">
-        <v>280</v>
+        <v>5</v>
       </c>
       <c s="9" t="inlineStr" r="F318">
         <is>
-          <t xml:space="preserve">Temporary Layoff</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G318">
-        <v>44148</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="319" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A319">
         <is>
-          <t xml:space="preserve">7436</t>
+          <t xml:space="preserve">7508</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B319">
         <is>
-          <t xml:space="preserve">Macy's Inc</t>
+          <t xml:space="preserve">Elmer's Restaurants</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C319">
@@ -10164,69 +10164,69 @@
         </is>
       </c>
       <c s="10" r="D319">
-        <v>44214</v>
+        <v>44148</v>
       </c>
       <c s="11" r="E319">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c s="9" t="inlineStr" r="F319">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Temporary Layoff</t>
         </is>
       </c>
       <c s="12" r="G319">
-        <v>44151</v>
+        <v>44148</v>
       </c>
     </row>
     <row r="320" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A320">
         <is>
-          <t xml:space="preserve">7401</t>
+          <t xml:space="preserve">7436</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B320">
         <is>
-          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
+          <t xml:space="preserve">Macy's Inc</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C320">
         <is>
-          <t xml:space="preserve">Beaverton</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D320">
-        <v>44186</v>
+        <v>44214</v>
       </c>
       <c s="11" r="E320">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c s="9" t="inlineStr" r="F320">
         <is>
-          <t xml:space="preserve">Reduction</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G320">
-        <v>44127</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="321" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A321">
         <is>
-          <t xml:space="preserve">7332</t>
+          <t xml:space="preserve">7401</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B321">
         <is>
-          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
+          <t xml:space="preserve">SYUFY Enterprises - VillaSport</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C321">
         <is>
-          <t xml:space="preserve">Portland</t>
+          <t xml:space="preserve">Beaverton</t>
         </is>
       </c>
       <c s="10" r="D321">
-        <v>44104</v>
+        <v>44186</v>
       </c>
       <c s="11" r="E321">
         <v>59</v>
@@ -10237,158 +10237,190 @@
         </is>
       </c>
       <c s="12" r="G321">
-        <v>44104</v>
+        <v>44127</v>
       </c>
     </row>
     <row r="322" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A322">
         <is>
-          <t xml:space="preserve">7309</t>
+          <t xml:space="preserve">7332</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B322">
         <is>
-          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
+          <t xml:space="preserve">DoubleTree - Hilton Portland</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C322">
         <is>
-          <t xml:space="preserve">Elgin</t>
+          <t xml:space="preserve">Portland</t>
         </is>
       </c>
       <c s="10" r="D322">
-        <v>44197</v>
+        <v>44104</v>
       </c>
       <c s="11" r="E322">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c s="9" t="inlineStr" r="F322">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Reduction</t>
         </is>
       </c>
       <c s="12" r="G322">
-        <v>44151</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="323" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A323">
         <is>
-          <t xml:space="preserve">8470</t>
+          <t xml:space="preserve">7309</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B323">
         <is>
-          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
+          <t xml:space="preserve">Boise Cascade - Elgin Plywood Facility</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C323">
         <is>
-          <t xml:space="preserve">ELGIN                         </t>
-        </is>
-      </c>
-      <c s="9" t="str" r="D323"/>
-      <c s="13" t="str" r="E323"/>
+          <t xml:space="preserve">Elgin</t>
+        </is>
+      </c>
+      <c s="10" r="D323">
+        <v>44197</v>
+      </c>
+      <c s="11" r="E323">
+        <v>229</v>
+      </c>
       <c s="9" t="inlineStr" r="F323">
         <is>
-          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
+          <t xml:space="preserve">Permanent closure</t>
         </is>
       </c>
       <c s="12" r="G323">
-        <v>44909</v>
+        <v>44151</v>
       </c>
     </row>
     <row r="324" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A324">
         <is>
-          <t xml:space="preserve">8592</t>
+          <t xml:space="preserve">8470</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B324">
         <is>
-          <t xml:space="preserve">Rise Services, Inc.</t>
+          <t xml:space="preserve">BOISE CASCADE ELGIN PLYWOOD MILL       </t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C324">
         <is>
-          <t xml:space="preserve">Mesa, AZ</t>
+          <t xml:space="preserve">ELGIN                         </t>
         </is>
       </c>
       <c s="9" t="str" r="D324"/>
       <c s="13" t="str" r="E324"/>
       <c s="9" t="inlineStr" r="F324">
         <is>
-          <t xml:space="preserve">Permanent closure</t>
+          <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
       <c s="12" r="G324">
-        <v>45125</v>
+        <v>44909</v>
       </c>
     </row>
     <row r="325" ht="18" customHeight="0">
       <c s="8" t="inlineStr" r="A325">
         <is>
-          <t xml:space="preserve">9324</t>
+          <t xml:space="preserve">8592</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="B325">
         <is>
-          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+          <t xml:space="preserve">Rise Services, Inc.</t>
         </is>
       </c>
       <c s="9" t="inlineStr" r="C325">
         <is>
-          <t xml:space="preserve">Los Angeles, CA</t>
+          <t xml:space="preserve">Mesa, AZ</t>
         </is>
       </c>
       <c s="9" t="str" r="D325"/>
       <c s="13" t="str" r="E325"/>
       <c s="9" t="inlineStr" r="F325">
         <is>
+          <t xml:space="preserve">Permanent closure</t>
+        </is>
+      </c>
+      <c s="12" r="G325">
+        <v>45125</v>
+      </c>
+    </row>
+    <row r="326" ht="18" customHeight="0">
+      <c s="8" t="inlineStr" r="A326">
+        <is>
+          <t xml:space="preserve">9324</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="B326">
+        <is>
+          <t xml:space="preserve">Zeco Systems, Inc. dba Shell EV Chargin</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C326">
+        <is>
+          <t xml:space="preserve">Los Angeles, CA</t>
+        </is>
+      </c>
+      <c s="9" t="str" r="D326"/>
+      <c s="13" t="str" r="E326"/>
+      <c s="9" t="inlineStr" r="F326">
+        <is>
           <t xml:space="preserve">Large Layoff - 10 or more workers</t>
         </is>
       </c>
-      <c s="12" r="G325">
+      <c s="12" r="G326">
         <v>45887</v>
       </c>
     </row>
-    <row r="326" ht="3.6" customHeight="0">
-      <c s="14" t="inlineStr" r="A326">
+    <row r="327" ht="3.55" customHeight="0">
+      <c s="14" t="inlineStr" r="A327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="B326">
+      <c s="14" t="inlineStr" r="B327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="C326">
+      <c s="14" t="inlineStr" r="C327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="D326">
+      <c s="14" t="inlineStr" r="D327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="E326">
+      <c s="14" t="inlineStr" r="E327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="F326">
+      <c s="14" t="inlineStr" r="F327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="14" t="inlineStr" r="G326">
+      <c s="14" t="inlineStr" r="G327">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
+    <row r="328" ht="0.05" customHeight="1"/>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:A2"/>
@@ -10398,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/29/2026 8:45:28 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/30/2026 10:48:38 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>

--- a/data/states/or/latest.xlsx
+++ b/data/states/or/latest.xlsx
@@ -10430,7 +10430,7 @@
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/30/2026 10:48:38 AM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;8 10/30/2026 8:29:13 PM &amp;R&amp;"Arial,Regular"&amp;8 Page 1 of 1 </oddFooter>
   </headerFooter>
   <drawing r:id="rId7"/>
 </worksheet>
